--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G5">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G38">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>6.57</v>
+        <v>2.45</v>
       </c>
       <c r="O43">
-        <v>3.38</v>
+        <v>2.78</v>
       </c>
       <c r="P43">
-        <v>1.51</v>
+        <v>2.92</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.45</v>
+        <v>6.57</v>
       </c>
       <c r="O44">
-        <v>2.78</v>
+        <v>3.38</v>
       </c>
       <c r="P44">
-        <v>2.92</v>
+        <v>1.51</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G50">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G54">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G77">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G92">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G98">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G105">

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G42">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G59">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G61">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G77">

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G19">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G42">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G77">

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G60">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G115">

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G38">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G39">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G42">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G61">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G77">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G88">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G92">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G98">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G105">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G115">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G119">

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G42">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G103">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G105">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G115">

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G42">

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q45">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC53">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G39">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.45</v>
+        <v>6.57</v>
       </c>
       <c r="O43">
-        <v>2.78</v>
+        <v>3.38</v>
       </c>
       <c r="P43">
-        <v>2.92</v>
+        <v>1.51</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>6.57</v>
+        <v>2.45</v>
       </c>
       <c r="O44">
-        <v>3.38</v>
+        <v>2.78</v>
       </c>
       <c r="P44">
-        <v>1.51</v>
+        <v>2.92</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O53">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P53">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB53">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9150,10 +9150,10 @@
         <v>0</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC54">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G77">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G92">

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G77">

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC23">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G76">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G83">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G84">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G92">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G105">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G118">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G119">

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G77">

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G99">

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17789,10 +17789,10 @@
         <v>0</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC107">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13557,10 +13557,10 @@
         <v>0</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE81">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q117">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU119"/>
+  <dimension ref="A1:AU112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G93">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G94">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G95">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G96">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,22 +16404,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,22 +16567,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16648,10 +16648,10 @@
         <v>0</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC100">
         <v>0</v>
@@ -16730,7 +16730,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G101">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G103">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G105">
@@ -17545,22 +17545,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,22 +17708,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O107">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="P107">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17789,10 +17789,10 @@
         <v>0</v>
       </c>
       <c r="AA107">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB107">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G108">
@@ -18029,27 +18029,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G109">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-08-14 21:00:00</t>
+          <t>2026-08-14 22:00:00</t>
         </is>
       </c>
     </row>
@@ -18192,27 +18192,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-08-14 21:00:00</t>
+          <t>2026-08-14 23:00:00</t>
         </is>
       </c>
     </row>
@@ -18355,27 +18355,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G111">
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-08-14 21:00:00</t>
+          <t>2026-08-14 23:00:00</t>
         </is>
       </c>
     </row>
@@ -18518,27 +18518,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G112">
@@ -18668,1147 +18668,6 @@
         <v>0</v>
       </c>
       <c r="AU112" t="inlineStr">
-        <is>
-          <t>2026-08-14 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Spartak Subotica</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Teleoptik</t>
-        </is>
-      </c>
-      <c r="G113">
-        <v>0</v>
-      </c>
-      <c r="H113">
-        <v>0</v>
-      </c>
-      <c r="I113">
-        <v>0</v>
-      </c>
-      <c r="J113">
-        <v>0</v>
-      </c>
-      <c r="K113">
-        <v>0</v>
-      </c>
-      <c r="L113">
-        <v>0</v>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N113">
-        <v>0</v>
-      </c>
-      <c r="O113">
-        <v>0</v>
-      </c>
-      <c r="P113">
-        <v>0</v>
-      </c>
-      <c r="Q113">
-        <v>0</v>
-      </c>
-      <c r="R113">
-        <v>0</v>
-      </c>
-      <c r="S113">
-        <v>0</v>
-      </c>
-      <c r="T113">
-        <v>0</v>
-      </c>
-      <c r="U113">
-        <v>0</v>
-      </c>
-      <c r="V113">
-        <v>0</v>
-      </c>
-      <c r="W113">
-        <v>0</v>
-      </c>
-      <c r="X113">
-        <v>0</v>
-      </c>
-      <c r="Y113">
-        <v>0</v>
-      </c>
-      <c r="Z113">
-        <v>0</v>
-      </c>
-      <c r="AA113">
-        <v>0</v>
-      </c>
-      <c r="AB113">
-        <v>0</v>
-      </c>
-      <c r="AC113">
-        <v>0</v>
-      </c>
-      <c r="AD113">
-        <v>0</v>
-      </c>
-      <c r="AE113">
-        <v>0</v>
-      </c>
-      <c r="AF113">
-        <v>0</v>
-      </c>
-      <c r="AG113">
-        <v>0</v>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ113">
-        <v>0</v>
-      </c>
-      <c r="AK113">
-        <v>0</v>
-      </c>
-      <c r="AL113">
-        <v>0</v>
-      </c>
-      <c r="AM113">
-        <v>-1</v>
-      </c>
-      <c r="AN113">
-        <v>-1</v>
-      </c>
-      <c r="AO113">
-        <v>-1</v>
-      </c>
-      <c r="AP113">
-        <v>-1</v>
-      </c>
-      <c r="AQ113">
-        <v>0</v>
-      </c>
-      <c r="AR113">
-        <v>0</v>
-      </c>
-      <c r="AS113">
-        <v>0</v>
-      </c>
-      <c r="AT113">
-        <v>0</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>2026-08-14 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Naftagas</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Dubočica</t>
-        </is>
-      </c>
-      <c r="G114">
-        <v>0</v>
-      </c>
-      <c r="H114">
-        <v>0</v>
-      </c>
-      <c r="I114">
-        <v>0</v>
-      </c>
-      <c r="J114">
-        <v>0</v>
-      </c>
-      <c r="K114">
-        <v>0</v>
-      </c>
-      <c r="L114">
-        <v>0</v>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N114">
-        <v>0</v>
-      </c>
-      <c r="O114">
-        <v>0</v>
-      </c>
-      <c r="P114">
-        <v>0</v>
-      </c>
-      <c r="Q114">
-        <v>0</v>
-      </c>
-      <c r="R114">
-        <v>0</v>
-      </c>
-      <c r="S114">
-        <v>0</v>
-      </c>
-      <c r="T114">
-        <v>0</v>
-      </c>
-      <c r="U114">
-        <v>0</v>
-      </c>
-      <c r="V114">
-        <v>0</v>
-      </c>
-      <c r="W114">
-        <v>0</v>
-      </c>
-      <c r="X114">
-        <v>0</v>
-      </c>
-      <c r="Y114">
-        <v>0</v>
-      </c>
-      <c r="Z114">
-        <v>0</v>
-      </c>
-      <c r="AA114">
-        <v>0</v>
-      </c>
-      <c r="AB114">
-        <v>0</v>
-      </c>
-      <c r="AC114">
-        <v>0</v>
-      </c>
-      <c r="AD114">
-        <v>0</v>
-      </c>
-      <c r="AE114">
-        <v>0</v>
-      </c>
-      <c r="AF114">
-        <v>0</v>
-      </c>
-      <c r="AG114">
-        <v>0</v>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ114">
-        <v>0</v>
-      </c>
-      <c r="AK114">
-        <v>0</v>
-      </c>
-      <c r="AL114">
-        <v>0</v>
-      </c>
-      <c r="AM114">
-        <v>-1</v>
-      </c>
-      <c r="AN114">
-        <v>-1</v>
-      </c>
-      <c r="AO114">
-        <v>-1</v>
-      </c>
-      <c r="AP114">
-        <v>-1</v>
-      </c>
-      <c r="AQ114">
-        <v>0</v>
-      </c>
-      <c r="AR114">
-        <v>0</v>
-      </c>
-      <c r="AS114">
-        <v>0</v>
-      </c>
-      <c r="AT114">
-        <v>0</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>2026-08-14 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Voždovac</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Grafičar</t>
-        </is>
-      </c>
-      <c r="G115">
-        <v>0</v>
-      </c>
-      <c r="H115">
-        <v>0</v>
-      </c>
-      <c r="I115">
-        <v>0</v>
-      </c>
-      <c r="J115">
-        <v>0</v>
-      </c>
-      <c r="K115">
-        <v>0</v>
-      </c>
-      <c r="L115">
-        <v>0</v>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N115">
-        <v>0</v>
-      </c>
-      <c r="O115">
-        <v>0</v>
-      </c>
-      <c r="P115">
-        <v>0</v>
-      </c>
-      <c r="Q115">
-        <v>0</v>
-      </c>
-      <c r="R115">
-        <v>0</v>
-      </c>
-      <c r="S115">
-        <v>0</v>
-      </c>
-      <c r="T115">
-        <v>0</v>
-      </c>
-      <c r="U115">
-        <v>0</v>
-      </c>
-      <c r="V115">
-        <v>0</v>
-      </c>
-      <c r="W115">
-        <v>0</v>
-      </c>
-      <c r="X115">
-        <v>0</v>
-      </c>
-      <c r="Y115">
-        <v>0</v>
-      </c>
-      <c r="Z115">
-        <v>0</v>
-      </c>
-      <c r="AA115">
-        <v>0</v>
-      </c>
-      <c r="AB115">
-        <v>0</v>
-      </c>
-      <c r="AC115">
-        <v>0</v>
-      </c>
-      <c r="AD115">
-        <v>0</v>
-      </c>
-      <c r="AE115">
-        <v>0</v>
-      </c>
-      <c r="AF115">
-        <v>0</v>
-      </c>
-      <c r="AG115">
-        <v>0</v>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ115">
-        <v>0</v>
-      </c>
-      <c r="AK115">
-        <v>0</v>
-      </c>
-      <c r="AL115">
-        <v>0</v>
-      </c>
-      <c r="AM115">
-        <v>-1</v>
-      </c>
-      <c r="AN115">
-        <v>-1</v>
-      </c>
-      <c r="AO115">
-        <v>-1</v>
-      </c>
-      <c r="AP115">
-        <v>-1</v>
-      </c>
-      <c r="AQ115">
-        <v>0</v>
-      </c>
-      <c r="AR115">
-        <v>0</v>
-      </c>
-      <c r="AS115">
-        <v>0</v>
-      </c>
-      <c r="AT115">
-        <v>0</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>2026-08-14 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Vancouver FC</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Pacific FC</t>
-        </is>
-      </c>
-      <c r="G116">
-        <v>0</v>
-      </c>
-      <c r="H116">
-        <v>0</v>
-      </c>
-      <c r="I116">
-        <v>0</v>
-      </c>
-      <c r="J116">
-        <v>0</v>
-      </c>
-      <c r="K116">
-        <v>0</v>
-      </c>
-      <c r="L116">
-        <v>0</v>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N116">
-        <v>0</v>
-      </c>
-      <c r="O116">
-        <v>0</v>
-      </c>
-      <c r="P116">
-        <v>0</v>
-      </c>
-      <c r="Q116">
-        <v>0</v>
-      </c>
-      <c r="R116">
-        <v>0</v>
-      </c>
-      <c r="S116">
-        <v>0</v>
-      </c>
-      <c r="T116">
-        <v>0</v>
-      </c>
-      <c r="U116">
-        <v>0</v>
-      </c>
-      <c r="V116">
-        <v>0</v>
-      </c>
-      <c r="W116">
-        <v>0</v>
-      </c>
-      <c r="X116">
-        <v>0</v>
-      </c>
-      <c r="Y116">
-        <v>0</v>
-      </c>
-      <c r="Z116">
-        <v>0</v>
-      </c>
-      <c r="AA116">
-        <v>0</v>
-      </c>
-      <c r="AB116">
-        <v>0</v>
-      </c>
-      <c r="AC116">
-        <v>0</v>
-      </c>
-      <c r="AD116">
-        <v>0</v>
-      </c>
-      <c r="AE116">
-        <v>0</v>
-      </c>
-      <c r="AF116">
-        <v>0</v>
-      </c>
-      <c r="AG116">
-        <v>0</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ116">
-        <v>0</v>
-      </c>
-      <c r="AK116">
-        <v>0</v>
-      </c>
-      <c r="AL116">
-        <v>0</v>
-      </c>
-      <c r="AM116">
-        <v>-1</v>
-      </c>
-      <c r="AN116">
-        <v>-1</v>
-      </c>
-      <c r="AO116">
-        <v>-1</v>
-      </c>
-      <c r="AP116">
-        <v>-1</v>
-      </c>
-      <c r="AQ116">
-        <v>0</v>
-      </c>
-      <c r="AR116">
-        <v>0</v>
-      </c>
-      <c r="AS116">
-        <v>0</v>
-      </c>
-      <c r="AT116">
-        <v>0</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>2026-08-14 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Denver Summit W</t>
-        </is>
-      </c>
-      <c r="G117">
-        <v>0</v>
-      </c>
-      <c r="H117">
-        <v>0</v>
-      </c>
-      <c r="I117">
-        <v>0</v>
-      </c>
-      <c r="J117">
-        <v>0</v>
-      </c>
-      <c r="K117">
-        <v>0</v>
-      </c>
-      <c r="L117">
-        <v>0</v>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N117">
-        <v>1.86</v>
-      </c>
-      <c r="O117">
-        <v>3.6</v>
-      </c>
-      <c r="P117">
-        <v>3.1</v>
-      </c>
-      <c r="Q117">
-        <v>0</v>
-      </c>
-      <c r="R117">
-        <v>0</v>
-      </c>
-      <c r="S117">
-        <v>0</v>
-      </c>
-      <c r="T117">
-        <v>0</v>
-      </c>
-      <c r="U117">
-        <v>0</v>
-      </c>
-      <c r="V117">
-        <v>0</v>
-      </c>
-      <c r="W117">
-        <v>0</v>
-      </c>
-      <c r="X117">
-        <v>0</v>
-      </c>
-      <c r="Y117">
-        <v>0</v>
-      </c>
-      <c r="Z117">
-        <v>0</v>
-      </c>
-      <c r="AA117">
-        <v>0</v>
-      </c>
-      <c r="AB117">
-        <v>0</v>
-      </c>
-      <c r="AC117">
-        <v>0</v>
-      </c>
-      <c r="AD117">
-        <v>0</v>
-      </c>
-      <c r="AE117">
-        <v>0</v>
-      </c>
-      <c r="AF117">
-        <v>0</v>
-      </c>
-      <c r="AG117">
-        <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ117">
-        <v>0</v>
-      </c>
-      <c r="AK117">
-        <v>0</v>
-      </c>
-      <c r="AL117">
-        <v>0</v>
-      </c>
-      <c r="AM117">
-        <v>-1</v>
-      </c>
-      <c r="AN117">
-        <v>-1</v>
-      </c>
-      <c r="AO117">
-        <v>-1</v>
-      </c>
-      <c r="AP117">
-        <v>-1</v>
-      </c>
-      <c r="AQ117">
-        <v>0</v>
-      </c>
-      <c r="AR117">
-        <v>0</v>
-      </c>
-      <c r="AS117">
-        <v>0</v>
-      </c>
-      <c r="AT117">
-        <v>0</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>2026-08-14 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Chicago Red Stars</t>
-        </is>
-      </c>
-      <c r="G118">
-        <v>0</v>
-      </c>
-      <c r="H118">
-        <v>0</v>
-      </c>
-      <c r="I118">
-        <v>0</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
-      </c>
-      <c r="K118">
-        <v>0</v>
-      </c>
-      <c r="L118">
-        <v>0</v>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N118">
-        <v>0</v>
-      </c>
-      <c r="O118">
-        <v>0</v>
-      </c>
-      <c r="P118">
-        <v>0</v>
-      </c>
-      <c r="Q118">
-        <v>0</v>
-      </c>
-      <c r="R118">
-        <v>0</v>
-      </c>
-      <c r="S118">
-        <v>0</v>
-      </c>
-      <c r="T118">
-        <v>0</v>
-      </c>
-      <c r="U118">
-        <v>0</v>
-      </c>
-      <c r="V118">
-        <v>0</v>
-      </c>
-      <c r="W118">
-        <v>0</v>
-      </c>
-      <c r="X118">
-        <v>0</v>
-      </c>
-      <c r="Y118">
-        <v>0</v>
-      </c>
-      <c r="Z118">
-        <v>0</v>
-      </c>
-      <c r="AA118">
-        <v>0</v>
-      </c>
-      <c r="AB118">
-        <v>0</v>
-      </c>
-      <c r="AC118">
-        <v>0</v>
-      </c>
-      <c r="AD118">
-        <v>0</v>
-      </c>
-      <c r="AE118">
-        <v>0</v>
-      </c>
-      <c r="AF118">
-        <v>0</v>
-      </c>
-      <c r="AG118">
-        <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ118">
-        <v>0</v>
-      </c>
-      <c r="AK118">
-        <v>0</v>
-      </c>
-      <c r="AL118">
-        <v>0</v>
-      </c>
-      <c r="AM118">
-        <v>-1</v>
-      </c>
-      <c r="AN118">
-        <v>-1</v>
-      </c>
-      <c r="AO118">
-        <v>-1</v>
-      </c>
-      <c r="AP118">
-        <v>-1</v>
-      </c>
-      <c r="AQ118">
-        <v>0</v>
-      </c>
-      <c r="AR118">
-        <v>0</v>
-      </c>
-      <c r="AS118">
-        <v>0</v>
-      </c>
-      <c r="AT118">
-        <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>2026-08-14 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="G119">
-        <v>0</v>
-      </c>
-      <c r="H119">
-        <v>0</v>
-      </c>
-      <c r="I119">
-        <v>0</v>
-      </c>
-      <c r="J119">
-        <v>0</v>
-      </c>
-      <c r="K119">
-        <v>0</v>
-      </c>
-      <c r="L119">
-        <v>0</v>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N119">
-        <v>0</v>
-      </c>
-      <c r="O119">
-        <v>0</v>
-      </c>
-      <c r="P119">
-        <v>0</v>
-      </c>
-      <c r="Q119">
-        <v>0</v>
-      </c>
-      <c r="R119">
-        <v>0</v>
-      </c>
-      <c r="S119">
-        <v>0</v>
-      </c>
-      <c r="T119">
-        <v>0</v>
-      </c>
-      <c r="U119">
-        <v>0</v>
-      </c>
-      <c r="V119">
-        <v>0</v>
-      </c>
-      <c r="W119">
-        <v>0</v>
-      </c>
-      <c r="X119">
-        <v>0</v>
-      </c>
-      <c r="Y119">
-        <v>0</v>
-      </c>
-      <c r="Z119">
-        <v>0</v>
-      </c>
-      <c r="AA119">
-        <v>0</v>
-      </c>
-      <c r="AB119">
-        <v>0</v>
-      </c>
-      <c r="AC119">
-        <v>0</v>
-      </c>
-      <c r="AD119">
-        <v>0</v>
-      </c>
-      <c r="AE119">
-        <v>0</v>
-      </c>
-      <c r="AF119">
-        <v>0</v>
-      </c>
-      <c r="AG119">
-        <v>0</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ119">
-        <v>0</v>
-      </c>
-      <c r="AK119">
-        <v>0</v>
-      </c>
-      <c r="AL119">
-        <v>0</v>
-      </c>
-      <c r="AM119">
-        <v>-1</v>
-      </c>
-      <c r="AN119">
-        <v>-1</v>
-      </c>
-      <c r="AO119">
-        <v>-1</v>
-      </c>
-      <c r="AP119">
-        <v>-1</v>
-      </c>
-      <c r="AQ119">
-        <v>0</v>
-      </c>
-      <c r="AR119">
-        <v>0</v>
-      </c>
-      <c r="AS119">
-        <v>0</v>
-      </c>
-      <c r="AT119">
-        <v>0</v>
-      </c>
-      <c r="AU119" t="inlineStr">
         <is>
           <t>2026-08-14 23:00:00</t>
         </is>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="Q66">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9313,10 +9313,10 @@
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC55">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G92">

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X5">
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1622,55 +1622,55 @@
         <v>2.26</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1948,55 +1948,55 @@
         <v>3.28</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>2.85</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>2.6</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,10 +5045,10 @@
         <v>3.12</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -5057,43 +5057,43 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
         <v>0</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5371,55 +5371,55 @@
         <v>2</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>3.31</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G42">
@@ -7653,55 +7653,55 @@
         <v>2.48</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q51">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G4">
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.25</v>
+        <v>1.44</v>
       </c>
       <c r="O4">
-        <v>3.73</v>
+        <v>5.16</v>
       </c>
       <c r="P4">
-        <v>2.12</v>
+        <v>6.24</v>
       </c>
       <c r="Q4">
-        <v>3.7</v>
+        <v>1.75</v>
       </c>
       <c r="R4">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="S4">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="T4">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="U4">
-        <v>2.29</v>
+        <v>1.84</v>
       </c>
       <c r="V4">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="W4">
+        <v>1.19</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>1.06</v>
+      </c>
+      <c r="Z4">
+        <v>6.2</v>
+      </c>
+      <c r="AA4">
+        <v>1.32</v>
+      </c>
+      <c r="AB4">
+        <v>3.05</v>
+      </c>
+      <c r="AC4">
+        <v>1.82</v>
+      </c>
+      <c r="AD4">
+        <v>2</v>
+      </c>
+      <c r="AE4">
+        <v>1.36</v>
+      </c>
+      <c r="AF4">
+        <v>1.47</v>
+      </c>
+      <c r="AG4">
+        <v>2.46</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.13</v>
       </c>
-      <c r="X4">
-        <v>1.01</v>
-      </c>
-      <c r="Y4">
-        <v>1.12</v>
-      </c>
-      <c r="Z4">
-        <v>4.65</v>
-      </c>
-      <c r="AA4">
-        <v>1.57</v>
-      </c>
-      <c r="AB4">
-        <v>2.2</v>
-      </c>
-      <c r="AC4">
-        <v>2.33</v>
-      </c>
-      <c r="AD4">
-        <v>1.48</v>
-      </c>
-      <c r="AE4">
-        <v>1.16</v>
-      </c>
-      <c r="AF4">
-        <v>1.48</v>
-      </c>
-      <c r="AG4">
-        <v>2.47</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.22</v>
-      </c>
       <c r="AK4">
-        <v>1.24</v>
+        <v>2.65</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.44</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
-        <v>5.16</v>
+        <v>3.73</v>
       </c>
       <c r="P5">
-        <v>6.24</v>
+        <v>2.12</v>
       </c>
       <c r="Q5">
-        <v>1.75</v>
+        <v>3.7</v>
       </c>
       <c r="R5">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="S5">
+        <v>1.25</v>
+      </c>
+      <c r="T5">
+        <v>3.6</v>
+      </c>
+      <c r="U5">
+        <v>2.29</v>
+      </c>
+      <c r="V5">
+        <v>1.57</v>
+      </c>
+      <c r="W5">
+        <v>1.13</v>
+      </c>
+      <c r="X5">
+        <v>1.01</v>
+      </c>
+      <c r="Y5">
+        <v>1.12</v>
+      </c>
+      <c r="Z5">
+        <v>4.65</v>
+      </c>
+      <c r="AA5">
+        <v>1.57</v>
+      </c>
+      <c r="AB5">
+        <v>2.2</v>
+      </c>
+      <c r="AC5">
+        <v>2.33</v>
+      </c>
+      <c r="AD5">
+        <v>1.48</v>
+      </c>
+      <c r="AE5">
         <v>1.16</v>
       </c>
-      <c r="T5">
-        <v>4.2</v>
-      </c>
-      <c r="U5">
-        <v>1.84</v>
-      </c>
-      <c r="V5">
-        <v>1.81</v>
-      </c>
-      <c r="W5">
-        <v>1.19</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>1.06</v>
-      </c>
-      <c r="Z5">
-        <v>6.2</v>
-      </c>
-      <c r="AA5">
-        <v>1.32</v>
-      </c>
-      <c r="AB5">
-        <v>3.05</v>
-      </c>
-      <c r="AC5">
-        <v>1.82</v>
-      </c>
-      <c r="AD5">
-        <v>2</v>
-      </c>
-      <c r="AE5">
-        <v>1.36</v>
-      </c>
       <c r="AF5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG5">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>2.65</v>
+        <v>1.24</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q79">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU112"/>
+  <dimension ref="A1:AU111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2763,55 +2763,55 @@
         <v>4.65</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -4556,55 +4556,55 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11402,55 +11402,55 @@
         <v>3.16</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -13195,55 +13195,55 @@
         <v>7.75</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14040,10 +14040,10 @@
         <v>0</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC84">
         <v>0</v>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G93">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,22 +16241,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16485,10 +16485,10 @@
         <v>0</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC99">
         <v>0</v>
@@ -16567,22 +16567,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O100">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="P100">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16648,10 +16648,10 @@
         <v>0</v>
       </c>
       <c r="AA100">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB100">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC100">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G107">
@@ -17866,27 +17866,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G108">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-08-14 21:00:00</t>
+          <t>2026-08-14 22:00:00</t>
         </is>
       </c>
     </row>
@@ -18029,12 +18029,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-08-14 22:00:00</t>
+          <t>2026-08-14 23:00:00</t>
         </is>
       </c>
     </row>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O110">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P110">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G111">
@@ -18505,169 +18505,6 @@
         <v>0</v>
       </c>
       <c r="AU111" t="inlineStr">
-        <is>
-          <t>2026-08-14 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="G112">
-        <v>0</v>
-      </c>
-      <c r="H112">
-        <v>0</v>
-      </c>
-      <c r="I112">
-        <v>0</v>
-      </c>
-      <c r="J112">
-        <v>0</v>
-      </c>
-      <c r="K112">
-        <v>0</v>
-      </c>
-      <c r="L112">
-        <v>0</v>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N112">
-        <v>0</v>
-      </c>
-      <c r="O112">
-        <v>0</v>
-      </c>
-      <c r="P112">
-        <v>0</v>
-      </c>
-      <c r="Q112">
-        <v>0</v>
-      </c>
-      <c r="R112">
-        <v>0</v>
-      </c>
-      <c r="S112">
-        <v>0</v>
-      </c>
-      <c r="T112">
-        <v>0</v>
-      </c>
-      <c r="U112">
-        <v>0</v>
-      </c>
-      <c r="V112">
-        <v>0</v>
-      </c>
-      <c r="W112">
-        <v>0</v>
-      </c>
-      <c r="X112">
-        <v>0</v>
-      </c>
-      <c r="Y112">
-        <v>0</v>
-      </c>
-      <c r="Z112">
-        <v>0</v>
-      </c>
-      <c r="AA112">
-        <v>0</v>
-      </c>
-      <c r="AB112">
-        <v>0</v>
-      </c>
-      <c r="AC112">
-        <v>0</v>
-      </c>
-      <c r="AD112">
-        <v>0</v>
-      </c>
-      <c r="AE112">
-        <v>0</v>
-      </c>
-      <c r="AF112">
-        <v>0</v>
-      </c>
-      <c r="AG112">
-        <v>0</v>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ112">
-        <v>0</v>
-      </c>
-      <c r="AK112">
-        <v>0</v>
-      </c>
-      <c r="AL112">
-        <v>0</v>
-      </c>
-      <c r="AM112">
-        <v>-1</v>
-      </c>
-      <c r="AN112">
-        <v>-1</v>
-      </c>
-      <c r="AO112">
-        <v>-1</v>
-      </c>
-      <c r="AP112">
-        <v>-1</v>
-      </c>
-      <c r="AQ112">
-        <v>0</v>
-      </c>
-      <c r="AR112">
-        <v>0</v>
-      </c>
-      <c r="AS112">
-        <v>0</v>
-      </c>
-      <c r="AT112">
-        <v>0</v>
-      </c>
-      <c r="AU112" t="inlineStr">
         <is>
           <t>2026-08-14 23:00:00</t>
         </is>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>2.29</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>2.44</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4067,34 +4067,34 @@
         <v>2.64</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA23">
         <v>1.86</v>
@@ -4103,19 +4103,19 @@
         <v>1.87</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -5051,10 +5051,10 @@
         <v>2.35</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U29">
         <v>2.32</v>
@@ -5066,7 +5066,7 @@
         <v>1.11</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
         <v>1.18</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G34">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G35">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G41">
@@ -7001,55 +7001,55 @@
         <v>0</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8142,55 +8142,55 @@
         <v>6.07</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8631,55 +8631,55 @@
         <v>2.11</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9120,34 +9120,34 @@
         <v>2.3</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="AA54">
         <v>1.79</v>
@@ -9156,19 +9156,19 @@
         <v>1.88</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9283,34 +9283,34 @@
         <v>2.82</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA55">
         <v>1.58</v>
@@ -9319,19 +9319,19 @@
         <v>2.2</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10424,55 +10424,55 @@
         <v>4.23</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>5.19</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10943,10 +10943,10 @@
         <v>0</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC65">
         <v>0</v>
@@ -11076,55 +11076,55 @@
         <v>5.37</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O69">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P69">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB69">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O72">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P72">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB72">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O74">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P74">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="O75">
-        <v>3.88</v>
+        <v>3.44</v>
       </c>
       <c r="P75">
-        <v>4.51</v>
+        <v>3.32</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA75">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AB75">
         <v>1.93</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="O77">
-        <v>3.44</v>
+        <v>4.15</v>
       </c>
       <c r="P77">
-        <v>3.32</v>
+        <v>4.97</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA77">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AB77">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13358,34 +13358,34 @@
         <v>5.53</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA80">
         <v>1.82</v>
@@ -13394,19 +13394,19 @@
         <v>1.87</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13521,40 +13521,40 @@
         <v>16</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X81">
         <v>0</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AC81">
         <v>2</v>
@@ -13563,13 +13563,13 @@
         <v>1.7</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>3.73</v>
+        <v>2.25</v>
       </c>
       <c r="O84">
-        <v>3.52</v>
+        <v>2.9</v>
       </c>
       <c r="P84">
-        <v>1.92</v>
+        <v>3.2</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA84">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AB84">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14336,55 +14336,55 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -16292,55 +16292,55 @@
         <v>0</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16455,34 +16455,34 @@
         <v>3.61</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA99">
         <v>1.85</v>
@@ -16491,19 +16491,19 @@
         <v>1.89</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G107">
@@ -18085,55 +18085,55 @@
         <v>3.1</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X109">
         <v>0</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18248,55 +18248,55 @@
         <v>0</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X110">
         <v>0</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X111">
         <v>0</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL111">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.44</v>
+        <v>3.25</v>
       </c>
       <c r="O4">
-        <v>5.16</v>
+        <v>3.73</v>
       </c>
       <c r="P4">
-        <v>6.24</v>
+        <v>2.12</v>
       </c>
       <c r="Q4">
-        <v>1.75</v>
+        <v>3.7</v>
       </c>
       <c r="R4">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="S4">
+        <v>1.25</v>
+      </c>
+      <c r="T4">
+        <v>3.6</v>
+      </c>
+      <c r="U4">
+        <v>2.29</v>
+      </c>
+      <c r="V4">
+        <v>1.57</v>
+      </c>
+      <c r="W4">
+        <v>1.13</v>
+      </c>
+      <c r="X4">
+        <v>1.01</v>
+      </c>
+      <c r="Y4">
+        <v>1.12</v>
+      </c>
+      <c r="Z4">
+        <v>4.65</v>
+      </c>
+      <c r="AA4">
+        <v>1.57</v>
+      </c>
+      <c r="AB4">
+        <v>2.2</v>
+      </c>
+      <c r="AC4">
+        <v>2.33</v>
+      </c>
+      <c r="AD4">
+        <v>1.48</v>
+      </c>
+      <c r="AE4">
         <v>1.16</v>
       </c>
-      <c r="T4">
-        <v>4.2</v>
-      </c>
-      <c r="U4">
-        <v>1.84</v>
-      </c>
-      <c r="V4">
-        <v>1.81</v>
-      </c>
-      <c r="W4">
-        <v>1.19</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>1.06</v>
-      </c>
-      <c r="Z4">
-        <v>6.2</v>
-      </c>
-      <c r="AA4">
-        <v>1.32</v>
-      </c>
-      <c r="AB4">
-        <v>3.05</v>
-      </c>
-      <c r="AC4">
-        <v>1.82</v>
-      </c>
-      <c r="AD4">
-        <v>2</v>
-      </c>
-      <c r="AE4">
-        <v>1.36</v>
-      </c>
       <c r="AF4">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AG4">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK4">
-        <v>2.65</v>
+        <v>1.24</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.25</v>
+        <v>1.44</v>
       </c>
       <c r="O5">
-        <v>3.73</v>
+        <v>5.16</v>
       </c>
       <c r="P5">
-        <v>2.12</v>
+        <v>6.24</v>
       </c>
       <c r="Q5">
-        <v>3.7</v>
+        <v>1.75</v>
       </c>
       <c r="R5">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="T5">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="U5">
-        <v>2.29</v>
+        <v>1.84</v>
       </c>
       <c r="V5">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="W5">
+        <v>1.19</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>1.06</v>
+      </c>
+      <c r="Z5">
+        <v>6.2</v>
+      </c>
+      <c r="AA5">
+        <v>1.32</v>
+      </c>
+      <c r="AB5">
+        <v>3.05</v>
+      </c>
+      <c r="AC5">
+        <v>1.82</v>
+      </c>
+      <c r="AD5">
+        <v>2</v>
+      </c>
+      <c r="AE5">
+        <v>1.36</v>
+      </c>
+      <c r="AF5">
+        <v>1.47</v>
+      </c>
+      <c r="AG5">
+        <v>2.46</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.13</v>
       </c>
-      <c r="X5">
-        <v>1.01</v>
-      </c>
-      <c r="Y5">
-        <v>1.12</v>
-      </c>
-      <c r="Z5">
-        <v>4.65</v>
-      </c>
-      <c r="AA5">
-        <v>1.57</v>
-      </c>
-      <c r="AB5">
-        <v>2.2</v>
-      </c>
-      <c r="AC5">
-        <v>2.33</v>
-      </c>
-      <c r="AD5">
-        <v>1.48</v>
-      </c>
-      <c r="AE5">
-        <v>1.16</v>
-      </c>
-      <c r="AF5">
-        <v>1.48</v>
-      </c>
-      <c r="AG5">
-        <v>2.47</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.22</v>
-      </c>
       <c r="AK5">
-        <v>1.24</v>
+        <v>2.65</v>
       </c>
       <c r="AL5">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -798,28 +798,28 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.58</v>
+        <v>4.45</v>
       </c>
       <c r="O3">
-        <v>3.46</v>
+        <v>3.35</v>
       </c>
       <c r="P3">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="Q3">
-        <v>5.42</v>
+        <v>5</v>
       </c>
       <c r="R3">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S3">
         <v>1.48</v>
       </c>
       <c r="T3">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="U3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="V3">
         <v>1.29</v>
@@ -828,31 +828,31 @@
         <v>1.02</v>
       </c>
       <c r="X3">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z3">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="AA3">
         <v>2.25</v>
       </c>
       <c r="AB3">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC3">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="AD3">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE3">
         <v>1.02</v>
       </c>
       <c r="AF3">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG3">
         <v>1.69</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AK3">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.23</v>
+        <v>2.49</v>
       </c>
       <c r="O24">
-        <v>4.9</v>
+        <v>2.97</v>
       </c>
       <c r="P24">
-        <v>10.9</v>
+        <v>2.6</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.49</v>
+        <v>1.23</v>
       </c>
       <c r="O25">
-        <v>2.97</v>
+        <v>4.9</v>
       </c>
       <c r="P25">
-        <v>2.6</v>
+        <v>10.9</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.73</v>
+        <v>2.25</v>
       </c>
       <c r="O83">
-        <v>3.52</v>
+        <v>2.9</v>
       </c>
       <c r="P83">
-        <v>1.92</v>
+        <v>3.2</v>
       </c>
       <c r="Q83">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="R83">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S83">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T83">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U83">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="V83">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W83">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X83">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y83">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="Z83">
-        <v>3.5</v>
+        <v>2.59</v>
       </c>
       <c r="AA83">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AB83">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="AC83">
-        <v>3.08</v>
+        <v>4.5</v>
       </c>
       <c r="AD83">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AE83">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF83">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AG83">
-        <v>2.01</v>
+        <v>1.71</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="AK83">
-        <v>1.23</v>
+        <v>1.65</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.25</v>
+        <v>3.73</v>
       </c>
       <c r="O84">
-        <v>2.9</v>
+        <v>3.52</v>
       </c>
       <c r="P84">
-        <v>3.2</v>
+        <v>1.92</v>
       </c>
       <c r="Q84">
-        <v>2.85</v>
+        <v>4.2</v>
       </c>
       <c r="R84">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S84">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T84">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U84">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="V84">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W84">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X84">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y84">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="Z84">
-        <v>2.59</v>
+        <v>3.5</v>
       </c>
       <c r="AA84">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AB84">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="AC84">
-        <v>4.5</v>
+        <v>3.08</v>
       </c>
       <c r="AD84">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AE84">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF84">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="AG84">
-        <v>1.71</v>
+        <v>2.01</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AK84">
-        <v>1.65</v>
+        <v>1.23</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G92">

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU111"/>
+  <dimension ref="A1:AU113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="O8">
-        <v>3.77</v>
+        <v>3.6</v>
       </c>
       <c r="P8">
+        <v>1.99</v>
+      </c>
+      <c r="Q8">
+        <v>4.05</v>
+      </c>
+      <c r="R8">
         <v>2.26</v>
-      </c>
-      <c r="Q8">
-        <v>3.7</v>
-      </c>
-      <c r="R8">
-        <v>2.3</v>
       </c>
       <c r="S8">
         <v>1.33</v>
@@ -1634,13 +1634,13 @@
         <v>3.2</v>
       </c>
       <c r="U8">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="V8">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
         <v>1</v>
@@ -1649,28 +1649,28 @@
         <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>3.68</v>
+        <v>4.22</v>
       </c>
       <c r="AA8">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AB8">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AC8">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="AD8">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF8">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AG8">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK8">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="O10">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="P10">
-        <v>3.28</v>
+        <v>2.85</v>
       </c>
       <c r="Q10">
         <v>3.39</v>
@@ -1978,16 +1978,16 @@
         <v>2.43</v>
       </c>
       <c r="AA10">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AB10">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC10">
-        <v>4.6</v>
+        <v>4.79</v>
       </c>
       <c r="AD10">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE10">
         <v>1.02</v>
@@ -3741,55 +3741,55 @@
         <v>2.86</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="Q26">
         <v>2.15</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10913,34 +10913,34 @@
         <v>1.78</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA65">
         <v>1.66</v>
@@ -10949,19 +10949,19 @@
         <v>2.15</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -13062,10 +13062,10 @@
         <v>0</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC78">
         <v>0</v>
@@ -13307,22 +13307,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O80">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P80">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="Q80">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R80">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S80">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T80">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U80">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V80">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W80">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X80">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y80">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z80">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AA80">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB80">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC80">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD80">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF80">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG80">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK80">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13465,12 +13465,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="O81">
-        <v>8.25</v>
+        <v>4.15</v>
       </c>
       <c r="P81">
-        <v>16</v>
+        <v>5.53</v>
       </c>
       <c r="Q81">
-        <v>1.52</v>
+        <v>2.05</v>
       </c>
       <c r="R81">
+        <v>2.38</v>
+      </c>
+      <c r="S81">
+        <v>1.32</v>
+      </c>
+      <c r="T81">
+        <v>3.1</v>
+      </c>
+      <c r="U81">
+        <v>2.5</v>
+      </c>
+      <c r="V81">
+        <v>1.44</v>
+      </c>
+      <c r="W81">
+        <v>1.11</v>
+      </c>
+      <c r="X81">
+        <v>1.05</v>
+      </c>
+      <c r="Y81">
+        <v>1.21</v>
+      </c>
+      <c r="Z81">
+        <v>3.62</v>
+      </c>
+      <c r="AA81">
+        <v>1.82</v>
+      </c>
+      <c r="AB81">
+        <v>1.87</v>
+      </c>
+      <c r="AC81">
         <v>3</v>
       </c>
-      <c r="S81">
-        <v>1.17</v>
-      </c>
-      <c r="T81">
-        <v>4.5</v>
-      </c>
-      <c r="U81">
-        <v>2.04</v>
-      </c>
-      <c r="V81">
-        <v>1.67</v>
-      </c>
-      <c r="W81">
+      <c r="AD81">
+        <v>1.38</v>
+      </c>
+      <c r="AE81">
         <v>1.15</v>
       </c>
-      <c r="X81">
-        <v>0</v>
-      </c>
-      <c r="Y81">
-        <v>1.08</v>
-      </c>
-      <c r="Z81">
-        <v>5.7</v>
-      </c>
-      <c r="AA81">
-        <v>1.43</v>
-      </c>
-      <c r="AB81">
-        <v>2.58</v>
-      </c>
-      <c r="AC81">
-        <v>2</v>
-      </c>
-      <c r="AD81">
-        <v>1.7</v>
-      </c>
-      <c r="AE81">
-        <v>1.25</v>
-      </c>
       <c r="AF81">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AG81">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AK81">
-        <v>5.2</v>
+        <v>2.27</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-08-14 16:15:00</t>
+          <t>2026-08-14 16:00:00</t>
         </is>
       </c>
     </row>
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-08-14 16:30:00</t>
+          <t>2026-08-14 16:15:00</t>
         </is>
       </c>
     </row>
@@ -13791,27 +13791,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O83">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P83">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q83">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R83">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S83">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T83">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U83">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V83">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W83">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X83">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Y83">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z83">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AA83">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB83">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC83">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD83">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE83">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF83">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG83">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK83">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-08-14 19:30:00</t>
+          <t>2026-08-14 16:30:00</t>
         </is>
       </c>
     </row>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>3.73</v>
+        <v>2.25</v>
       </c>
       <c r="O84">
-        <v>3.52</v>
+        <v>2.9</v>
       </c>
       <c r="P84">
-        <v>1.92</v>
+        <v>3.2</v>
       </c>
       <c r="Q84">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="R84">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S84">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T84">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U84">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="V84">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W84">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X84">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y84">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="Z84">
-        <v>3.5</v>
+        <v>2.59</v>
       </c>
       <c r="AA84">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AB84">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="AC84">
-        <v>3.08</v>
+        <v>4.5</v>
       </c>
       <c r="AD84">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AE84">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF84">
-        <v>1.72</v>
+        <v>2.02</v>
       </c>
       <c r="AG84">
-        <v>2.01</v>
+        <v>1.71</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="AK84">
-        <v>1.23</v>
+        <v>1.65</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14117,12 +14117,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.25</v>
+        <v>3.73</v>
       </c>
       <c r="O85">
-        <v>3.15</v>
+        <v>3.52</v>
       </c>
       <c r="P85">
-        <v>2.85</v>
+        <v>1.92</v>
       </c>
       <c r="Q85">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="R85">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S85">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T85">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="U85">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="V85">
         <v>1.4</v>
       </c>
       <c r="W85">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y85">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z85">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA85">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AB85">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC85">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AD85">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE85">
         <v>1.08</v>
       </c>
       <c r="AF85">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AG85">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AK85">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-08-14 20:00:00</t>
+          <t>2026-08-14 19:30:00</t>
         </is>
       </c>
     </row>
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q86">
-        <v>3.38</v>
+        <v>2.8</v>
       </c>
       <c r="R86">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="S86">
-        <v>1.73</v>
+        <v>1.39</v>
       </c>
       <c r="T86">
-        <v>2.04</v>
+        <v>2.73</v>
       </c>
       <c r="U86">
-        <v>4.55</v>
+        <v>2.65</v>
       </c>
       <c r="V86">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="W86">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X86">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="Z86">
-        <v>1.99</v>
+        <v>3.6</v>
       </c>
       <c r="AA86">
-        <v>3.4</v>
+        <v>1.88</v>
       </c>
       <c r="AB86">
-        <v>1.33</v>
+        <v>1.88</v>
       </c>
       <c r="AC86">
-        <v>7.3</v>
+        <v>2.97</v>
       </c>
       <c r="AD86">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AE86">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AF86">
-        <v>2.51</v>
+        <v>1.66</v>
       </c>
       <c r="AG86">
-        <v>1.44</v>
+        <v>2.06</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AK86">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-08-14 20:30:00</t>
+          <t>2026-08-14 20:00:00</t>
         </is>
       </c>
     </row>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O87">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P87">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14606,27 +14606,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-08-14 21:00:00</t>
+          <t>2026-08-14 20:30:00</t>
         </is>
       </c>
     </row>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G91">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G92">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G93">
@@ -15589,22 +15589,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G94">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G96">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,22 +16241,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G98">
@@ -16292,55 +16292,55 @@
         <v>0</v>
       </c>
       <c r="Q98">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="R98">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S98">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T98">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="U98">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="V98">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W98">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X98">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y98">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z98">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA98">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB98">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC98">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AD98">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE98">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF98">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG98">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK98">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16404,22 +16404,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O99">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="P99">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="Q99">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R99">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S99">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T99">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="U99">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="V99">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W99">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X99">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y99">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z99">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA99">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB99">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC99">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD99">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE99">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF99">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG99">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK99">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16567,22 +16567,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G100">
@@ -16618,55 +16618,55 @@
         <v>0</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16730,22 +16730,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G107">
@@ -17866,27 +17866,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G108">
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-08-14 22:00:00</t>
+          <t>2026-08-14 21:00:00</t>
         </is>
       </c>
     </row>
@@ -18029,27 +18029,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O109">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P109">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q109">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R109">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S109">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T109">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U109">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V109">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W109">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X109">
         <v>0</v>
       </c>
       <c r="Y109">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z109">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA109">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB109">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AC109">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD109">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE109">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF109">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG109">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK109">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-08-14 23:00:00</t>
+          <t>2026-08-14 21:00:00</t>
         </is>
       </c>
     </row>
@@ -18192,12 +18192,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="Q110">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="R110">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S110">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T110">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U110">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="V110">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W110">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X110">
         <v>0</v>
       </c>
       <c r="Y110">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z110">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA110">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB110">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AC110">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD110">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE110">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF110">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG110">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK110">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-08-14 23:00:00</t>
+          <t>2026-08-14 22:00:00</t>
         </is>
       </c>
     </row>
@@ -18370,141 +18370,467 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
+          <t>San Diego Wave</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Denver Summit W</t>
+        </is>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N111">
+        <v>1.86</v>
+      </c>
+      <c r="O111">
+        <v>3.6</v>
+      </c>
+      <c r="P111">
+        <v>3.1</v>
+      </c>
+      <c r="Q111">
+        <v>2.3</v>
+      </c>
+      <c r="R111">
+        <v>2.3</v>
+      </c>
+      <c r="S111">
+        <v>1.26</v>
+      </c>
+      <c r="T111">
+        <v>3.28</v>
+      </c>
+      <c r="U111">
+        <v>2.36</v>
+      </c>
+      <c r="V111">
+        <v>1.48</v>
+      </c>
+      <c r="W111">
+        <v>1.11</v>
+      </c>
+      <c r="X111">
+        <v>0</v>
+      </c>
+      <c r="Y111">
+        <v>1.16</v>
+      </c>
+      <c r="Z111">
+        <v>4.2</v>
+      </c>
+      <c r="AA111">
+        <v>1.66</v>
+      </c>
+      <c r="AB111">
+        <v>2.16</v>
+      </c>
+      <c r="AC111">
+        <v>2.59</v>
+      </c>
+      <c r="AD111">
+        <v>1.39</v>
+      </c>
+      <c r="AE111">
+        <v>1.12</v>
+      </c>
+      <c r="AF111">
+        <v>1.57</v>
+      </c>
+      <c r="AG111">
+        <v>2.16</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ111">
+        <v>1.2</v>
+      </c>
+      <c r="AK111">
+        <v>1.82</v>
+      </c>
+      <c r="AL111">
+        <v>0</v>
+      </c>
+      <c r="AM111">
+        <v>-1</v>
+      </c>
+      <c r="AN111">
+        <v>-1</v>
+      </c>
+      <c r="AO111">
+        <v>-1</v>
+      </c>
+      <c r="AP111">
+        <v>-1</v>
+      </c>
+      <c r="AQ111">
+        <v>0</v>
+      </c>
+      <c r="AR111">
+        <v>0</v>
+      </c>
+      <c r="AS111">
+        <v>0</v>
+      </c>
+      <c r="AT111">
+        <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Seattle Reign</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Chicago Red Stars</t>
+        </is>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
+      </c>
+      <c r="Q112">
+        <v>1.87</v>
+      </c>
+      <c r="R112">
+        <v>2.55</v>
+      </c>
+      <c r="S112">
+        <v>1.24</v>
+      </c>
+      <c r="T112">
+        <v>3.42</v>
+      </c>
+      <c r="U112">
+        <v>2.29</v>
+      </c>
+      <c r="V112">
+        <v>1.51</v>
+      </c>
+      <c r="W112">
+        <v>1.12</v>
+      </c>
+      <c r="X112">
+        <v>0</v>
+      </c>
+      <c r="Y112">
+        <v>1.13</v>
+      </c>
+      <c r="Z112">
+        <v>4.5</v>
+      </c>
+      <c r="AA112">
+        <v>1.57</v>
+      </c>
+      <c r="AB112">
+        <v>2.23</v>
+      </c>
+      <c r="AC112">
+        <v>2.43</v>
+      </c>
+      <c r="AD112">
+        <v>1.44</v>
+      </c>
+      <c r="AE112">
+        <v>1.14</v>
+      </c>
+      <c r="AF112">
+        <v>1.63</v>
+      </c>
+      <c r="AG112">
+        <v>2.1</v>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ112">
+        <v>1.13</v>
+      </c>
+      <c r="AK112">
+        <v>2.59</v>
+      </c>
+      <c r="AL112">
+        <v>0</v>
+      </c>
+      <c r="AM112">
+        <v>-1</v>
+      </c>
+      <c r="AN112">
+        <v>-1</v>
+      </c>
+      <c r="AO112">
+        <v>-1</v>
+      </c>
+      <c r="AP112">
+        <v>-1</v>
+      </c>
+      <c r="AQ112">
+        <v>0</v>
+      </c>
+      <c r="AR112">
+        <v>0</v>
+      </c>
+      <c r="AS112">
+        <v>0</v>
+      </c>
+      <c r="AT112">
+        <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>2026-08-14 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
           <t>Utah Royals</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>Bay</t>
         </is>
       </c>
-      <c r="G111">
-        <v>0</v>
-      </c>
-      <c r="H111">
-        <v>0</v>
-      </c>
-      <c r="I111">
-        <v>0</v>
-      </c>
-      <c r="J111">
-        <v>0</v>
-      </c>
-      <c r="K111">
-        <v>0</v>
-      </c>
-      <c r="L111">
-        <v>0</v>
-      </c>
-      <c r="M111" t="inlineStr">
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N111">
+      <c r="N113">
         <v>1.68</v>
       </c>
-      <c r="O111">
+      <c r="O113">
         <v>3.85</v>
       </c>
-      <c r="P111">
+      <c r="P113">
         <v>4.05</v>
       </c>
-      <c r="Q111">
+      <c r="Q113">
         <v>2.23</v>
       </c>
-      <c r="R111">
+      <c r="R113">
         <v>2.34</v>
       </c>
-      <c r="S111">
+      <c r="S113">
         <v>1.22</v>
       </c>
-      <c r="T111">
+      <c r="T113">
         <v>3.8</v>
       </c>
-      <c r="U111">
+      <c r="U113">
         <v>2.26</v>
       </c>
-      <c r="V111">
+      <c r="V113">
         <v>1.55</v>
       </c>
-      <c r="W111">
+      <c r="W113">
         <v>1.13</v>
       </c>
-      <c r="X111">
-        <v>0</v>
-      </c>
-      <c r="Y111">
+      <c r="X113">
+        <v>0</v>
+      </c>
+      <c r="Y113">
         <v>1.18</v>
       </c>
-      <c r="Z111">
+      <c r="Z113">
         <v>4.5</v>
       </c>
-      <c r="AA111">
+      <c r="AA113">
         <v>1.55</v>
       </c>
-      <c r="AB111">
+      <c r="AB113">
         <v>2.27</v>
       </c>
-      <c r="AC111">
+      <c r="AC113">
         <v>2.48</v>
       </c>
-      <c r="AD111">
+      <c r="AD113">
         <v>1.43</v>
       </c>
-      <c r="AE111">
+      <c r="AE113">
         <v>1.16</v>
       </c>
-      <c r="AF111">
+      <c r="AF113">
         <v>1.6</v>
       </c>
-      <c r="AG111">
+      <c r="AG113">
         <v>2.15</v>
       </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ111">
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ113">
         <v>1.16</v>
       </c>
-      <c r="AK111">
+      <c r="AK113">
         <v>2.1</v>
       </c>
-      <c r="AL111">
-        <v>0</v>
-      </c>
-      <c r="AM111">
-        <v>-1</v>
-      </c>
-      <c r="AN111">
-        <v>-1</v>
-      </c>
-      <c r="AO111">
-        <v>-1</v>
-      </c>
-      <c r="AP111">
-        <v>-1</v>
-      </c>
-      <c r="AQ111">
-        <v>0</v>
-      </c>
-      <c r="AR111">
-        <v>0</v>
-      </c>
-      <c r="AS111">
-        <v>0</v>
-      </c>
-      <c r="AT111">
-        <v>0</v>
-      </c>
-      <c r="AU111" t="inlineStr">
+      <c r="AL113">
+        <v>0</v>
+      </c>
+      <c r="AM113">
+        <v>-1</v>
+      </c>
+      <c r="AN113">
+        <v>-1</v>
+      </c>
+      <c r="AO113">
+        <v>-1</v>
+      </c>
+      <c r="AP113">
+        <v>-1</v>
+      </c>
+      <c r="AQ113">
+        <v>0</v>
+      </c>
+      <c r="AR113">
+        <v>0</v>
+      </c>
+      <c r="AS113">
+        <v>0</v>
+      </c>
+      <c r="AT113">
+        <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
         <is>
           <t>2026-08-14 23:00:00</t>
         </is>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -855,7 +855,7 @@
         <v>2</v>
       </c>
       <c r="AG3">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
         <v>1.18</v>
@@ -961,37 +961,37 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O4">
-        <v>3.73</v>
+        <v>3.6</v>
       </c>
       <c r="P4">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="Q4">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="R4">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="S4">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T4">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U4">
         <v>2.29</v>
       </c>
       <c r="V4">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W4">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
         <v>1.12</v>
@@ -1003,19 +1003,19 @@
         <v>1.57</v>
       </c>
       <c r="AB4">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AC4">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AD4">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE4">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AF4">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AG4">
         <v>2.47</v>
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="O5">
-        <v>5.16</v>
+        <v>4.96</v>
       </c>
       <c r="P5">
-        <v>6.24</v>
+        <v>5.65</v>
       </c>
       <c r="Q5">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="R5">
         <v>2.85</v>
@@ -1145,43 +1145,43 @@
         <v>4.2</v>
       </c>
       <c r="U5">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="V5">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="W5">
         <v>1.19</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z5">
-        <v>6.2</v>
+        <v>6.31</v>
       </c>
       <c r="AA5">
         <v>1.32</v>
       </c>
       <c r="AB5">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AC5">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AD5">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AE5">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AF5">
         <v>1.47</v>
       </c>
       <c r="AG5">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK5">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1290,46 +1290,46 @@
         <v>2.1</v>
       </c>
       <c r="O6">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="P6">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="Q6">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="R6">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="S6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T6">
-        <v>2.86</v>
+        <v>2.67</v>
       </c>
       <c r="U6">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W6">
         <v>1.03</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z6">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AA6">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AB6">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AC6">
         <v>3.3</v>
@@ -1338,13 +1338,13 @@
         <v>1.27</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF6">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AG6">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
         <v>1.73</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="O22">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="P22">
-        <v>3.22</v>
+        <v>2.64</v>
       </c>
       <c r="Q22">
-        <v>2.58</v>
+        <v>3.2</v>
       </c>
       <c r="R22">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S22">
+        <v>1.38</v>
+      </c>
+      <c r="T22">
+        <v>2.72</v>
+      </c>
+      <c r="U22">
+        <v>2.73</v>
+      </c>
+      <c r="V22">
+        <v>1.42</v>
+      </c>
+      <c r="W22">
+        <v>1.07</v>
+      </c>
+      <c r="X22">
+        <v>1</v>
+      </c>
+      <c r="Y22">
+        <v>1.25</v>
+      </c>
+      <c r="Z22">
+        <v>3.38</v>
+      </c>
+      <c r="AA22">
+        <v>1.86</v>
+      </c>
+      <c r="AB22">
+        <v>1.87</v>
+      </c>
+      <c r="AC22">
+        <v>2.99</v>
+      </c>
+      <c r="AD22">
         <v>1.3</v>
       </c>
-      <c r="T22">
-        <v>3.1</v>
-      </c>
-      <c r="U22">
-        <v>2.5</v>
-      </c>
-      <c r="V22">
-        <v>1.44</v>
-      </c>
-      <c r="W22">
-        <v>1.12</v>
-      </c>
-      <c r="X22">
-        <v>1.04</v>
-      </c>
-      <c r="Y22">
-        <v>1.22</v>
-      </c>
-      <c r="Z22">
-        <v>3.8</v>
-      </c>
-      <c r="AA22">
-        <v>1.75</v>
-      </c>
-      <c r="AB22">
-        <v>1.95</v>
-      </c>
-      <c r="AC22">
-        <v>2.15</v>
-      </c>
-      <c r="AD22">
-        <v>1.6</v>
-      </c>
       <c r="AE22">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF22">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG22">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="O23">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="P23">
-        <v>2.64</v>
+        <v>3.22</v>
       </c>
       <c r="Q23">
-        <v>3.2</v>
+        <v>2.58</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="S23">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="U23">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="V23">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>3.38</v>
+        <v>3.8</v>
       </c>
       <c r="AA23">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AB23">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC23">
-        <v>2.99</v>
+        <v>2.15</v>
       </c>
       <c r="AD23">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AE23">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>2.22</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -5546,10 +5546,10 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W32">
         <v>0</v>
@@ -5564,25 +5564,25 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.88</v>
+        <v>3.55</v>
       </c>
       <c r="O51">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="P51">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="Q51">
-        <v>4.82</v>
+        <v>4.71</v>
       </c>
       <c r="R51">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S51">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="T51">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="U51">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="V51">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W51">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X51">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Y51">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="Z51">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AA51">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AB51">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC51">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="AD51">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE51">
         <v>1.03</v>
       </c>
       <c r="AF51">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="AG51">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.33</v>
       </c>
       <c r="AK51">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9763,19 +9763,19 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="O58">
         <v>3.8</v>
       </c>
       <c r="P58">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q58">
+        <v>2.29</v>
+      </c>
+      <c r="R58">
         <v>2.27</v>
-      </c>
-      <c r="R58">
-        <v>2.41</v>
       </c>
       <c r="S58">
         <v>1.3</v>
@@ -9799,7 +9799,7 @@
         <v>1.22</v>
       </c>
       <c r="Z58">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA58">
         <v>1.69</v>
@@ -9808,16 +9808,16 @@
         <v>2.11</v>
       </c>
       <c r="AC58">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="AD58">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE58">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF58">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AG58">
         <v>2.13</v>
@@ -9926,25 +9926,25 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="O59">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P59">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q59">
         <v>2.3</v>
       </c>
       <c r="R59">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="S59">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T59">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="U59">
         <v>2.32</v>
@@ -9962,19 +9962,19 @@
         <v>1.18</v>
       </c>
       <c r="Z59">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AA59">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AB59">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AC59">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD59">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE59">
         <v>1.15</v>
@@ -9999,7 +9999,7 @@
         <v>1.29</v>
       </c>
       <c r="AK59">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="O62">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="P62">
-        <v>4.23</v>
+        <v>4.6</v>
       </c>
       <c r="Q62">
         <v>2.41</v>
@@ -10430,7 +10430,7 @@
         <v>2.03</v>
       </c>
       <c r="S62">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="T62">
         <v>2.5</v>
@@ -10445,34 +10445,34 @@
         <v>1.06</v>
       </c>
       <c r="X62">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y62">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z62">
         <v>3</v>
       </c>
       <c r="AA62">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB62">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AC62">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="AD62">
         <v>1.25</v>
       </c>
       <c r="AE62">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF62">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AG62">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="O66">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P66">
-        <v>5.37</v>
+        <v>4.94</v>
       </c>
       <c r="Q66">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="R66">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="S66">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T66">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="U66">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V66">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W66">
         <v>1.11</v>
       </c>
       <c r="X66">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y66">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z66">
-        <v>4.1</v>
+        <v>4.62</v>
       </c>
       <c r="AA66">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AB66">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="AC66">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AD66">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AE66">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF66">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AG66">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AK66">
         <v>2.25</v>
@@ -11891,34 +11891,34 @@
         <v>2.22</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AA71">
         <v>1.87</v>
@@ -11927,19 +11927,19 @@
         <v>1.83</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -14499,55 +14499,55 @@
         <v>0</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -16609,65 +16609,65 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q100">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="R100">
         <v>2.7</v>
       </c>
       <c r="S100">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T100">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="U100">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="V100">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W100">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X100">
         <v>1.01</v>
       </c>
       <c r="Y100">
+        <v>1.15</v>
+      </c>
+      <c r="Z100">
+        <v>4.35</v>
+      </c>
+      <c r="AA100">
+        <v>1.67</v>
+      </c>
+      <c r="AB100">
+        <v>2.25</v>
+      </c>
+      <c r="AC100">
+        <v>2.51</v>
+      </c>
+      <c r="AD100">
+        <v>1.44</v>
+      </c>
+      <c r="AE100">
         <v>1.14</v>
       </c>
-      <c r="Z100">
-        <v>4.33</v>
-      </c>
-      <c r="AA100">
-        <v>1.57</v>
-      </c>
-      <c r="AB100">
-        <v>2.32</v>
-      </c>
-      <c r="AC100">
-        <v>2.41</v>
-      </c>
-      <c r="AD100">
+      <c r="AF100">
+        <v>2.35</v>
+      </c>
+      <c r="AG100">
         <v>1.5</v>
       </c>
-      <c r="AE100">
-        <v>1.16</v>
-      </c>
-      <c r="AF100">
-        <v>2.4</v>
-      </c>
-      <c r="AG100">
-        <v>1.48</v>
-      </c>
       <c r="AH100" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK100">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC110">
         <v>0</v>
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="O111">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P111">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="Q111">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="R111">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="S111">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="T111">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="U111">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="V111">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="W111">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X111">
         <v>0</v>
       </c>
       <c r="Y111">
+        <v>1.18</v>
+      </c>
+      <c r="Z111">
+        <v>4.5</v>
+      </c>
+      <c r="AA111">
+        <v>1.55</v>
+      </c>
+      <c r="AB111">
+        <v>2.27</v>
+      </c>
+      <c r="AC111">
+        <v>2.48</v>
+      </c>
+      <c r="AD111">
+        <v>1.43</v>
+      </c>
+      <c r="AE111">
         <v>1.16</v>
       </c>
-      <c r="Z111">
-        <v>4.2</v>
-      </c>
-      <c r="AA111">
-        <v>1.66</v>
-      </c>
-      <c r="AB111">
-        <v>2.16</v>
-      </c>
-      <c r="AC111">
-        <v>2.59</v>
-      </c>
-      <c r="AD111">
-        <v>1.39</v>
-      </c>
-      <c r="AE111">
-        <v>1.12</v>
-      </c>
       <c r="AF111">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG111">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK111">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q112">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="R112">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="S112">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="T112">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="U112">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="V112">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W112">
+        <v>1.11</v>
+      </c>
+      <c r="X112">
+        <v>1.03</v>
+      </c>
+      <c r="Y112">
+        <v>1.16</v>
+      </c>
+      <c r="Z112">
+        <v>4.2</v>
+      </c>
+      <c r="AA112">
+        <v>1.66</v>
+      </c>
+      <c r="AB112">
+        <v>2.16</v>
+      </c>
+      <c r="AC112">
+        <v>2.59</v>
+      </c>
+      <c r="AD112">
+        <v>1.39</v>
+      </c>
+      <c r="AE112">
         <v>1.12</v>
       </c>
-      <c r="X112">
-        <v>0</v>
-      </c>
-      <c r="Y112">
-        <v>1.13</v>
-      </c>
-      <c r="Z112">
-        <v>4.5</v>
-      </c>
-      <c r="AA112">
+      <c r="AF112">
         <v>1.57</v>
       </c>
-      <c r="AB112">
-        <v>2.23</v>
-      </c>
-      <c r="AC112">
-        <v>2.43</v>
-      </c>
-      <c r="AD112">
-        <v>1.44</v>
-      </c>
-      <c r="AE112">
-        <v>1.14</v>
-      </c>
-      <c r="AF112">
-        <v>1.63</v>
-      </c>
       <c r="AG112">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK112">
-        <v>2.59</v>
+        <v>1.82</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O113">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P113">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Q113">
-        <v>2.23</v>
+        <v>1.87</v>
       </c>
       <c r="R113">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="S113">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T113">
-        <v>3.8</v>
+        <v>3.42</v>
       </c>
       <c r="U113">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="V113">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W113">
+        <v>1.12</v>
+      </c>
+      <c r="X113">
+        <v>0</v>
+      </c>
+      <c r="Y113">
         <v>1.13</v>
-      </c>
-      <c r="X113">
-        <v>0</v>
-      </c>
-      <c r="Y113">
-        <v>1.18</v>
       </c>
       <c r="Z113">
         <v>4.5</v>
       </c>
       <c r="AA113">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB113">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AC113">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="AD113">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE113">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF113">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AG113">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK113">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="AL113">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="O14">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="Q14">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="R14">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="U14">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="V14">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z14">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="AA14">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB14">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AC14">
-        <v>3.37</v>
+        <v>3.8</v>
       </c>
       <c r="AD14">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE14">
         <v>1.04</v>
       </c>
       <c r="AF14">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AG14">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK14">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -11230,37 +11230,37 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O67">
+        <v>3.6</v>
+      </c>
+      <c r="P67">
         <v>3.8</v>
       </c>
-      <c r="P67">
-        <v>3.95</v>
-      </c>
       <c r="Q67">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="R67">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S67">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T67">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="U67">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="V67">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W67">
         <v>1.05</v>
       </c>
       <c r="X67">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y67">
         <v>1.26</v>
@@ -11269,22 +11269,22 @@
         <v>3.58</v>
       </c>
       <c r="AA67">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB67">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC67">
         <v>2.97</v>
       </c>
       <c r="AD67">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE67">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF67">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG67">
         <v>1.95</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK67">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,49 +11393,49 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="O68">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P68">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="Q68">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="R68">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S68">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T68">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="U68">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="V68">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W68">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X68">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z68">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA68">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AB68">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC68">
         <v>3.42</v>
@@ -11447,10 +11447,10 @@
         <v>1.05</v>
       </c>
       <c r="AF68">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG68">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK68">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G109">

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="O82">
-        <v>8.25</v>
+        <v>7.5</v>
       </c>
       <c r="P82">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Q82">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R82">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="S82">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T82">
-        <v>4.5</v>
+        <v>3.88</v>
       </c>
       <c r="U82">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V82">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="W82">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X82">
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z82">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AA82">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AB82">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="AC82">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AD82">
         <v>1.7</v>
       </c>
       <c r="AE82">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF82">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG82">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>1.1</v>
       </c>
       <c r="AK82">
-        <v>5.2</v>
+        <v>4.98</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14004,61 +14004,61 @@
         <v>2.25</v>
       </c>
       <c r="O84">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P84">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q84">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="R84">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S84">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="T84">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="U84">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V84">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W84">
         <v>1.05</v>
       </c>
       <c r="X84">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y84">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z84">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AA84">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AB84">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AC84">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AD84">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE84">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AF84">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AG84">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK84">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,25 +14164,25 @@
         </is>
       </c>
       <c r="N85">
-        <v>3.73</v>
+        <v>3.4</v>
       </c>
       <c r="O85">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="P85">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q85">
-        <v>4.2</v>
+        <v>4.34</v>
       </c>
       <c r="R85">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S85">
         <v>1.38</v>
       </c>
       <c r="T85">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="U85">
         <v>2.69</v>
@@ -14194,19 +14194,19 @@
         <v>1.06</v>
       </c>
       <c r="X85">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y85">
         <v>1.27</v>
       </c>
       <c r="Z85">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="AA85">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AB85">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AC85">
         <v>3.08</v>
@@ -14215,13 +14215,13 @@
         <v>1.28</v>
       </c>
       <c r="AE85">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF85">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG85">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AK85">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O86">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P86">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q86">
         <v>2.8</v>
@@ -14342,10 +14342,10 @@
         <v>2.25</v>
       </c>
       <c r="S86">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="T86">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="U86">
         <v>2.65</v>
@@ -14360,31 +14360,31 @@
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z86">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="AA86">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB86">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC86">
-        <v>2.97</v>
+        <v>3.24</v>
       </c>
       <c r="AD86">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE86">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF86">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AG86">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>1.4</v>
       </c>
       <c r="AK86">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AL86">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.45</v>
+        <v>3.9</v>
       </c>
       <c r="O3">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="P3">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Q3">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="R3">
         <v>2</v>
@@ -816,10 +816,10 @@
         <v>1.48</v>
       </c>
       <c r="T3">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="U3">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="V3">
         <v>1.29</v>
@@ -834,13 +834,13 @@
         <v>1.38</v>
       </c>
       <c r="Z3">
-        <v>2.84</v>
+        <v>2.64</v>
       </c>
       <c r="AA3">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AB3">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC3">
         <v>4.05</v>
@@ -849,13 +849,13 @@
         <v>1.17</v>
       </c>
       <c r="AE3">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF3">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG3">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK3">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.45</v>
+        <v>3.56</v>
       </c>
       <c r="O8">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P8">
         <v>1.99</v>
@@ -1646,16 +1646,16 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>4.22</v>
+        <v>3.94</v>
       </c>
       <c r="AA8">
         <v>1.78</v>
       </c>
       <c r="AB8">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC8">
         <v>2.65</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
         <v>1.32</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O10">
         <v>2.8</v>
@@ -1948,10 +1948,10 @@
         <v>2.85</v>
       </c>
       <c r="Q10">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="R10">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="S10">
         <v>1.58</v>
@@ -1966,7 +1966,7 @@
         <v>1.24</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
         <v>1.06</v>
@@ -1978,10 +1978,10 @@
         <v>2.43</v>
       </c>
       <c r="AA10">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="AB10">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC10">
         <v>4.79</v>
@@ -2591,52 +2591,52 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="O14">
         <v>3.2</v>
       </c>
       <c r="P14">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="Q14">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="R14">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="S14">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T14">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="U14">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="V14">
         <v>1.34</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z14">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="AA14">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AB14">
         <v>1.67</v>
       </c>
       <c r="AC14">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD14">
         <v>1.22</v>
@@ -2648,7 +2648,7 @@
         <v>1.82</v>
       </c>
       <c r="AG14">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,34 +2754,34 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="O15">
+        <v>4.2</v>
+      </c>
+      <c r="P15">
         <v>4.3</v>
-      </c>
-      <c r="P15">
-        <v>4.65</v>
       </c>
       <c r="Q15">
         <v>2.15</v>
       </c>
       <c r="R15">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="S15">
         <v>1.18</v>
       </c>
       <c r="T15">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="U15">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="V15">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="W15">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2796,16 +2796,16 @@
         <v>1.36</v>
       </c>
       <c r="AB15">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC15">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AD15">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AE15">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF15">
         <v>1.43</v>
@@ -2827,7 +2827,7 @@
         <v>1.17</v>
       </c>
       <c r="AK15">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="O20">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="P20">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="Q20">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="R20">
         <v>1.83</v>
@@ -3608,10 +3608,10 @@
         <v>2.49</v>
       </c>
       <c r="AA20">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AB20">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AC20">
         <v>4.45</v>
@@ -3626,7 +3626,7 @@
         <v>2.01</v>
       </c>
       <c r="AG20">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="O21">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="P21">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="Q21">
         <v>2.61</v>
@@ -3747,7 +3747,7 @@
         <v>2.29</v>
       </c>
       <c r="S21">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
         <v>3.35</v>
@@ -3759,13 +3759,13 @@
         <v>1.53</v>
       </c>
       <c r="W21">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z21">
         <v>4.45</v>
@@ -3786,10 +3786,10 @@
         <v>1.15</v>
       </c>
       <c r="AF21">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AG21">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3895,58 +3895,58 @@
         </is>
       </c>
       <c r="N22">
+        <v>2.45</v>
+      </c>
+      <c r="O22">
+        <v>3.1</v>
+      </c>
+      <c r="P22">
         <v>2.6</v>
       </c>
-      <c r="O22">
-        <v>3.24</v>
-      </c>
-      <c r="P22">
-        <v>2.64</v>
-      </c>
       <c r="Q22">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="R22">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S22">
         <v>1.38</v>
       </c>
       <c r="T22">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="U22">
         <v>2.73</v>
       </c>
       <c r="V22">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
         <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z22">
-        <v>3.38</v>
+        <v>3.78</v>
       </c>
       <c r="AA22">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AB22">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC22">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="AD22">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE22">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF22">
         <v>1.67</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK22">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,40 +4058,40 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O23">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="Q23">
-        <v>2.58</v>
+        <v>2.85</v>
       </c>
       <c r="R23">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U23">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V23">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W23">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
         <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z23">
         <v>3.8</v>
@@ -4100,13 +4100,13 @@
         <v>1.75</v>
       </c>
       <c r="AB23">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC23">
-        <v>2.15</v>
+        <v>2.95</v>
       </c>
       <c r="AD23">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AE23">
         <v>1.14</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="O25">
-        <v>4.9</v>
+        <v>4.41</v>
       </c>
       <c r="P25">
-        <v>10.9</v>
+        <v>7.95</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4559,49 +4559,49 @@
         <v>2.15</v>
       </c>
       <c r="R26">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S26">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T26">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="U26">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W26">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
         <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z26">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AA26">
+        <v>1.84</v>
+      </c>
+      <c r="AB26">
         <v>1.85</v>
       </c>
-      <c r="AB26">
-        <v>1.95</v>
-      </c>
       <c r="AC26">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD26">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE26">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG26">
         <v>1.95</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK26">
         <v>2.03</v>
@@ -6355,19 +6355,19 @@
         <v>1.95</v>
       </c>
       <c r="S37">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T37">
         <v>2.53</v>
       </c>
       <c r="U37">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X37">
         <v>1.03</v>
@@ -6376,13 +6376,13 @@
         <v>1.28</v>
       </c>
       <c r="Z37">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA37">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB37">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC37">
         <v>3.2</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK37">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,25 +6512,25 @@
         <v>3.6</v>
       </c>
       <c r="Q38">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="R38">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S38">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T38">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="U38">
         <v>3.14</v>
       </c>
       <c r="V38">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W38">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X38">
         <v>1.01</v>
@@ -6542,16 +6542,16 @@
         <v>2.92</v>
       </c>
       <c r="AA38">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AB38">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AC38">
-        <v>3.72</v>
+        <v>3.77</v>
       </c>
       <c r="AD38">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE38">
         <v>1.03</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK38">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,22 +6675,22 @@
         <v>2.65</v>
       </c>
       <c r="Q39">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R39">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T39">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="U39">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="V39">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W39">
         <v>1.04</v>
@@ -6699,22 +6699,22 @@
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z39">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="AA39">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AB39">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC39">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="AD39">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE39">
         <v>1.06</v>
@@ -6723,7 +6723,7 @@
         <v>1.73</v>
       </c>
       <c r="AG39">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AK39">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7001,55 +7001,55 @@
         <v>0</v>
       </c>
       <c r="Q41">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="R41">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="S41">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U41">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="V41">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W41">
         <v>1.04</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z41">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="AA41">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AB41">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AC41">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AD41">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE41">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF41">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG41">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,25 +7164,25 @@
         <v>3.05</v>
       </c>
       <c r="Q42">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="R42">
         <v>2.09</v>
       </c>
       <c r="S42">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T42">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="U42">
         <v>3.08</v>
       </c>
       <c r="V42">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W42">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X42">
         <v>1.04</v>
@@ -7191,16 +7191,16 @@
         <v>1.35</v>
       </c>
       <c r="Z42">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AA42">
         <v>2.2</v>
       </c>
       <c r="AB42">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC42">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="AD42">
         <v>1.19</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>6.57</v>
+        <v>3.05</v>
       </c>
       <c r="O43">
-        <v>3.38</v>
+        <v>2.97</v>
       </c>
       <c r="P43">
-        <v>1.51</v>
+        <v>2.24</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="O44">
         <v>2.78</v>
       </c>
       <c r="P44">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7644,19 +7644,19 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.57</v>
+        <v>2.11</v>
       </c>
       <c r="O45">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P45">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="Q45">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="R45">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S45">
         <v>1.31</v>
@@ -7665,43 +7665,43 @@
         <v>3.15</v>
       </c>
       <c r="U45">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V45">
         <v>1.51</v>
       </c>
       <c r="W45">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X45">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
         <v>1.18</v>
       </c>
       <c r="Z45">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AA45">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB45">
         <v>2.15</v>
       </c>
       <c r="AC45">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AD45">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE45">
         <v>1.18</v>
       </c>
       <c r="AF45">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AG45">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK45">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="O46">
-        <v>3.95</v>
+        <v>3.38</v>
       </c>
       <c r="P46">
-        <v>10.6</v>
+        <v>5.77</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="O48">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P48">
-        <v>6.07</v>
+        <v>5.67</v>
       </c>
       <c r="Q48">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="R48">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="S48">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U48">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V48">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W48">
         <v>1.08</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>4.07</v>
+        <v>4.14</v>
       </c>
       <c r="AA48">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB48">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC48">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="AD48">
         <v>1.4</v>
       </c>
       <c r="AE48">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF48">
         <v>1.75</v>
       </c>
       <c r="AG48">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK48">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="O50">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="P50">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="Q50">
         <v>2.45</v>
@@ -8474,25 +8474,25 @@
         <v>2.3</v>
       </c>
       <c r="S50">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="U50">
         <v>2.27</v>
       </c>
       <c r="V50">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W50">
         <v>1.11</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z50">
         <v>4.4</v>
@@ -8501,22 +8501,22 @@
         <v>1.57</v>
       </c>
       <c r="AB50">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AC50">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AD50">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE50">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF50">
         <v>1.5</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK50">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8631,43 +8631,43 @@
         <v>2.17</v>
       </c>
       <c r="Q51">
-        <v>4.71</v>
+        <v>4.33</v>
       </c>
       <c r="R51">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="S51">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="T51">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="U51">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="V51">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W51">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X51">
         <v>1.08</v>
       </c>
       <c r="Y51">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="Z51">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AA51">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="AB51">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC51">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="AD51">
         <v>1.08</v>
@@ -8676,26 +8676,26 @@
         <v>1.03</v>
       </c>
       <c r="AF51">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="AG51">
+        <v>1.6</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.57</v>
       </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.33</v>
-      </c>
       <c r="AK51">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9111,22 +9111,22 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O54">
         <v>3.4</v>
       </c>
       <c r="P54">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q54">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="R54">
         <v>2.3</v>
       </c>
       <c r="S54">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T54">
         <v>3.25</v>
@@ -9135,37 +9135,37 @@
         <v>2.47</v>
       </c>
       <c r="V54">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W54">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X54">
         <v>1.03</v>
       </c>
       <c r="Y54">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z54">
-        <v>4.38</v>
+        <v>4.25</v>
       </c>
       <c r="AA54">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="AB54">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="AC54">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AD54">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE54">
         <v>1.17</v>
       </c>
       <c r="AF54">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG54">
         <v>2.3</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK54">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9274,16 +9274,16 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="O55">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P55">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="Q55">
-        <v>2.83</v>
+        <v>2.59</v>
       </c>
       <c r="R55">
         <v>2.23</v>
@@ -9295,7 +9295,7 @@
         <v>3.34</v>
       </c>
       <c r="U55">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="V55">
         <v>1.56</v>
@@ -9307,22 +9307,22 @@
         <v>1.03</v>
       </c>
       <c r="Y55">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z55">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="AA55">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AB55">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AC55">
         <v>2.4</v>
       </c>
       <c r="AD55">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE55">
         <v>1.21</v>
@@ -9331,7 +9331,7 @@
         <v>1.49</v>
       </c>
       <c r="AG55">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AK55">
         <v>1.6</v>
@@ -9443,58 +9443,58 @@
         <v>4</v>
       </c>
       <c r="P56">
-        <v>3.9</v>
+        <v>4.07</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="O57">
         <v>3.7</v>
       </c>
       <c r="P57">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9766,7 +9766,7 @@
         <v>1.7</v>
       </c>
       <c r="O58">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P58">
         <v>3.9</v>
@@ -9787,7 +9787,7 @@
         <v>2.44</v>
       </c>
       <c r="V58">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W58">
         <v>1.08</v>
@@ -9796,10 +9796,10 @@
         <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z58">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA58">
         <v>1.69</v>
@@ -9811,13 +9811,13 @@
         <v>2.59</v>
       </c>
       <c r="AD58">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AE58">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF58">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG58">
         <v>2.13</v>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK58">
         <v>1.99</v>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O59">
         <v>3.6</v>
@@ -9935,55 +9935,55 @@
         <v>3.6</v>
       </c>
       <c r="Q59">
+        <v>2.25</v>
+      </c>
+      <c r="R59">
         <v>2.3</v>
       </c>
-      <c r="R59">
-        <v>2.29</v>
-      </c>
       <c r="S59">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T59">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="U59">
         <v>2.32</v>
       </c>
       <c r="V59">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W59">
         <v>1.09</v>
       </c>
       <c r="X59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y59">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z59">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AA59">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AB59">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AC59">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AD59">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE59">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF59">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG59">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10427,52 +10427,52 @@
         <v>2.41</v>
       </c>
       <c r="R62">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S62">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T62">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U62">
         <v>3.2</v>
       </c>
       <c r="V62">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W62">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X62">
         <v>1.05</v>
       </c>
       <c r="Y62">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z62">
         <v>3</v>
       </c>
       <c r="AA62">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AB62">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AC62">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AD62">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE62">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF62">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AG62">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK62">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10587,16 +10587,16 @@
         <v>11.5</v>
       </c>
       <c r="Q63">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R63">
         <v>2.9</v>
       </c>
       <c r="S63">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T63">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="U63">
         <v>2.1</v>
@@ -10605,16 +10605,16 @@
         <v>1.64</v>
       </c>
       <c r="W63">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X63">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z63">
-        <v>5.19</v>
+        <v>5.5</v>
       </c>
       <c r="AA63">
         <v>1.47</v>
@@ -10623,19 +10623,19 @@
         <v>2.6</v>
       </c>
       <c r="AC63">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AD63">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE63">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF63">
         <v>2.05</v>
       </c>
       <c r="AG63">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK63">
-        <v>3.96</v>
+        <v>5.45</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,13 +10750,13 @@
         <v>2.2</v>
       </c>
       <c r="Q64">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="R64">
         <v>2.27</v>
       </c>
       <c r="S64">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T64">
         <v>3.25</v>
@@ -10768,19 +10768,19 @@
         <v>1.44</v>
       </c>
       <c r="W64">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X64">
         <v>1.04</v>
       </c>
       <c r="Y64">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z64">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="AA64">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB64">
         <v>2</v>
@@ -10904,25 +10904,25 @@
         </is>
       </c>
       <c r="N65">
-        <v>4.17</v>
+        <v>3.4</v>
       </c>
       <c r="O65">
-        <v>4.17</v>
+        <v>3.78</v>
       </c>
       <c r="P65">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="Q65">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="R65">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S65">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T65">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U65">
         <v>2.39</v>
@@ -10934,34 +10934,34 @@
         <v>1.08</v>
       </c>
       <c r="X65">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
         <v>1.2</v>
       </c>
       <c r="Z65">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA65">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB65">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AC65">
-        <v>2.51</v>
+        <v>2.73</v>
       </c>
       <c r="AD65">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE65">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF65">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AG65">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="AK65">
         <v>1.22</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O66">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P66">
-        <v>4.94</v>
+        <v>5.05</v>
       </c>
       <c r="Q66">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="R66">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="S66">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T66">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="U66">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="V66">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W66">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X66">
         <v>1.04</v>
       </c>
       <c r="Y66">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z66">
-        <v>4.62</v>
+        <v>4.15</v>
       </c>
       <c r="AA66">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AB66">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AC66">
-        <v>2.59</v>
+        <v>2.43</v>
       </c>
       <c r="AD66">
         <v>1.51</v>
       </c>
       <c r="AE66">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF66">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AG66">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK66">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11233,7 +11233,7 @@
         <v>1.75</v>
       </c>
       <c r="O67">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P67">
         <v>3.8</v>
@@ -11242,7 +11242,7 @@
         <v>2.26</v>
       </c>
       <c r="R67">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S67">
         <v>1.3</v>
@@ -11251,10 +11251,10 @@
         <v>3.08</v>
       </c>
       <c r="U67">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="V67">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
         <v>1.05</v>
@@ -11263,28 +11263,28 @@
         <v>1.04</v>
       </c>
       <c r="Y67">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="Z67">
         <v>3.58</v>
       </c>
       <c r="AA67">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AB67">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC67">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AD67">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE67">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF67">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG67">
         <v>1.95</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK67">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,49 +11393,49 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="O68">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="P68">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q68">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="R68">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S68">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="T68">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="U68">
         <v>2.82</v>
       </c>
       <c r="V68">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W68">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X68">
         <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z68">
-        <v>3</v>
+        <v>3.19</v>
       </c>
       <c r="AA68">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB68">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC68">
         <v>3.42</v>
@@ -11447,10 +11447,10 @@
         <v>1.05</v>
       </c>
       <c r="AF68">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG68">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK68">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O71">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P71">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q71">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R71">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S71">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T71">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U71">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V71">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W71">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y71">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z71">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AA71">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AB71">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC71">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD71">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE71">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF71">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG71">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK71">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O73">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P73">
-        <v>4.51</v>
+        <v>0</v>
       </c>
       <c r="Q73">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R73">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S73">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T73">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U73">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="V73">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W73">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X73">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y73">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z73">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA73">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB73">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC73">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD73">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE73">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF73">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG73">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK73">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="O75">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P75">
-        <v>3.32</v>
+        <v>4</v>
       </c>
       <c r="Q75">
-        <v>2.71</v>
+        <v>2.16</v>
       </c>
       <c r="R75">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S75">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T75">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="U75">
-        <v>2.69</v>
+        <v>2.89</v>
       </c>
       <c r="V75">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W75">
+        <v>1.08</v>
+      </c>
+      <c r="X75">
+        <v>1.01</v>
+      </c>
+      <c r="Y75">
+        <v>1.3</v>
+      </c>
+      <c r="Z75">
+        <v>3.38</v>
+      </c>
+      <c r="AA75">
+        <v>1.87</v>
+      </c>
+      <c r="AB75">
+        <v>1.84</v>
+      </c>
+      <c r="AC75">
+        <v>3.1</v>
+      </c>
+      <c r="AD75">
+        <v>1.3</v>
+      </c>
+      <c r="AE75">
         <v>1.07</v>
       </c>
-      <c r="X75">
-        <v>1</v>
-      </c>
-      <c r="Y75">
-        <v>1.25</v>
-      </c>
-      <c r="Z75">
-        <v>3.8</v>
-      </c>
-      <c r="AA75">
-        <v>1.78</v>
-      </c>
-      <c r="AB75">
-        <v>1.93</v>
-      </c>
-      <c r="AC75">
-        <v>3.01</v>
-      </c>
-      <c r="AD75">
-        <v>1.36</v>
-      </c>
-      <c r="AE75">
-        <v>1.11</v>
-      </c>
       <c r="AF75">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AG75">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK75">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="O76">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="P76">
-        <v>4.51</v>
+        <v>5.5</v>
       </c>
       <c r="Q76">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="R76">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S76">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T76">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="U76">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="V76">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="W76">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X76">
         <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z76">
-        <v>3.43</v>
+        <v>4.1</v>
       </c>
       <c r="AA76">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AB76">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="AC76">
-        <v>3.05</v>
+        <v>2.45</v>
       </c>
       <c r="AD76">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AE76">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF76">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AG76">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK76">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,31 +12860,31 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.6</v>
+        <v>2.64</v>
       </c>
       <c r="O77">
-        <v>4.15</v>
+        <v>3.2</v>
       </c>
       <c r="P77">
-        <v>4.97</v>
+        <v>2.37</v>
       </c>
       <c r="Q77">
-        <v>2.03</v>
+        <v>2.97</v>
       </c>
       <c r="R77">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S77">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T77">
-        <v>3.4</v>
+        <v>3.03</v>
       </c>
       <c r="U77">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="V77">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="W77">
         <v>1.08</v>
@@ -12893,31 +12893,31 @@
         <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z77">
-        <v>4.4</v>
+        <v>3.52</v>
       </c>
       <c r="AA77">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AB77">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC77">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="AD77">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AE77">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF77">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AG77">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AK77">
-        <v>2.42</v>
+        <v>1.39</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="O78">
         <v>3.5</v>
       </c>
       <c r="P78">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13195,25 +13195,25 @@
         <v>7.75</v>
       </c>
       <c r="Q79">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R79">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="S79">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T79">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U79">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="V79">
         <v>1.67</v>
       </c>
       <c r="W79">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X79">
         <v>1.01</v>
@@ -13231,13 +13231,13 @@
         <v>2.62</v>
       </c>
       <c r="AC79">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AD79">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE79">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AF79">
         <v>1.66</v>
@@ -13259,7 +13259,7 @@
         <v>1.09</v>
       </c>
       <c r="AK79">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="O81">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="P81">
-        <v>5.53</v>
+        <v>5</v>
       </c>
       <c r="Q81">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="R81">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S81">
         <v>1.32</v>
       </c>
       <c r="T81">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U81">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V81">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W81">
+        <v>1.07</v>
+      </c>
+      <c r="X81">
+        <v>1.04</v>
+      </c>
+      <c r="Y81">
+        <v>1.25</v>
+      </c>
+      <c r="Z81">
+        <v>3.92</v>
+      </c>
+      <c r="AA81">
+        <v>1.8</v>
+      </c>
+      <c r="AB81">
+        <v>2</v>
+      </c>
+      <c r="AC81">
+        <v>2.97</v>
+      </c>
+      <c r="AD81">
+        <v>1.37</v>
+      </c>
+      <c r="AE81">
         <v>1.11</v>
       </c>
-      <c r="X81">
-        <v>1.05</v>
-      </c>
-      <c r="Y81">
-        <v>1.21</v>
-      </c>
-      <c r="Z81">
-        <v>3.62</v>
-      </c>
-      <c r="AA81">
-        <v>1.82</v>
-      </c>
-      <c r="AB81">
-        <v>1.87</v>
-      </c>
-      <c r="AC81">
-        <v>3</v>
-      </c>
-      <c r="AD81">
-        <v>1.38</v>
-      </c>
-      <c r="AE81">
-        <v>1.15</v>
-      </c>
       <c r="AF81">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG81">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK81">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,31 +13675,31 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="O82">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="P82">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q82">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R82">
-        <v>3.11</v>
+        <v>2.83</v>
       </c>
       <c r="S82">
         <v>1.2</v>
       </c>
       <c r="T82">
-        <v>3.88</v>
+        <v>4.5</v>
       </c>
       <c r="U82">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="V82">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="W82">
         <v>1.14</v>
@@ -13708,10 +13708,10 @@
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z82">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="AA82">
         <v>1.39</v>
@@ -13723,16 +13723,16 @@
         <v>2.17</v>
       </c>
       <c r="AD82">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE82">
         <v>1.24</v>
       </c>
       <c r="AF82">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AG82">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK82">
         <v>4.98</v>
@@ -14010,25 +14010,25 @@
         <v>3.1</v>
       </c>
       <c r="Q84">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="R84">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S84">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="T84">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="U84">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V84">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W84">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X84">
         <v>1.1</v>
@@ -14040,13 +14040,13 @@
         <v>2.56</v>
       </c>
       <c r="AA84">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="AB84">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AC84">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="AD84">
         <v>1.17</v>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK84">
         <v>1.57</v>
@@ -14179,13 +14179,13 @@
         <v>2.25</v>
       </c>
       <c r="S85">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T85">
         <v>2.77</v>
       </c>
       <c r="U85">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="V85">
         <v>1.4</v>
@@ -14194,7 +14194,7 @@
         <v>1.06</v>
       </c>
       <c r="X85">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y85">
         <v>1.27</v>
@@ -14203,7 +14203,7 @@
         <v>3.64</v>
       </c>
       <c r="AA85">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AB85">
         <v>1.75</v>
@@ -14212,10 +14212,10 @@
         <v>3.08</v>
       </c>
       <c r="AD85">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE85">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF85">
         <v>1.73</v>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="AK85">
         <v>1.26</v>
@@ -14499,55 +14499,55 @@
         <v>0</v>
       </c>
       <c r="Q87">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R87">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S87">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="T87">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U87">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V87">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W87">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X87">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y87">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z87">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA87">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="AB87">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC87">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD87">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE87">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF87">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AG87">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK87">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="O88">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="P88">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -16609,22 +16609,22 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="O100">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="P100">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q100">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R100">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="S100">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T100">
         <v>3.25</v>
@@ -16636,37 +16636,37 @@
         <v>1.49</v>
       </c>
       <c r="W100">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X100">
         <v>1.01</v>
       </c>
       <c r="Y100">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z100">
         <v>4.35</v>
       </c>
       <c r="AA100">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AB100">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="AC100">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="AD100">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE100">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF100">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AG100">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>1.07</v>
       </c>
       <c r="AK100">
-        <v>4.45</v>
+        <v>4.82</v>
       </c>
       <c r="AL100">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,31 +13675,31 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="O82">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P82">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="Q82">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="R82">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S82">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T82">
-        <v>2.95</v>
+        <v>3.34</v>
       </c>
       <c r="U82">
-        <v>2.89</v>
+        <v>2.36</v>
       </c>
       <c r="V82">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="W82">
         <v>1.08</v>
@@ -13708,31 +13708,31 @@
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z82">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="AA82">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AB82">
-        <v>1.84</v>
+        <v>2.26</v>
       </c>
       <c r="AC82">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="AD82">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE82">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF82">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AG82">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK82">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,31 +13838,31 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="O83">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P83">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="Q83">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="R83">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S83">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T83">
-        <v>3.34</v>
+        <v>2.95</v>
       </c>
       <c r="U83">
-        <v>2.36</v>
+        <v>2.89</v>
       </c>
       <c r="V83">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="W83">
         <v>1.08</v>
@@ -13871,31 +13871,31 @@
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z83">
-        <v>4.1</v>
+        <v>3.38</v>
       </c>
       <c r="AA83">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AB83">
-        <v>2.26</v>
+        <v>1.84</v>
       </c>
       <c r="AC83">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AD83">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE83">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF83">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AG83">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK83">
-        <v>2.38</v>
+        <v>1.96</v>
       </c>
       <c r="AL83">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,31 +13675,31 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="O82">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P82">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="Q82">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="R82">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S82">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T82">
-        <v>3.34</v>
+        <v>2.95</v>
       </c>
       <c r="U82">
-        <v>2.36</v>
+        <v>2.89</v>
       </c>
       <c r="V82">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="W82">
         <v>1.08</v>
@@ -13708,31 +13708,31 @@
         <v>1.01</v>
       </c>
       <c r="Y82">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z82">
-        <v>4.1</v>
+        <v>3.38</v>
       </c>
       <c r="AA82">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AB82">
-        <v>2.26</v>
+        <v>1.84</v>
       </c>
       <c r="AC82">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AD82">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE82">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF82">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AG82">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK82">
-        <v>2.38</v>
+        <v>1.96</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,31 +13838,31 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="O83">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P83">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="Q83">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="R83">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S83">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T83">
-        <v>2.95</v>
+        <v>3.34</v>
       </c>
       <c r="U83">
-        <v>2.89</v>
+        <v>2.36</v>
       </c>
       <c r="V83">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="W83">
         <v>1.08</v>
@@ -13871,31 +13871,31 @@
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z83">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="AA83">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AB83">
-        <v>1.84</v>
+        <v>2.26</v>
       </c>
       <c r="AC83">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="AD83">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE83">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AF83">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AG83">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK83">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="AL83">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="O3">
         <v>3.22</v>
       </c>
       <c r="P3">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q3">
-        <v>5.25</v>
+        <v>4.7</v>
       </c>
       <c r="R3">
         <v>2</v>
@@ -816,16 +816,16 @@
         <v>1.48</v>
       </c>
       <c r="T3">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="U3">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="V3">
         <v>1.29</v>
       </c>
       <c r="W3">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
         <v>1.04</v>
@@ -837,25 +837,25 @@
         <v>2.64</v>
       </c>
       <c r="AA3">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AB3">
         <v>1.61</v>
       </c>
       <c r="AC3">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="AD3">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AG3">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>1.48</v>
       </c>
       <c r="O5">
-        <v>3.72</v>
+        <v>5.2</v>
       </c>
       <c r="P5">
-        <v>2.1</v>
+        <v>5.9</v>
       </c>
       <c r="Q5">
-        <v>3.16</v>
+        <v>1.83</v>
       </c>
       <c r="R5">
-        <v>2.29</v>
+        <v>2.94</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T5">
-        <v>3.36</v>
+        <v>4.2</v>
       </c>
       <c r="U5">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="V5">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="W5">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="Z5">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AA5">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AB5">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AC5">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AD5">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AE5">
+        <v>1.33</v>
+      </c>
+      <c r="AF5">
+        <v>1.49</v>
+      </c>
+      <c r="AG5">
+        <v>2.38</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.16</v>
       </c>
-      <c r="AF5">
-        <v>1.53</v>
-      </c>
-      <c r="AG5">
-        <v>2.3</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.78</v>
-      </c>
       <c r="AK5">
-        <v>1.24</v>
+        <v>3</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.36</v>
+        <v>3.35</v>
       </c>
       <c r="O6">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="P6">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="Q6">
-        <v>1.83</v>
+        <v>3.16</v>
       </c>
       <c r="R6">
-        <v>2.95</v>
+        <v>2.45</v>
       </c>
       <c r="S6">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>4.2</v>
+        <v>3.36</v>
       </c>
       <c r="U6">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="V6">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="W6">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AA6">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AB6">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="AC6">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AD6">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="AE6">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AF6">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AG6">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.07</v>
+        <v>1.78</v>
       </c>
       <c r="AK6">
-        <v>2.29</v>
+        <v>1.24</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1453,13 +1453,13 @@
         <v>2.02</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="P7">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="Q7">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="R7">
         <v>2.04</v>
@@ -1471,7 +1471,7 @@
         <v>2.8</v>
       </c>
       <c r="U7">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V7">
         <v>1.38</v>
@@ -1486,13 +1486,13 @@
         <v>1.25</v>
       </c>
       <c r="Z7">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA7">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AB7">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AC7">
         <v>3.35</v>
@@ -1776,58 +1776,58 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.56</v>
+        <v>3.44</v>
       </c>
       <c r="O9">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P9">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q9">
-        <v>4.05</v>
+        <v>3.94</v>
       </c>
       <c r="R9">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T9">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="U9">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="AA9">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AB9">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="AC9">
         <v>2.65</v>
       </c>
       <c r="AD9">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE9">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF9">
         <v>1.6</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.3</v>
+        <v>1.79</v>
       </c>
       <c r="AK9">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.66</v>
+        <v>2.51</v>
       </c>
       <c r="O11">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="P11">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="Q11">
         <v>3.4</v>
       </c>
       <c r="R11">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="S11">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="T11">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="U11">
         <v>3.44</v>
@@ -2129,7 +2129,7 @@
         <v>1.24</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
         <v>1.06</v>
@@ -2138,22 +2138,22 @@
         <v>1.44</v>
       </c>
       <c r="Z11">
-        <v>2.43</v>
+        <v>2.64</v>
       </c>
       <c r="AA11">
         <v>2.55</v>
       </c>
       <c r="AB11">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC11">
         <v>4.79</v>
       </c>
       <c r="AD11">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF11">
         <v>2.02</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,31 +2917,31 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
         <v>3.35</v>
       </c>
       <c r="Q16">
-        <v>2.83</v>
+        <v>2.58</v>
       </c>
       <c r="R16">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="S16">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T16">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="U16">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="V16">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="W16">
         <v>1.03</v>
@@ -2950,16 +2950,16 @@
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z16">
         <v>3.08</v>
       </c>
       <c r="AA16">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB16">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AC16">
         <v>3.5</v>
@@ -2974,7 +2974,7 @@
         <v>1.82</v>
       </c>
       <c r="AG16">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.3</v>
       </c>
       <c r="AK16">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="O17">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P17">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="Q17">
         <v>2.15</v>
@@ -3095,49 +3095,49 @@
         <v>2.6</v>
       </c>
       <c r="S17">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T17">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="U17">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="V17">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="W17">
         <v>1.19</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z17">
-        <v>5.75</v>
+        <v>5.45</v>
       </c>
       <c r="AA17">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AB17">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AC17">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AD17">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AE17">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF17">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AG17">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O19">
         <v>3.6</v>
@@ -3415,7 +3415,7 @@
         <v>2.4</v>
       </c>
       <c r="Q19">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="R19">
         <v>2.44</v>
@@ -3427,10 +3427,10 @@
         <v>3.98</v>
       </c>
       <c r="U19">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V19">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="W19">
         <v>1.2</v>
@@ -3439,19 +3439,19 @@
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z19">
-        <v>6.1</v>
+        <v>5.75</v>
       </c>
       <c r="AA19">
         <v>1.36</v>
       </c>
       <c r="AB19">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AC19">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AD19">
         <v>1.76</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK19">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>4.05</v>
       </c>
       <c r="R22">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="S22">
         <v>1.56</v>
@@ -3943,7 +3943,7 @@
         <v>4.45</v>
       </c>
       <c r="AD22">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE22">
         <v>1</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AK22">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="O23">
         <v>3.65</v>
       </c>
       <c r="P23">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="Q23">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="R23">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T23">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="U23">
+        <v>2.36</v>
+      </c>
+      <c r="V23">
+        <v>1.56</v>
+      </c>
+      <c r="W23">
+        <v>1.1</v>
+      </c>
+      <c r="X23">
+        <v>1.03</v>
+      </c>
+      <c r="Y23">
+        <v>1.17</v>
+      </c>
+      <c r="Z23">
+        <v>4.65</v>
+      </c>
+      <c r="AA23">
+        <v>1.58</v>
+      </c>
+      <c r="AB23">
         <v>2.32</v>
       </c>
-      <c r="V23">
-        <v>1.53</v>
-      </c>
-      <c r="W23">
-        <v>1.13</v>
-      </c>
-      <c r="X23">
-        <v>1.01</v>
-      </c>
-      <c r="Y23">
-        <v>1.14</v>
-      </c>
-      <c r="Z23">
-        <v>4.45</v>
-      </c>
-      <c r="AA23">
-        <v>1.59</v>
-      </c>
-      <c r="AB23">
-        <v>2.29</v>
-      </c>
       <c r="AC23">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AD23">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AE23">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF23">
         <v>1.5</v>
       </c>
       <c r="AG23">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK23">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,28 +4221,28 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O24">
+        <v>3.4</v>
+      </c>
+      <c r="P24">
+        <v>2.8</v>
+      </c>
+      <c r="Q24">
         <v>3.1</v>
       </c>
-      <c r="P24">
-        <v>2.6</v>
-      </c>
-      <c r="Q24">
-        <v>3.11</v>
-      </c>
       <c r="R24">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S24">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T24">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="U24">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V24">
         <v>1.4</v>
@@ -4254,28 +4254,28 @@
         <v>1</v>
       </c>
       <c r="Y24">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z24">
-        <v>3.78</v>
+        <v>3.38</v>
       </c>
       <c r="AA24">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AB24">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC24">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="AD24">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE24">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF24">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG24">
         <v>2.1</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AK24">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4387,58 +4387,58 @@
         <v>2.25</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q25">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="R25">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S25">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T25">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="U25">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="V25">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z25">
         <v>3.8</v>
       </c>
       <c r="AA25">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB25">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC25">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="AD25">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE25">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG25">
         <v>2.15</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK25">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4873,52 +4873,52 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="O28">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="P28">
-        <v>4.51</v>
+        <v>4.25</v>
       </c>
       <c r="Q28">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="R28">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="S28">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T28">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="U28">
         <v>2.62</v>
       </c>
       <c r="V28">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z28">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA28">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AB28">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AC28">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AD28">
         <v>1.3</v>
@@ -4927,7 +4927,7 @@
         <v>1.11</v>
       </c>
       <c r="AF28">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG28">
         <v>1.95</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5208,55 +5208,55 @@
         <v>2.69</v>
       </c>
       <c r="Q30">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="R30">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S30">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T30">
         <v>3.16</v>
       </c>
       <c r="U30">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V30">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W30">
         <v>1.11</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
         <v>1.2</v>
       </c>
       <c r="Z30">
-        <v>4.39</v>
+        <v>4.2</v>
       </c>
       <c r="AA30">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AB30">
         <v>2.15</v>
       </c>
       <c r="AC30">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AD30">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE30">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF30">
         <v>1.5</v>
       </c>
       <c r="AG30">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AK30">
         <v>1.56</v>
@@ -5371,22 +5371,22 @@
         <v>3.15</v>
       </c>
       <c r="Q31">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="R31">
         <v>2.2</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T31">
         <v>3.16</v>
       </c>
       <c r="U31">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="V31">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W31">
         <v>1.08</v>
@@ -5398,13 +5398,13 @@
         <v>1.16</v>
       </c>
       <c r="Z31">
-        <v>4.1</v>
+        <v>4.29</v>
       </c>
       <c r="AA31">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AB31">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AC31">
         <v>2.52</v>
@@ -5413,7 +5413,7 @@
         <v>1.41</v>
       </c>
       <c r="AE31">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF31">
         <v>1.52</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK31">
         <v>1.68</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -6017,28 +6017,28 @@
         <v>1.85</v>
       </c>
       <c r="O35">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P35">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q35">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="R35">
         <v>2.21</v>
       </c>
       <c r="S35">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U35">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V35">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W35">
         <v>1.07</v>
@@ -6050,28 +6050,28 @@
         <v>1.18</v>
       </c>
       <c r="Z35">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA35">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB35">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AC35">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="AD35">
         <v>1.43</v>
       </c>
       <c r="AE35">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AF35">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AG35">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK35">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6675,25 +6675,25 @@
         <v>2.55</v>
       </c>
       <c r="Q39">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="R39">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="S39">
         <v>1.43</v>
       </c>
       <c r="T39">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="U39">
-        <v>2.82</v>
+        <v>2.97</v>
       </c>
       <c r="V39">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W39">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
         <v>1.03</v>
@@ -6708,13 +6708,13 @@
         <v>1.96</v>
       </c>
       <c r="AB39">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC39">
         <v>3.2</v>
       </c>
       <c r="AD39">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE39">
         <v>1.06</v>
@@ -6723,7 +6723,7 @@
         <v>1.72</v>
       </c>
       <c r="AG39">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.4</v>
       </c>
       <c r="AK39">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6844,46 +6844,46 @@
         <v>1.98</v>
       </c>
       <c r="S40">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T40">
         <v>2.56</v>
       </c>
       <c r="U40">
-        <v>3.14</v>
+        <v>3.02</v>
       </c>
       <c r="V40">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W40">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z40">
-        <v>2.92</v>
+        <v>3.06</v>
       </c>
       <c r="AA40">
         <v>2.08</v>
       </c>
       <c r="AB40">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AC40">
-        <v>3.77</v>
+        <v>3.7</v>
       </c>
       <c r="AD40">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE40">
         <v>1.03</v>
       </c>
       <c r="AF40">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG40">
         <v>1.85</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK40">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,10 +7001,10 @@
         <v>2.65</v>
       </c>
       <c r="Q41">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R41">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S41">
         <v>1.41</v>
@@ -7013,10 +7013,10 @@
         <v>2.59</v>
       </c>
       <c r="U41">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="V41">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W41">
         <v>1.04</v>
@@ -7025,19 +7025,19 @@
         <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z41">
         <v>3.05</v>
       </c>
       <c r="AA41">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AB41">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC41">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="AD41">
         <v>1.26</v>
@@ -7333,19 +7333,19 @@
         <v>2.06</v>
       </c>
       <c r="S43">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T43">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="U43">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="V43">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W43">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
         <v>1.01</v>
@@ -7360,22 +7360,22 @@
         <v>1.86</v>
       </c>
       <c r="AB43">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AC43">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD43">
         <v>1.28</v>
       </c>
       <c r="AE43">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF43">
         <v>1.69</v>
       </c>
       <c r="AG43">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK43">
         <v>1.59</v>
@@ -7481,10 +7481,10 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="O44">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P44">
         <v>3.05</v>
@@ -7493,13 +7493,13 @@
         <v>2.99</v>
       </c>
       <c r="R44">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="S44">
         <v>1.47</v>
       </c>
       <c r="T44">
-        <v>2.69</v>
+        <v>2.41</v>
       </c>
       <c r="U44">
         <v>3.08</v>
@@ -7520,16 +7520,16 @@
         <v>2.74</v>
       </c>
       <c r="AA44">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AB44">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC44">
         <v>3.74</v>
       </c>
       <c r="AD44">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE44">
         <v>1.03</v>
@@ -7554,7 +7554,7 @@
         <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="O47">
         <v>3.6</v>
       </c>
       <c r="P47">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="Q47">
         <v>2.45</v>
@@ -7985,49 +7985,49 @@
         <v>2.23</v>
       </c>
       <c r="S47">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T47">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="U47">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="V47">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W47">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y47">
         <v>1.18</v>
       </c>
       <c r="Z47">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA47">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB47">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC47">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AD47">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE47">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF47">
         <v>1.49</v>
       </c>
       <c r="AG47">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8465,43 +8465,43 @@
         <v>4.2</v>
       </c>
       <c r="P50">
-        <v>5.67</v>
+        <v>4.8</v>
       </c>
       <c r="Q50">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R50">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
       <c r="S50">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T50">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U50">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="V50">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W50">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y50">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>4.14</v>
+        <v>3.95</v>
       </c>
       <c r="AA50">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AB50">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC50">
         <v>2.82</v>
@@ -8510,7 +8510,7 @@
         <v>1.4</v>
       </c>
       <c r="AE50">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF50">
         <v>1.75</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AK50">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8785,37 +8785,37 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="O52">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="Q52">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="R52">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="S52">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="T52">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="U52">
         <v>2.27</v>
       </c>
       <c r="V52">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W52">
         <v>1.11</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
         <v>1.17</v>
@@ -8824,19 +8824,19 @@
         <v>4.4</v>
       </c>
       <c r="AA52">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB52">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="AC52">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="AD52">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE52">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF52">
         <v>1.5</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
         <v>1.67</v>
@@ -9437,31 +9437,31 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O56">
         <v>3.4</v>
       </c>
       <c r="P56">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q56">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="R56">
         <v>2.3</v>
       </c>
       <c r="S56">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T56">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="U56">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="V56">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W56">
         <v>1.13</v>
@@ -9470,28 +9470,28 @@
         <v>1.03</v>
       </c>
       <c r="Y56">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z56">
         <v>4.25</v>
       </c>
       <c r="AA56">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB56">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AC56">
         <v>2.6</v>
       </c>
       <c r="AD56">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE56">
         <v>1.17</v>
       </c>
       <c r="AF56">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AG56">
         <v>2.3</v>
@@ -10252,19 +10252,19 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="O61">
         <v>3.55</v>
       </c>
       <c r="P61">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="Q61">
-        <v>2.59</v>
+        <v>2.8</v>
       </c>
       <c r="R61">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S61">
         <v>1.28</v>
@@ -10273,43 +10273,43 @@
         <v>3.34</v>
       </c>
       <c r="U61">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="V61">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W61">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X61">
         <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z61">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="AA61">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB61">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AC61">
         <v>2.4</v>
       </c>
       <c r="AD61">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE61">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AF61">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AG61">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AK61">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O62">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P62">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q62">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="R62">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S62">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="T62">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="U62">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V62">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W62">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X62">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y62">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z62">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA62">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB62">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AC62">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD62">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE62">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF62">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG62">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK62">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O63">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P63">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Q63">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S63">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T63">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U63">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V63">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W63">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X63">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y63">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z63">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA63">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AB63">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AC63">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AD63">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE63">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF63">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG63">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK63">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="O64">
         <v>3.6</v>
       </c>
       <c r="P64">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="Q64">
         <v>2.25</v>
@@ -10756,49 +10756,49 @@
         <v>2.3</v>
       </c>
       <c r="S64">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T64">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="U64">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V64">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W64">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X64">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y64">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z64">
-        <v>4.6</v>
+        <v>3.88</v>
       </c>
       <c r="AA64">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AB64">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC64">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="AD64">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AE64">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF64">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG64">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK64">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>5.19</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11233,28 +11233,28 @@
         <v>1.65</v>
       </c>
       <c r="O67">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P67">
-        <v>4.07</v>
+        <v>3.75</v>
       </c>
       <c r="Q67">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="R67">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="S67">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="T67">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U67">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="V67">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="W67">
         <v>1.21</v>
@@ -11263,16 +11263,16 @@
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z67">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AA67">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB67">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AC67">
         <v>1.85</v>
@@ -11396,61 +11396,61 @@
         <v>1.7</v>
       </c>
       <c r="O68">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P68">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q68">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="R68">
         <v>2.1</v>
       </c>
       <c r="S68">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T68">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U68">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="V68">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W68">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X68">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
         <v>1.32</v>
       </c>
       <c r="Z68">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AA68">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AB68">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC68">
-        <v>4.1</v>
+        <v>3.72</v>
       </c>
       <c r="AD68">
         <v>1.21</v>
       </c>
       <c r="AE68">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF68">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AG68">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AK68">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11562,55 +11562,55 @@
         <v>6.75</v>
       </c>
       <c r="P69">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Q69">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="R69">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="S69">
         <v>1.2</v>
       </c>
       <c r="T69">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="U69">
         <v>2.1</v>
       </c>
       <c r="V69">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W69">
+        <v>1.18</v>
+      </c>
+      <c r="X69">
+        <v>1.01</v>
+      </c>
+      <c r="Y69">
         <v>1.14</v>
       </c>
-      <c r="X69">
-        <v>1.02</v>
-      </c>
-      <c r="Y69">
-        <v>1.15</v>
-      </c>
       <c r="Z69">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AA69">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AB69">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="AC69">
         <v>2.18</v>
       </c>
       <c r="AD69">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AE69">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF69">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AG69">
         <v>1.7</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AK69">
-        <v>5.45</v>
+        <v>4.6</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,28 +11719,28 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="O70">
         <v>3.75</v>
       </c>
       <c r="P70">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q70">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="R70">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S70">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U70">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="V70">
         <v>1.44</v>
@@ -11761,7 +11761,7 @@
         <v>1.73</v>
       </c>
       <c r="AB70">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC70">
         <v>2.78</v>
@@ -11770,7 +11770,7 @@
         <v>1.34</v>
       </c>
       <c r="AE70">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF70">
         <v>1.59</v>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK70">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O71">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P71">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q71">
-        <v>4.2</v>
+        <v>3.74</v>
       </c>
       <c r="R71">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S71">
         <v>1.28</v>
       </c>
       <c r="T71">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U71">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
       <c r="V71">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W71">
         <v>1.08</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y71">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z71">
-        <v>3.9</v>
+        <v>4.21</v>
       </c>
       <c r="AA71">
         <v>1.65</v>
       </c>
       <c r="AB71">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="AC71">
-        <v>2.73</v>
+        <v>2.48</v>
       </c>
       <c r="AD71">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE71">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF71">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AG71">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AK71">
         <v>1.22</v>
@@ -12045,25 +12045,25 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O72">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P72">
-        <v>5.03</v>
+        <v>4.5</v>
       </c>
       <c r="Q72">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R72">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="S72">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T72">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U72">
         <v>2.5</v>
@@ -12081,7 +12081,7 @@
         <v>1.2</v>
       </c>
       <c r="Z72">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA72">
         <v>1.62</v>
@@ -12118,7 +12118,7 @@
         <v>1.19</v>
       </c>
       <c r="AK72">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12208,25 +12208,25 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="O73">
         <v>3.85</v>
       </c>
       <c r="P73">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q73">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="R73">
         <v>2.23</v>
       </c>
       <c r="S73">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T73">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="U73">
         <v>2.62</v>
@@ -12235,7 +12235,7 @@
         <v>1.4</v>
       </c>
       <c r="W73">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X73">
         <v>1.04</v>
@@ -12259,13 +12259,13 @@
         <v>1.29</v>
       </c>
       <c r="AE73">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF73">
         <v>1.73</v>
       </c>
       <c r="AG73">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12371,28 +12371,28 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="O74">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P74">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q74">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="R74">
         <v>1.95</v>
       </c>
       <c r="S74">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="T74">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="U74">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="V74">
         <v>1.33</v>
@@ -12401,34 +12401,34 @@
         <v>1.03</v>
       </c>
       <c r="X74">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y74">
         <v>1.33</v>
       </c>
       <c r="Z74">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="AA74">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB74">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AC74">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AD74">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE74">
         <v>1.05</v>
       </c>
       <c r="AF74">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG74">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK74">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -13026,13 +13026,13 @@
         <v>1.7</v>
       </c>
       <c r="O78">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="P78">
-        <v>4.2</v>
+        <v>3.73</v>
       </c>
       <c r="Q78">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="R78">
         <v>2.36</v>
@@ -13041,19 +13041,19 @@
         <v>1.33</v>
       </c>
       <c r="T78">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="U78">
         <v>2.6</v>
       </c>
       <c r="V78">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W78">
         <v>1.08</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y78">
         <v>1.25</v>
@@ -13062,25 +13062,25 @@
         <v>3.45</v>
       </c>
       <c r="AA78">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AB78">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AC78">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="AD78">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AE78">
         <v>1.1</v>
       </c>
       <c r="AF78">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AG78">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK78">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13352,13 +13352,13 @@
         <v>2.12</v>
       </c>
       <c r="O80">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="P80">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q80">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="R80">
         <v>2.12</v>
@@ -13367,37 +13367,37 @@
         <v>1.35</v>
       </c>
       <c r="T80">
-        <v>3.16</v>
+        <v>2.94</v>
       </c>
       <c r="U80">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="V80">
         <v>1.44</v>
       </c>
       <c r="W80">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X80">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z80">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="AA80">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AB80">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AC80">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="AD80">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE80">
         <v>1.1</v>
@@ -13515,37 +13515,37 @@
         <v>2.64</v>
       </c>
       <c r="O81">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="P81">
-        <v>2.37</v>
+        <v>2.21</v>
       </c>
       <c r="Q81">
         <v>2.97</v>
       </c>
       <c r="R81">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S81">
         <v>1.35</v>
       </c>
       <c r="T81">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="U81">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="V81">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W81">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z81">
         <v>3.52</v>
@@ -13554,7 +13554,7 @@
         <v>1.82</v>
       </c>
       <c r="AB81">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC81">
         <v>3.1</v>
@@ -13563,13 +13563,13 @@
         <v>1.3</v>
       </c>
       <c r="AE81">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF81">
         <v>1.63</v>
       </c>
       <c r="AG81">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13678,61 +13678,61 @@
         <v>1.7</v>
       </c>
       <c r="O82">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="P82">
         <v>4</v>
       </c>
       <c r="Q82">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="R82">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S82">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T82">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="U82">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="V82">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W82">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X82">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y82">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z82">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="AA82">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AB82">
         <v>1.84</v>
       </c>
       <c r="AC82">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD82">
         <v>1.3</v>
       </c>
       <c r="AE82">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF82">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AG82">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK82">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,25 +13838,25 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="O83">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P83">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="Q83">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R83">
         <v>2.28</v>
       </c>
       <c r="S83">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T83">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="U83">
         <v>2.36</v>
@@ -13868,7 +13868,7 @@
         <v>1.08</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y83">
         <v>1.18</v>
@@ -13877,19 +13877,19 @@
         <v>4.1</v>
       </c>
       <c r="AA83">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB83">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AC83">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AD83">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE83">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF83">
         <v>1.68</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK83">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="O84">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P84">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14194,7 +14194,7 @@
         <v>1.18</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
         <v>1.08</v>
@@ -14206,7 +14206,7 @@
         <v>1.38</v>
       </c>
       <c r="AB85">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AC85">
         <v>2.04</v>
@@ -14215,13 +14215,13 @@
         <v>1.67</v>
       </c>
       <c r="AE85">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF85">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG85">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AK85">
         <v>3.05</v>
@@ -14490,31 +14490,31 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="O87">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="P87">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="Q87">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="R87">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="S87">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T87">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U87">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="V87">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W87">
         <v>1.07</v>
@@ -14523,31 +14523,31 @@
         <v>1.04</v>
       </c>
       <c r="Y87">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z87">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AA87">
         <v>1.8</v>
       </c>
       <c r="AB87">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC87">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="AD87">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AE87">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF87">
         <v>1.8</v>
       </c>
       <c r="AG87">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14653,25 +14653,25 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="O88">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="P88">
         <v>11</v>
       </c>
       <c r="Q88">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R88">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="S88">
         <v>1.2</v>
       </c>
       <c r="T88">
-        <v>4.5</v>
+        <v>3.88</v>
       </c>
       <c r="U88">
         <v>2.13</v>
@@ -14680,37 +14680,37 @@
         <v>1.67</v>
       </c>
       <c r="W88">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z88">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="AA88">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB88">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="AC88">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AD88">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AE88">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF88">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG88">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AK88">
-        <v>4.98</v>
+        <v>4</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14982,10 +14982,10 @@
         <v>2.25</v>
       </c>
       <c r="O90">
+        <v>2.9</v>
+      </c>
+      <c r="P90">
         <v>3</v>
-      </c>
-      <c r="P90">
-        <v>3.1</v>
       </c>
       <c r="Q90">
         <v>3.05</v>
@@ -14994,22 +14994,22 @@
         <v>2.02</v>
       </c>
       <c r="S90">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="T90">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="U90">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="V90">
         <v>1.25</v>
       </c>
       <c r="W90">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X90">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y90">
         <v>1.48</v>
@@ -15018,19 +15018,19 @@
         <v>2.56</v>
       </c>
       <c r="AA90">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="AB90">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AC90">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="AD90">
         <v>1.17</v>
       </c>
       <c r="AE90">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AF90">
         <v>2.05</v>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK90">
         <v>1.57</v>
@@ -15142,28 +15142,28 @@
         </is>
       </c>
       <c r="N91">
+        <v>3.7</v>
+      </c>
+      <c r="O91">
         <v>3.4</v>
       </c>
-      <c r="O91">
-        <v>3.3</v>
-      </c>
       <c r="P91">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q91">
-        <v>4.34</v>
+        <v>4.45</v>
       </c>
       <c r="R91">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S91">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T91">
-        <v>2.77</v>
+        <v>3.01</v>
       </c>
       <c r="U91">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="V91">
         <v>1.4</v>
@@ -15172,34 +15172,34 @@
         <v>1.06</v>
       </c>
       <c r="X91">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y91">
         <v>1.27</v>
       </c>
       <c r="Z91">
-        <v>3.64</v>
+        <v>3.35</v>
       </c>
       <c r="AA91">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AB91">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC91">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AD91">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE91">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF91">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG91">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK91">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15637,52 +15637,52 @@
         <v>3.6</v>
       </c>
       <c r="P94">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q94">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="R94">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="S94">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T94">
         <v>2.95</v>
       </c>
       <c r="U94">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="V94">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W94">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X94">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y94">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z94">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="AA94">
+        <v>1.82</v>
+      </c>
+      <c r="AB94">
         <v>1.85</v>
       </c>
-      <c r="AB94">
-        <v>1.9</v>
-      </c>
       <c r="AC94">
-        <v>3.05</v>
+        <v>3.34</v>
       </c>
       <c r="AD94">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE94">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF94">
         <v>1.82</v>
@@ -15704,7 +15704,7 @@
         <v>1.23</v>
       </c>
       <c r="AK94">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AL94">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="O2">
         <v>3.5</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O16">
         <v>3.25</v>
       </c>
       <c r="P16">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="Q16">
         <v>2.58</v>
@@ -2938,31 +2938,31 @@
         <v>2.65</v>
       </c>
       <c r="U16">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="V16">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W16">
         <v>1.03</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z16">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="AA16">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB16">
         <v>1.71</v>
       </c>
       <c r="AC16">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="AD16">
         <v>1.22</v>
@@ -5691,61 +5691,61 @@
         <v>2.5</v>
       </c>
       <c r="O33">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="Q33">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="R33">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="S33">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T33">
         <v>3.75</v>
       </c>
       <c r="U33">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="V33">
         <v>1.67</v>
       </c>
       <c r="W33">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X33">
         <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z33">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AA33">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB33">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC33">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AD33">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AE33">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AF33">
         <v>1.38</v>
       </c>
       <c r="AG33">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.57</v>
       </c>
       <c r="AK33">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,65 +7318,65 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q43">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="R43">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="S43">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="T43">
-        <v>2.9</v>
+        <v>2.41</v>
       </c>
       <c r="U43">
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="V43">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W43">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="Z43">
-        <v>3.59</v>
+        <v>2.74</v>
       </c>
       <c r="AA43">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="AB43">
+        <v>1.65</v>
+      </c>
+      <c r="AC43">
+        <v>3.74</v>
+      </c>
+      <c r="AD43">
+        <v>1.23</v>
+      </c>
+      <c r="AE43">
+        <v>1.03</v>
+      </c>
+      <c r="AF43">
+        <v>1.85</v>
+      </c>
+      <c r="AG43">
         <v>1.84</v>
       </c>
-      <c r="AC43">
-        <v>3.25</v>
-      </c>
-      <c r="AD43">
-        <v>1.28</v>
-      </c>
-      <c r="AE43">
-        <v>1.11</v>
-      </c>
-      <c r="AF43">
-        <v>1.69</v>
-      </c>
-      <c r="AG43">
-        <v>2</v>
-      </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK43">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O44">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P44">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q44">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="R44">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="S44">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="T44">
-        <v>2.41</v>
+        <v>2.9</v>
       </c>
       <c r="U44">
-        <v>3.08</v>
+        <v>2.62</v>
       </c>
       <c r="V44">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="W44">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="Z44">
-        <v>2.74</v>
+        <v>3.59</v>
       </c>
       <c r="AA44">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="AB44">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AC44">
-        <v>3.74</v>
+        <v>3.25</v>
       </c>
       <c r="AD44">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE44">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF44">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AG44">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8957,10 +8957,10 @@
         <v>2.17</v>
       </c>
       <c r="Q53">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="R53">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="S53">
         <v>1.63</v>
@@ -8972,7 +8972,7 @@
         <v>3.9</v>
       </c>
       <c r="V53">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W53">
         <v>1.04</v>
@@ -8981,28 +8981,28 @@
         <v>1.08</v>
       </c>
       <c r="Y53">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Z53">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AA53">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="AB53">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC53">
         <v>5.65</v>
       </c>
       <c r="AD53">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE53">
         <v>1.03</v>
       </c>
       <c r="AF53">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AG53">
         <v>1.6</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AK53">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,80 +10741,80 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="O64">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P64">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q64">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="R64">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="S64">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="T64">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="U64">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="V64">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="W64">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="X64">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
+        <v>1.1</v>
+      </c>
+      <c r="Z64">
+        <v>6.5</v>
+      </c>
+      <c r="AA64">
+        <v>1.3</v>
+      </c>
+      <c r="AB64">
+        <v>2.97</v>
+      </c>
+      <c r="AC64">
+        <v>1.89</v>
+      </c>
+      <c r="AD64">
+        <v>1.9</v>
+      </c>
+      <c r="AE64">
+        <v>1.35</v>
+      </c>
+      <c r="AF64">
+        <v>1.36</v>
+      </c>
+      <c r="AG64">
+        <v>2.9</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
         <v>1.18</v>
       </c>
-      <c r="Z64">
-        <v>3.88</v>
-      </c>
-      <c r="AA64">
-        <v>1.69</v>
-      </c>
-      <c r="AB64">
-        <v>2.1</v>
-      </c>
-      <c r="AC64">
-        <v>2.59</v>
-      </c>
-      <c r="AD64">
-        <v>1.39</v>
-      </c>
-      <c r="AE64">
-        <v>1.15</v>
-      </c>
-      <c r="AF64">
-        <v>1.65</v>
-      </c>
-      <c r="AG64">
-        <v>2.13</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>1.25</v>
-      </c>
       <c r="AK64">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O65">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="P65">
+        <v>3.89</v>
+      </c>
+      <c r="Q65">
+        <v>2.3</v>
+      </c>
+      <c r="R65">
+        <v>2.48</v>
+      </c>
+      <c r="S65">
+        <v>1.26</v>
+      </c>
+      <c r="T65">
         <v>3.5</v>
       </c>
-      <c r="Q65">
-        <v>2.28</v>
-      </c>
-      <c r="R65">
-        <v>2.4</v>
-      </c>
-      <c r="S65">
-        <v>1.22</v>
-      </c>
-      <c r="T65">
-        <v>3.6</v>
-      </c>
       <c r="U65">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="V65">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="W65">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y65">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z65">
-        <v>5.19</v>
+        <v>4.65</v>
       </c>
       <c r="AA65">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AB65">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="AC65">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AD65">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AE65">
         <v>1.22</v>
       </c>
       <c r="AF65">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG65">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK65">
         <v>1.95</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="O66">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P66">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="Q66">
         <v>2.25</v>
       </c>
       <c r="R66">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S66">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T66">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U66">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V66">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W66">
         <v>1.11</v>
       </c>
       <c r="X66">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y66">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z66">
-        <v>4.6</v>
+        <v>3.88</v>
       </c>
       <c r="AA66">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AB66">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="AC66">
-        <v>2.35</v>
+        <v>2.59</v>
       </c>
       <c r="AD66">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AE66">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AF66">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG66">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="O67">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="P67">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="Q67">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="R67">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="S67">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T67">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="U67">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="V67">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="W67">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z67">
-        <v>6.5</v>
+        <v>5.19</v>
       </c>
       <c r="AA67">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AB67">
-        <v>2.97</v>
+        <v>2.54</v>
       </c>
       <c r="AC67">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="AD67">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="AE67">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AF67">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AG67">
-        <v>2.9</v>
+        <v>2.43</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>2.11</v>
+        <v>1.93</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11405,7 +11405,7 @@
         <v>2.36</v>
       </c>
       <c r="R68">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S68">
         <v>1.41</v>
@@ -11429,7 +11429,7 @@
         <v>1.32</v>
       </c>
       <c r="Z68">
-        <v>2.92</v>
+        <v>3.06</v>
       </c>
       <c r="AA68">
         <v>2.09</v>
@@ -11444,7 +11444,7 @@
         <v>1.21</v>
       </c>
       <c r="AE68">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF68">
         <v>2</v>
@@ -12211,7 +12211,7 @@
         <v>1.78</v>
       </c>
       <c r="O73">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="P73">
         <v>3.75</v>
@@ -12220,13 +12220,13 @@
         <v>2.36</v>
       </c>
       <c r="R73">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="S73">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T73">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U73">
         <v>2.62</v>
@@ -12256,7 +12256,7 @@
         <v>3.04</v>
       </c>
       <c r="AD73">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AE73">
         <v>1.12</v>
@@ -12281,7 +12281,7 @@
         <v>1.19</v>
       </c>
       <c r="AK73">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12380,7 +12380,7 @@
         <v>3.1</v>
       </c>
       <c r="Q74">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R74">
         <v>1.95</v>
@@ -12392,7 +12392,7 @@
         <v>2.5</v>
       </c>
       <c r="U74">
-        <v>2.84</v>
+        <v>3.07</v>
       </c>
       <c r="V74">
         <v>1.33</v>
@@ -12410,10 +12410,10 @@
         <v>3</v>
       </c>
       <c r="AA74">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB74">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC74">
         <v>3.48</v>
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="O88">
         <v>6.1</v>
@@ -14671,7 +14671,7 @@
         <v>1.2</v>
       </c>
       <c r="T88">
-        <v>3.88</v>
+        <v>4.5</v>
       </c>
       <c r="U88">
         <v>2.13</v>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK88">
         <v>4</v>
@@ -15305,28 +15305,28 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="O92">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P92">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="Q92">
         <v>2.98</v>
       </c>
       <c r="R92">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="S92">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T92">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="U92">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V92">
         <v>1.4</v>
@@ -15344,16 +15344,16 @@
         <v>3.65</v>
       </c>
       <c r="AA92">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AB92">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC92">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD92">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE92">
         <v>1.08</v>
@@ -15477,16 +15477,16 @@
         <v>0</v>
       </c>
       <c r="Q93">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R93">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="S93">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="T93">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="U93">
         <v>4.5</v>
@@ -15495,37 +15495,37 @@
         <v>1.17</v>
       </c>
       <c r="W93">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X93">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Y93">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Z93">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="AA93">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AB93">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC93">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AD93">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AE93">
         <v>1.02</v>
       </c>
       <c r="AF93">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="AG93">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK93">
         <v>1.54</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="O106">
         <v>6</v>
@@ -17599,52 +17599,52 @@
         <v>1.56</v>
       </c>
       <c r="R106">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="S106">
         <v>1.25</v>
       </c>
       <c r="T106">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U106">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="V106">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="W106">
+        <v>1.13</v>
+      </c>
+      <c r="X106">
+        <v>1.03</v>
+      </c>
+      <c r="Y106">
         <v>1.15</v>
       </c>
-      <c r="X106">
-        <v>1.01</v>
-      </c>
-      <c r="Y106">
-        <v>1.19</v>
-      </c>
       <c r="Z106">
-        <v>4.35</v>
+        <v>3.9</v>
       </c>
       <c r="AA106">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AB106">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="AC106">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AD106">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE106">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF106">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AG106">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>1.07</v>
       </c>
       <c r="AK106">
-        <v>4.82</v>
+        <v>4.33</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17759,22 +17759,22 @@
         <v>3.61</v>
       </c>
       <c r="Q107">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R107">
         <v>2.1</v>
       </c>
       <c r="S107">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T107">
         <v>2.75</v>
       </c>
       <c r="U107">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="V107">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W107">
         <v>1.06</v>
@@ -17783,22 +17783,22 @@
         <v>1.03</v>
       </c>
       <c r="Y107">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z107">
         <v>3.08</v>
       </c>
       <c r="AA107">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="AB107">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AC107">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AD107">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AE107">
         <v>1.07</v>
@@ -17807,7 +17807,7 @@
         <v>1.68</v>
       </c>
       <c r="AG107">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>4.05</v>
       </c>
       <c r="Q109">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="R109">
         <v>2.28</v>
@@ -18094,13 +18094,13 @@
         <v>1.26</v>
       </c>
       <c r="T109">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="U109">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V109">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W109">
         <v>1.11</v>
@@ -18109,16 +18109,16 @@
         <v>0</v>
       </c>
       <c r="Y109">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z109">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="AA109">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AB109">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AC109">
         <v>2.52</v>
@@ -18130,7 +18130,7 @@
         <v>1.13</v>
       </c>
       <c r="AF109">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG109">
         <v>2.15</v>
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK109">
         <v>1.94</v>
@@ -18248,10 +18248,10 @@
         <v>0</v>
       </c>
       <c r="Q110">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="R110">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="S110">
         <v>1.25</v>
@@ -18284,7 +18284,7 @@
         <v>2.19</v>
       </c>
       <c r="AC110">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="AD110">
         <v>1.43</v>
@@ -18293,7 +18293,7 @@
         <v>1.13</v>
       </c>
       <c r="AF110">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AG110">
         <v>2.1</v>
@@ -18309,7 +18309,7 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AK110">
         <v>2.59</v>
@@ -18411,22 +18411,22 @@
         <v>3.1</v>
       </c>
       <c r="Q111">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="R111">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="S111">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T111">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="U111">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="V111">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W111">
         <v>1.11</v>
@@ -18441,25 +18441,25 @@
         <v>3.94</v>
       </c>
       <c r="AA111">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AB111">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AC111">
         <v>2.7</v>
       </c>
       <c r="AD111">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE111">
         <v>1.1</v>
       </c>
       <c r="AF111">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG111">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK111">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AL111">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
+        <v>3.35</v>
+      </c>
+      <c r="O5">
+        <v>3.6</v>
+      </c>
+      <c r="P5">
+        <v>2.1</v>
+      </c>
+      <c r="Q5">
+        <v>3.16</v>
+      </c>
+      <c r="R5">
+        <v>2.45</v>
+      </c>
+      <c r="S5">
+        <v>1.25</v>
+      </c>
+      <c r="T5">
+        <v>3.36</v>
+      </c>
+      <c r="U5">
+        <v>2.2</v>
+      </c>
+      <c r="V5">
+        <v>1.62</v>
+      </c>
+      <c r="W5">
+        <v>1.1</v>
+      </c>
+      <c r="X5">
+        <v>1.03</v>
+      </c>
+      <c r="Y5">
+        <v>1.18</v>
+      </c>
+      <c r="Z5">
+        <v>4.5</v>
+      </c>
+      <c r="AA5">
+        <v>1.6</v>
+      </c>
+      <c r="AB5">
+        <v>2.35</v>
+      </c>
+      <c r="AC5">
+        <v>2.4</v>
+      </c>
+      <c r="AD5">
         <v>1.48</v>
       </c>
-      <c r="O5">
-        <v>5.2</v>
-      </c>
-      <c r="P5">
-        <v>5.9</v>
-      </c>
-      <c r="Q5">
-        <v>1.83</v>
-      </c>
-      <c r="R5">
-        <v>2.94</v>
-      </c>
-      <c r="S5">
-        <v>1.18</v>
-      </c>
-      <c r="T5">
-        <v>4.2</v>
-      </c>
-      <c r="U5">
-        <v>1.85</v>
-      </c>
-      <c r="V5">
-        <v>1.81</v>
-      </c>
-      <c r="W5">
-        <v>1.2</v>
-      </c>
-      <c r="X5">
-        <v>1.01</v>
-      </c>
-      <c r="Y5">
-        <v>1.08</v>
-      </c>
-      <c r="Z5">
-        <v>7</v>
-      </c>
-      <c r="AA5">
-        <v>1.33</v>
-      </c>
-      <c r="AB5">
-        <v>3.1</v>
-      </c>
-      <c r="AC5">
-        <v>1.92</v>
-      </c>
-      <c r="AD5">
-        <v>1.9</v>
-      </c>
       <c r="AE5">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AF5">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AG5">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.16</v>
+        <v>1.78</v>
       </c>
       <c r="AK5">
-        <v>3</v>
+        <v>1.24</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.35</v>
+        <v>1.48</v>
       </c>
       <c r="O6">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="P6">
-        <v>2.1</v>
+        <v>5.9</v>
       </c>
       <c r="Q6">
-        <v>3.16</v>
+        <v>1.83</v>
       </c>
       <c r="R6">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="S6">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T6">
-        <v>3.36</v>
+        <v>4.2</v>
       </c>
       <c r="U6">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="V6">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="Z6">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AB6">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AC6">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AD6">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="AE6">
+        <v>1.33</v>
+      </c>
+      <c r="AF6">
+        <v>1.49</v>
+      </c>
+      <c r="AG6">
+        <v>2.38</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
         <v>1.16</v>
       </c>
-      <c r="AF6">
-        <v>1.45</v>
-      </c>
-      <c r="AG6">
-        <v>2.45</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.78</v>
-      </c>
       <c r="AK6">
-        <v>1.24</v>
+        <v>3</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
+        <v>1.98</v>
+      </c>
+      <c r="O39">
+        <v>3.25</v>
+      </c>
+      <c r="P39">
+        <v>3.6</v>
+      </c>
+      <c r="Q39">
         <v>2.65</v>
       </c>
-      <c r="O39">
-        <v>3.05</v>
-      </c>
-      <c r="P39">
-        <v>2.55</v>
-      </c>
-      <c r="Q39">
-        <v>3.1</v>
-      </c>
       <c r="R39">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="S39">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T39">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="U39">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="V39">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X39">
+        <v>1.01</v>
+      </c>
+      <c r="Y39">
+        <v>1.35</v>
+      </c>
+      <c r="Z39">
+        <v>3.06</v>
+      </c>
+      <c r="AA39">
+        <v>2.08</v>
+      </c>
+      <c r="AB39">
+        <v>1.67</v>
+      </c>
+      <c r="AC39">
+        <v>3.7</v>
+      </c>
+      <c r="AD39">
+        <v>1.2</v>
+      </c>
+      <c r="AE39">
         <v>1.03</v>
       </c>
-      <c r="Y39">
-        <v>1.28</v>
-      </c>
-      <c r="Z39">
-        <v>3.05</v>
-      </c>
-      <c r="AA39">
-        <v>1.96</v>
-      </c>
-      <c r="AB39">
-        <v>1.75</v>
-      </c>
-      <c r="AC39">
-        <v>3.2</v>
-      </c>
-      <c r="AD39">
-        <v>1.26</v>
-      </c>
-      <c r="AE39">
-        <v>1.06</v>
-      </c>
       <c r="AF39">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="AK39">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="O40">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P40">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q40">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="R40">
         <v>1.98</v>
       </c>
       <c r="S40">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T40">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="U40">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="V40">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W40">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z40">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="AA40">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AB40">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AC40">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AD40">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AE40">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF40">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AG40">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK40">
-        <v>1.73</v>
+        <v>1.43</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S41">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U41">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V41">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y41">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z41">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA41">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG41">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK41">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O43">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P43">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q43">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="R43">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="S43">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="T43">
-        <v>2.41</v>
+        <v>2.9</v>
       </c>
       <c r="U43">
-        <v>3.08</v>
+        <v>2.62</v>
       </c>
       <c r="V43">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="W43">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="Z43">
-        <v>2.74</v>
+        <v>3.59</v>
       </c>
       <c r="AA43">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="AB43">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AC43">
-        <v>3.74</v>
+        <v>3.25</v>
       </c>
       <c r="AD43">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE43">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF43">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AG43">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK43">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G44">
@@ -7490,55 +7490,55 @@
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S44">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T44">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V44">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W44">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y44">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z44">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="AA44">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB44">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC44">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD44">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE44">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF44">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK44">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="O64">
-        <v>4.3</v>
+        <v>3.88</v>
       </c>
       <c r="P64">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="Q64">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="R64">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="S64">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="T64">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="U64">
-        <v>1.85</v>
+        <v>2.31</v>
       </c>
       <c r="V64">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="W64">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="X64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Z64">
-        <v>6.5</v>
+        <v>4.65</v>
       </c>
       <c r="AA64">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AB64">
-        <v>2.97</v>
+        <v>2.33</v>
       </c>
       <c r="AC64">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="AD64">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AE64">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AF64">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AG64">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK64">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="O65">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P65">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="Q65">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R65">
-        <v>2.48</v>
+        <v>2.27</v>
       </c>
       <c r="S65">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T65">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U65">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="V65">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W65">
         <v>1.11</v>
       </c>
       <c r="X65">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z65">
-        <v>4.65</v>
+        <v>3.88</v>
       </c>
       <c r="AA65">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AB65">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AC65">
-        <v>2.35</v>
+        <v>2.59</v>
       </c>
       <c r="AD65">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AE65">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AF65">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AG65">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="O66">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P66">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q66">
         <v>2.25</v>
       </c>
       <c r="R66">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="S66">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T66">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U66">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="V66">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="W66">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X66">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z66">
-        <v>3.88</v>
+        <v>5.19</v>
       </c>
       <c r="AA66">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="AB66">
-        <v>2.1</v>
+        <v>2.54</v>
       </c>
       <c r="AC66">
-        <v>2.59</v>
+        <v>2.19</v>
       </c>
       <c r="AD66">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AE66">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AF66">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AG66">
-        <v>2.1</v>
+        <v>2.43</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="O67">
+        <v>4.3</v>
+      </c>
+      <c r="P67">
         <v>3.75</v>
       </c>
-      <c r="P67">
-        <v>3.5</v>
-      </c>
       <c r="Q67">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="R67">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="S67">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T67">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="U67">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="V67">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="W67">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z67">
-        <v>5.19</v>
+        <v>6.5</v>
       </c>
       <c r="AA67">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AB67">
-        <v>2.54</v>
+        <v>2.97</v>
       </c>
       <c r="AC67">
-        <v>2.19</v>
+        <v>1.89</v>
       </c>
       <c r="AD67">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="AE67">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AF67">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AG67">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK67">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -14979,19 +14979,19 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O90">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P90">
         <v>3</v>
       </c>
       <c r="Q90">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="R90">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S90">
         <v>1.48</v>
@@ -15000,43 +15000,43 @@
         <v>2.48</v>
       </c>
       <c r="U90">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="V90">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W90">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X90">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y90">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Z90">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AA90">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AB90">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AC90">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AD90">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE90">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AF90">
         <v>2.05</v>
       </c>
       <c r="AG90">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>1.36</v>
       </c>
       <c r="AK90">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15148,7 +15148,7 @@
         <v>3.4</v>
       </c>
       <c r="P91">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q91">
         <v>4.45</v>
@@ -15160,10 +15160,10 @@
         <v>1.36</v>
       </c>
       <c r="T91">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="U91">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="V91">
         <v>1.4</v>
@@ -15172,7 +15172,7 @@
         <v>1.06</v>
       </c>
       <c r="X91">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y91">
         <v>1.27</v>
@@ -15196,10 +15196,10 @@
         <v>1.1</v>
       </c>
       <c r="AF91">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AG91">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK91">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15646,7 +15646,7 @@
         <v>2.33</v>
       </c>
       <c r="S94">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T94">
         <v>2.95</v>
@@ -15655,13 +15655,13 @@
         <v>2.6</v>
       </c>
       <c r="V94">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W94">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X94">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y94">
         <v>1.22</v>
@@ -15670,16 +15670,16 @@
         <v>3.69</v>
       </c>
       <c r="AA94">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AB94">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC94">
         <v>3.34</v>
       </c>
       <c r="AD94">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE94">
         <v>1.1</v>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK94">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AL94">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="O17">
         <v>3.1</v>
       </c>
       <c r="P17">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="Q17">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R17">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S17">
         <v>1.42</v>
       </c>
       <c r="T17">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U17">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V17">
         <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z17">
         <v>2.9</v>
       </c>
       <c r="AA17">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB17">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AC17">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AD17">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE17">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF17">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG17">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.61</v>
+        <v>2.55</v>
       </c>
       <c r="O21">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q21">
-        <v>2.16</v>
+        <v>3.2</v>
       </c>
       <c r="R21">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="S21">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="U21">
-        <v>2.31</v>
+        <v>2.46</v>
       </c>
       <c r="V21">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W21">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z21">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="AA21">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AB21">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC21">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AD21">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AE21">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF21">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AG21">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>2.06</v>
+        <v>1.37</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.55</v>
+        <v>1.61</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="P22">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="Q22">
-        <v>3.2</v>
+        <v>2.16</v>
       </c>
       <c r="R22">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T22">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="U22">
-        <v>2.46</v>
+        <v>2.31</v>
       </c>
       <c r="V22">
+        <v>1.5</v>
+      </c>
+      <c r="W22">
+        <v>1.1</v>
+      </c>
+      <c r="X22">
+        <v>1.01</v>
+      </c>
+      <c r="Y22">
+        <v>1.22</v>
+      </c>
+      <c r="Z22">
+        <v>4</v>
+      </c>
+      <c r="AA22">
+        <v>1.67</v>
+      </c>
+      <c r="AB22">
+        <v>2.2</v>
+      </c>
+      <c r="AC22">
+        <v>2.43</v>
+      </c>
+      <c r="AD22">
         <v>1.44</v>
       </c>
-      <c r="W22">
-        <v>1.12</v>
-      </c>
-      <c r="X22">
-        <v>1.03</v>
-      </c>
-      <c r="Y22">
-        <v>1.23</v>
-      </c>
-      <c r="Z22">
-        <v>3.45</v>
-      </c>
-      <c r="AA22">
-        <v>1.76</v>
-      </c>
-      <c r="AB22">
-        <v>2.1</v>
-      </c>
-      <c r="AC22">
-        <v>2.7</v>
-      </c>
-      <c r="AD22">
-        <v>1.32</v>
-      </c>
       <c r="AE22">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF22">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AG22">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK22">
-        <v>1.37</v>
+        <v>2.06</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="O27">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="P27">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4876,13 +4876,13 @@
         <v>1.27</v>
       </c>
       <c r="O28">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="P28">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="Q28">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R28">
         <v>2.24</v>
@@ -5036,61 +5036,61 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="O29">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P29">
-        <v>4.8</v>
+        <v>4.98</v>
       </c>
       <c r="Q29">
         <v>2.14</v>
       </c>
       <c r="R29">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="S29">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T29">
         <v>2.96</v>
       </c>
       <c r="U29">
-        <v>2.74</v>
+        <v>2.45</v>
       </c>
       <c r="V29">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
         <v>3.5</v>
       </c>
       <c r="AA29">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB29">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC29">
         <v>2.92</v>
       </c>
       <c r="AD29">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE29">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF29">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG29">
         <v>1.9</v>
@@ -5109,7 +5109,7 @@
         <v>1.17</v>
       </c>
       <c r="AK29">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5694,55 +5694,55 @@
         <v>3.5</v>
       </c>
       <c r="P33">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="Q33">
         <v>2.8</v>
       </c>
       <c r="R33">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="U33">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="V33">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W33">
         <v>1.06</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z33">
-        <v>3.88</v>
+        <v>3.95</v>
       </c>
       <c r="AA33">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB33">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AC33">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AD33">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE33">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF33">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG33">
         <v>2.25</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="O38">
         <v>3.2</v>
       </c>
       <c r="P38">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q38">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R38">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="S38">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T38">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="U38">
         <v>2.91</v>
       </c>
       <c r="V38">
+        <v>1.37</v>
+      </c>
+      <c r="W38">
+        <v>1.02</v>
+      </c>
+      <c r="X38">
+        <v>1.04</v>
+      </c>
+      <c r="Y38">
         <v>1.33</v>
       </c>
-      <c r="W38">
-        <v>1.05</v>
-      </c>
-      <c r="X38">
-        <v>1</v>
-      </c>
-      <c r="Y38">
-        <v>1.32</v>
-      </c>
       <c r="Z38">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="AA38">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB38">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AC38">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD38">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE38">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF38">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG38">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK38">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,49 +6666,49 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="O39">
         <v>3.2</v>
       </c>
       <c r="P39">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="Q39">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R39">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="S39">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T39">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="U39">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="V39">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W39">
+        <v>1.05</v>
+      </c>
+      <c r="X39">
         <v>1.02</v>
-      </c>
-      <c r="X39">
-        <v>1.04</v>
       </c>
       <c r="Y39">
         <v>1.33</v>
       </c>
       <c r="Z39">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA39">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB39">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC39">
         <v>3.5</v>
@@ -6720,10 +6720,10 @@
         <v>1.04</v>
       </c>
       <c r="AF39">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG39">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK39">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="O40">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P40">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="Q40">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="R40">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="S40">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T40">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="U40">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="V40">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="W40">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X40">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y40">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z40">
-        <v>3.27</v>
+        <v>2.74</v>
       </c>
       <c r="AA40">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AB40">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AC40">
-        <v>3.34</v>
+        <v>3.72</v>
       </c>
       <c r="AD40">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE40">
         <v>1.05</v>
       </c>
       <c r="AF40">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AG40">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="O41">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P41">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q41">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R41">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="S41">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T41">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="U41">
         <v>2.9</v>
       </c>
       <c r="V41">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W41">
+        <v>1.04</v>
+      </c>
+      <c r="X41">
+        <v>1.03</v>
+      </c>
+      <c r="Y41">
+        <v>1.32</v>
+      </c>
+      <c r="Z41">
+        <v>3.27</v>
+      </c>
+      <c r="AA41">
+        <v>2.07</v>
+      </c>
+      <c r="AB41">
+        <v>1.74</v>
+      </c>
+      <c r="AC41">
+        <v>3.34</v>
+      </c>
+      <c r="AD41">
+        <v>1.24</v>
+      </c>
+      <c r="AE41">
         <v>1.05</v>
-      </c>
-      <c r="X41">
-        <v>1.02</v>
-      </c>
-      <c r="Y41">
-        <v>1.33</v>
-      </c>
-      <c r="Z41">
-        <v>3.14</v>
-      </c>
-      <c r="AA41">
-        <v>2.04</v>
-      </c>
-      <c r="AB41">
-        <v>1.69</v>
-      </c>
-      <c r="AC41">
-        <v>3.5</v>
-      </c>
-      <c r="AD41">
-        <v>1.22</v>
-      </c>
-      <c r="AE41">
-        <v>1.04</v>
       </c>
       <c r="AF41">
         <v>1.78</v>
       </c>
       <c r="AG41">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK41">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="O42">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P42">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="Q42">
-        <v>2.99</v>
+        <v>2.56</v>
       </c>
       <c r="R42">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S42">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="T42">
-        <v>2.41</v>
+        <v>2.86</v>
       </c>
       <c r="U42">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="V42">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W42">
         <v>1.05</v>
       </c>
       <c r="X42">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z42">
-        <v>2.74</v>
+        <v>3.22</v>
       </c>
       <c r="AA42">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="AB42">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AC42">
-        <v>3.72</v>
+        <v>3.42</v>
       </c>
       <c r="AD42">
         <v>1.23</v>
       </c>
       <c r="AE42">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF42">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG42">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK42">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7810,10 +7810,10 @@
         <v>3.43</v>
       </c>
       <c r="O46">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="P46">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7973,10 +7973,10 @@
         <v>2.6</v>
       </c>
       <c r="O47">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="P47">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q47">
         <v>3.54</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK47">
         <v>1.38</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="O49">
-        <v>3.45</v>
+        <v>3.21</v>
       </c>
       <c r="P49">
-        <v>5.4</v>
+        <v>4.64</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="O53">
-        <v>12.6</v>
+        <v>11</v>
       </c>
       <c r="P53">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -9117,40 +9117,40 @@
         <v>3.7</v>
       </c>
       <c r="P54">
-        <v>3.11</v>
+        <v>3.55</v>
       </c>
       <c r="Q54">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="R54">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="S54">
         <v>1.25</v>
       </c>
       <c r="T54">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="U54">
         <v>2.24</v>
       </c>
       <c r="V54">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W54">
         <v>1.12</v>
       </c>
       <c r="X54">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
         <v>1.17</v>
       </c>
       <c r="Z54">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="AA54">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB54">
         <v>2.25</v>
@@ -9162,10 +9162,10 @@
         <v>1.5</v>
       </c>
       <c r="AE54">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF54">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG54">
         <v>2.45</v>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK54">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="O64">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="P64">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="Q64">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="R64">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="S64">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T64">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="U64">
-        <v>1.85</v>
+        <v>2.31</v>
       </c>
       <c r="V64">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="W64">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="X64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="Z64">
-        <v>6.3</v>
+        <v>4.65</v>
       </c>
       <c r="AA64">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AB64">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="AC64">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AD64">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AE64">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AF64">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG64">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK64">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="O65">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P65">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="Q65">
+        <v>2.25</v>
+      </c>
+      <c r="R65">
         <v>2.3</v>
       </c>
-      <c r="R65">
-        <v>2.32</v>
-      </c>
       <c r="S65">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T65">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="U65">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="V65">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W65">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X65">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z65">
-        <v>4.65</v>
+        <v>4.15</v>
       </c>
       <c r="AA65">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AB65">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AC65">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="AD65">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AE65">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF65">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG65">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="O66">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="P66">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="Q66">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="R66">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S66">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T66">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U66">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="V66">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="W66">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X66">
         <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z66">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="AA66">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="AB66">
-        <v>2.04</v>
+        <v>2.54</v>
       </c>
       <c r="AC66">
-        <v>2.59</v>
+        <v>2.21</v>
       </c>
       <c r="AD66">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="AE66">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AF66">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AG66">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="O67">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P67">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="Q67">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R67">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S67">
+        <v>1.18</v>
+      </c>
+      <c r="T67">
+        <v>4.33</v>
+      </c>
+      <c r="U67">
+        <v>1.86</v>
+      </c>
+      <c r="V67">
+        <v>1.85</v>
+      </c>
+      <c r="W67">
         <v>1.22</v>
-      </c>
-      <c r="T67">
-        <v>3.6</v>
-      </c>
-      <c r="U67">
-        <v>2.16</v>
-      </c>
-      <c r="V67">
-        <v>1.65</v>
-      </c>
-      <c r="W67">
-        <v>1.13</v>
       </c>
       <c r="X67">
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z67">
-        <v>5.26</v>
+        <v>6.3</v>
       </c>
       <c r="AA67">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="AB67">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="AC67">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="AD67">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AE67">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AF67">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG67">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK67">
-        <v>1.92</v>
+        <v>2.11</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="O68">
         <v>4.45</v>
       </c>
       <c r="P68">
-        <v>5.02</v>
+        <v>5.2</v>
       </c>
       <c r="Q68">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="R68">
         <v>2.5</v>
       </c>
       <c r="S68">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T68">
         <v>3.9</v>
       </c>
       <c r="U68">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="V68">
         <v>1.64</v>
       </c>
       <c r="W68">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z68">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AA68">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AB68">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="AC68">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AD68">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AE68">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF68">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG68">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK68">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,25 +11556,25 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="O69">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="P69">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="Q69">
         <v>1.92</v>
       </c>
       <c r="R69">
-        <v>2.47</v>
+        <v>2.69</v>
       </c>
       <c r="S69">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T69">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U69">
         <v>2.21</v>
@@ -11583,37 +11583,37 @@
         <v>1.61</v>
       </c>
       <c r="W69">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X69">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="Z69">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AA69">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB69">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="AC69">
-        <v>2.27</v>
+        <v>2.19</v>
       </c>
       <c r="AD69">
         <v>1.61</v>
       </c>
       <c r="AE69">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF69">
         <v>1.6</v>
       </c>
       <c r="AG69">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK69">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="O73">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P73">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q73">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="R73">
         <v>2.28</v>
       </c>
       <c r="S73">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T73">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="U73">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="V73">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W73">
         <v>1.1</v>
       </c>
       <c r="X73">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z73">
-        <v>4.38</v>
+        <v>4.63</v>
       </c>
       <c r="AA73">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AB73">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AC73">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AD73">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE73">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF73">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG73">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>1.8</v>
       </c>
       <c r="AK73">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12534,46 +12534,46 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="O75">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P75">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q75">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="R75">
-        <v>2.09</v>
+        <v>2.28</v>
       </c>
       <c r="S75">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="T75">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="U75">
         <v>2.74</v>
       </c>
       <c r="V75">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W75">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X75">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z75">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AA75">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB75">
         <v>1.83</v>
@@ -12582,16 +12582,16 @@
         <v>3.2</v>
       </c>
       <c r="AD75">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE75">
         <v>1.07</v>
       </c>
       <c r="AF75">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG75">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>1.29</v>
       </c>
       <c r="AK75">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,16 +12697,16 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="O76">
         <v>3.2</v>
       </c>
       <c r="P76">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="Q76">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="R76">
         <v>1.93</v>
@@ -12715,7 +12715,7 @@
         <v>1.48</v>
       </c>
       <c r="T76">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U76">
         <v>3.05</v>
@@ -12733,10 +12733,10 @@
         <v>1.33</v>
       </c>
       <c r="Z76">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AA76">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AB76">
         <v>1.67</v>
@@ -12745,16 +12745,16 @@
         <v>4.1</v>
       </c>
       <c r="AD76">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE76">
         <v>1.04</v>
       </c>
       <c r="AF76">
+        <v>1.8</v>
+      </c>
+      <c r="AG76">
         <v>1.85</v>
-      </c>
-      <c r="AG76">
-        <v>1.86</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>1.3</v>
       </c>
       <c r="AK76">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,80 +12860,80 @@
         </is>
       </c>
       <c r="N77">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O77">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="P77">
         <v>1.95</v>
       </c>
       <c r="Q77">
-        <v>3.93</v>
+        <v>3.58</v>
       </c>
       <c r="R77">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="S77">
+        <v>1.37</v>
+      </c>
+      <c r="T77">
+        <v>2.91</v>
+      </c>
+      <c r="U77">
+        <v>2.7</v>
+      </c>
+      <c r="V77">
         <v>1.38</v>
       </c>
-      <c r="T77">
-        <v>2.63</v>
-      </c>
-      <c r="U77">
-        <v>2.95</v>
-      </c>
-      <c r="V77">
-        <v>1.35</v>
-      </c>
       <c r="W77">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X77">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y77">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="Z77">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="AA77">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AB77">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AC77">
-        <v>3.94</v>
+        <v>3.49</v>
       </c>
       <c r="AD77">
+        <v>1.28</v>
+      </c>
+      <c r="AE77">
+        <v>1.1</v>
+      </c>
+      <c r="AF77">
+        <v>1.73</v>
+      </c>
+      <c r="AG77">
+        <v>1.92</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ77">
         <v>1.24</v>
       </c>
-      <c r="AE77">
-        <v>1.04</v>
-      </c>
-      <c r="AF77">
-        <v>1.82</v>
-      </c>
-      <c r="AG77">
-        <v>1.8</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ77">
-        <v>1.74</v>
-      </c>
       <c r="AK77">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="O78">
-        <v>3.12</v>
+        <v>3.03</v>
       </c>
       <c r="P78">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q78">
-        <v>3.58</v>
+        <v>2.82</v>
       </c>
       <c r="R78">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="S78">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T78">
-        <v>2.91</v>
+        <v>2.63</v>
       </c>
       <c r="U78">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="V78">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W78">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X78">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z78">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="AA78">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AB78">
-        <v>1.89</v>
+        <v>1.69</v>
       </c>
       <c r="AC78">
-        <v>3.49</v>
+        <v>3.75</v>
       </c>
       <c r="AD78">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE78">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF78">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AG78">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK78">
-        <v>1.23</v>
+        <v>1.68</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="O79">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="P79">
-        <v>4.5</v>
+        <v>5.55</v>
       </c>
       <c r="Q79">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="R79">
+        <v>2.38</v>
+      </c>
+      <c r="S79">
+        <v>1.3</v>
+      </c>
+      <c r="T79">
+        <v>3.3</v>
+      </c>
+      <c r="U79">
+        <v>2.36</v>
+      </c>
+      <c r="V79">
+        <v>1.5</v>
+      </c>
+      <c r="W79">
+        <v>1.08</v>
+      </c>
+      <c r="X79">
+        <v>1.04</v>
+      </c>
+      <c r="Y79">
+        <v>1.14</v>
+      </c>
+      <c r="Z79">
+        <v>4.4</v>
+      </c>
+      <c r="AA79">
+        <v>1.6</v>
+      </c>
+      <c r="AB79">
         <v>2.15</v>
       </c>
-      <c r="S79">
-        <v>1.36</v>
-      </c>
-      <c r="T79">
-        <v>2.89</v>
-      </c>
-      <c r="U79">
-        <v>2.75</v>
-      </c>
-      <c r="V79">
-        <v>1.4</v>
-      </c>
-      <c r="W79">
-        <v>1.05</v>
-      </c>
-      <c r="X79">
-        <v>1.05</v>
-      </c>
-      <c r="Y79">
-        <v>1.23</v>
-      </c>
-      <c r="Z79">
-        <v>3.5</v>
-      </c>
-      <c r="AA79">
-        <v>1.87</v>
-      </c>
-      <c r="AB79">
-        <v>1.9</v>
-      </c>
       <c r="AC79">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="AD79">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AE79">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AF79">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AG79">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,19 +13349,19 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="O80">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="P80">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q80">
-        <v>2.82</v>
+        <v>3.93</v>
       </c>
       <c r="R80">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="S80">
         <v>1.38</v>
@@ -13370,43 +13370,43 @@
         <v>2.63</v>
       </c>
       <c r="U80">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="V80">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W80">
         <v>1.07</v>
       </c>
       <c r="X80">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y80">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Z80">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="AA80">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB80">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC80">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="AD80">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE80">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF80">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AG80">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.3</v>
+        <v>1.74</v>
       </c>
       <c r="AK80">
-        <v>1.68</v>
+        <v>1.21</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,31 +13512,31 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.59</v>
+        <v>2.12</v>
       </c>
       <c r="O81">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P81">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q81">
-        <v>3.25</v>
+        <v>2.71</v>
       </c>
       <c r="R81">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S81">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T81">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="U81">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="V81">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W81">
         <v>1.06</v>
@@ -13545,31 +13545,31 @@
         <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z81">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AA81">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AB81">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AC81">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AD81">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE81">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF81">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG81">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AK81">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,58 +13675,58 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.53</v>
+        <v>2.59</v>
       </c>
       <c r="O82">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="P82">
-        <v>5.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q82">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="R82">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="S82">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T82">
+        <v>2.85</v>
+      </c>
+      <c r="U82">
+        <v>2.95</v>
+      </c>
+      <c r="V82">
+        <v>1.4</v>
+      </c>
+      <c r="W82">
+        <v>1.06</v>
+      </c>
+      <c r="X82">
+        <v>1.01</v>
+      </c>
+      <c r="Y82">
+        <v>1.25</v>
+      </c>
+      <c r="Z82">
         <v>3.3</v>
       </c>
-      <c r="U82">
-        <v>2.36</v>
-      </c>
-      <c r="V82">
-        <v>1.5</v>
-      </c>
-      <c r="W82">
-        <v>1.08</v>
-      </c>
-      <c r="X82">
-        <v>1.04</v>
-      </c>
-      <c r="Y82">
-        <v>1.14</v>
-      </c>
-      <c r="Z82">
-        <v>4.4</v>
-      </c>
       <c r="AA82">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="AB82">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AC82">
-        <v>2.45</v>
+        <v>3.05</v>
       </c>
       <c r="AD82">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="AE82">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF82">
         <v>1.68</v>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AK82">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.12</v>
+        <v>1.71</v>
       </c>
       <c r="O83">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P83">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q83">
-        <v>2.71</v>
+        <v>2.31</v>
       </c>
       <c r="R83">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S83">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T83">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="U83">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V83">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W83">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y83">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z83">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA83">
+        <v>1.87</v>
+      </c>
+      <c r="AB83">
+        <v>1.9</v>
+      </c>
+      <c r="AC83">
+        <v>3.25</v>
+      </c>
+      <c r="AD83">
+        <v>1.33</v>
+      </c>
+      <c r="AE83">
+        <v>1.08</v>
+      </c>
+      <c r="AF83">
         <v>1.78</v>
       </c>
-      <c r="AB83">
-        <v>1.95</v>
-      </c>
-      <c r="AC83">
-        <v>3.1</v>
-      </c>
-      <c r="AD83">
-        <v>1.36</v>
-      </c>
-      <c r="AE83">
-        <v>1.14</v>
-      </c>
-      <c r="AF83">
-        <v>1.62</v>
-      </c>
       <c r="AG83">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15148,58 +15148,58 @@
         <v>3</v>
       </c>
       <c r="P91">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="Q91">
+        <v>3.1</v>
+      </c>
+      <c r="R91">
+        <v>1.89</v>
+      </c>
+      <c r="S91">
+        <v>1.49</v>
+      </c>
+      <c r="T91">
+        <v>2.6</v>
+      </c>
+      <c r="U91">
         <v>3.2</v>
       </c>
-      <c r="R91">
-        <v>1.94</v>
-      </c>
-      <c r="S91">
-        <v>1.45</v>
-      </c>
-      <c r="T91">
-        <v>2.44</v>
-      </c>
-      <c r="U91">
-        <v>3.14</v>
-      </c>
       <c r="V91">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W91">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X91">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y91">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z91">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="AA91">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AB91">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AC91">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD91">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE91">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF91">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG91">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK91">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AL91">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -644,10 +644,10 @@
         <v>2.72</v>
       </c>
       <c r="Q2">
-        <v>2.9</v>
+        <v>2.54</v>
       </c>
       <c r="R2">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="S2">
         <v>1.33</v>
@@ -662,7 +662,7 @@
         <v>1.41</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X2">
         <v>1.04</v>
@@ -671,28 +671,28 @@
         <v>1.19</v>
       </c>
       <c r="Z2">
-        <v>3.65</v>
+        <v>3.74</v>
       </c>
       <c r="AA2">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB2">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AC2">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="AD2">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE2">
         <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG2">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.4</v>
       </c>
       <c r="AK2">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O3">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q3">
         <v>4.5</v>
       </c>
       <c r="R3">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S3">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T3">
         <v>2.6</v>
       </c>
       <c r="U3">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="V3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
         <v>1.02</v>
@@ -834,28 +834,28 @@
         <v>1.4</v>
       </c>
       <c r="Z3">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="AA3">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AB3">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC3">
-        <v>4.2</v>
+        <v>4.71</v>
       </c>
       <c r="AD3">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AG3">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.32</v>
       </c>
       <c r="AK3">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="O4">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="P4">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="R4">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="S4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T4">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U4">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="V4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W4">
         <v>1.11</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z4">
-        <v>3.88</v>
+        <v>4.33</v>
       </c>
       <c r="AA4">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB4">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AC4">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AD4">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE4">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF4">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG4">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK4">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1127,28 +1127,28 @@
         <v>1.4</v>
       </c>
       <c r="O5">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="P5">
-        <v>4.5</v>
+        <v>5.13</v>
       </c>
       <c r="Q5">
         <v>1.83</v>
       </c>
       <c r="R5">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="S5">
         <v>1.18</v>
       </c>
       <c r="T5">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U5">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V5">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W5">
         <v>1.19</v>
@@ -1157,10 +1157,10 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z5">
-        <v>6.65</v>
+        <v>6.82</v>
       </c>
       <c r="AA5">
         <v>1.33</v>
@@ -1169,16 +1169,16 @@
         <v>3.1</v>
       </c>
       <c r="AC5">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AD5">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AE5">
         <v>1.33</v>
       </c>
       <c r="AF5">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG5">
         <v>2.45</v>
@@ -1197,7 +1197,7 @@
         <v>1.14</v>
       </c>
       <c r="AK5">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,34 +1287,34 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O6">
         <v>3.5</v>
       </c>
       <c r="P6">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q6">
-        <v>3.87</v>
+        <v>3.3</v>
       </c>
       <c r="R6">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="S6">
         <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.8</v>
+        <v>3.36</v>
       </c>
       <c r="U6">
         <v>2.25</v>
       </c>
       <c r="V6">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
         <v>1.01</v>
@@ -1323,16 +1323,16 @@
         <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="AA6">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB6">
         <v>2.3</v>
       </c>
       <c r="AC6">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AD6">
         <v>1.53</v>
@@ -1344,7 +1344,7 @@
         <v>1.45</v>
       </c>
       <c r="AG6">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O7">
-        <v>3.17</v>
+        <v>3.35</v>
       </c>
       <c r="P7">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q7">
         <v>2.63</v>
@@ -1468,7 +1468,7 @@
         <v>1.38</v>
       </c>
       <c r="T7">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="U7">
         <v>2.81</v>
@@ -1477,10 +1477,10 @@
         <v>1.37</v>
       </c>
       <c r="W7">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
         <v>1.25</v>
@@ -1492,22 +1492,22 @@
         <v>1.95</v>
       </c>
       <c r="AB7">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC7">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AD7">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE7">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF7">
         <v>1.75</v>
       </c>
       <c r="AG7">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1613,61 +1613,61 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O8">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="P8">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="Q8">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R8">
-        <v>2.53</v>
+        <v>2.32</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T8">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="U8">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V8">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W8">
         <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>4.33</v>
+        <v>3.84</v>
       </c>
       <c r="AA8">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB8">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC8">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="AD8">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE8">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF8">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AG8">
         <v>1.8</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AK8">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="O9">
         <v>3.58</v>
@@ -1785,10 +1785,10 @@
         <v>2</v>
       </c>
       <c r="Q9">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="R9">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="S9">
         <v>1.35</v>
@@ -1797,7 +1797,7 @@
         <v>3.08</v>
       </c>
       <c r="U9">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
       <c r="V9">
         <v>1.49</v>
@@ -1812,28 +1812,28 @@
         <v>1.23</v>
       </c>
       <c r="Z9">
-        <v>3.78</v>
+        <v>4.21</v>
       </c>
       <c r="AA9">
         <v>1.75</v>
       </c>
       <c r="AB9">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AC9">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="AD9">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE9">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF9">
         <v>1.6</v>
       </c>
       <c r="AG9">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="AK9">
         <v>1.36</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="O11">
         <v>3.3</v>
       </c>
       <c r="P11">
-        <v>4.5</v>
+        <v>4.89</v>
       </c>
       <c r="Q11">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="R11">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="S11">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T11">
-        <v>2.36</v>
+        <v>2.75</v>
       </c>
       <c r="U11">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="V11">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z11">
-        <v>2.69</v>
+        <v>2.97</v>
       </c>
       <c r="AA11">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB11">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC11">
-        <v>4.15</v>
+        <v>3.54</v>
       </c>
       <c r="AD11">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AE11">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AF11">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AG11">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,10 +2268,10 @@
         <v>2.38</v>
       </c>
       <c r="O12">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P12">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="Q12">
         <v>3.35</v>
@@ -2280,10 +2280,10 @@
         <v>1.82</v>
       </c>
       <c r="S12">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T12">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="U12">
         <v>3.44</v>
@@ -2298,19 +2298,19 @@
         <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z12">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="AA12">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="AB12">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AC12">
-        <v>4.55</v>
+        <v>4.86</v>
       </c>
       <c r="AD12">
         <v>1.13</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AK12">
         <v>1.48</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="O14">
         <v>3.15</v>
@@ -2606,49 +2606,49 @@
         <v>1.87</v>
       </c>
       <c r="S14">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T14">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U14">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="V14">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z14">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="AA14">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB14">
         <v>1.6</v>
       </c>
       <c r="AC14">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AD14">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF14">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG14">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.28</v>
       </c>
       <c r="AK14">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,22 +2763,22 @@
         <v>4.74</v>
       </c>
       <c r="Q15">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="R15">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S15">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T15">
         <v>2.75</v>
       </c>
       <c r="U15">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="V15">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W15">
         <v>1.05</v>
@@ -2787,31 +2787,31 @@
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z15">
-        <v>2.73</v>
+        <v>2.81</v>
       </c>
       <c r="AA15">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AB15">
         <v>1.62</v>
       </c>
       <c r="AC15">
-        <v>3.96</v>
+        <v>3.82</v>
       </c>
       <c r="AD15">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE15">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AG15">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AK15">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O16">
         <v>3.4</v>
@@ -2929,7 +2929,7 @@
         <v>3</v>
       </c>
       <c r="R16">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="S16">
         <v>1.33</v>
@@ -2938,43 +2938,43 @@
         <v>3.2</v>
       </c>
       <c r="U16">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z16">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="AA16">
         <v>1.72</v>
       </c>
       <c r="AB16">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AC16">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD16">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE16">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AG16">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O18">
         <v>3.7</v>
       </c>
       <c r="P18">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q18">
         <v>2.25</v>
       </c>
       <c r="R18">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="S18">
         <v>1.22</v>
@@ -3264,31 +3264,31 @@
         <v>3.75</v>
       </c>
       <c r="U18">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="V18">
         <v>1.62</v>
       </c>
       <c r="W18">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
         <v>1.14</v>
       </c>
       <c r="Z18">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA18">
         <v>1.46</v>
       </c>
       <c r="AB18">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AC18">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AD18">
         <v>1.58</v>
@@ -3300,7 +3300,7 @@
         <v>1.48</v>
       </c>
       <c r="AG18">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.17</v>
       </c>
       <c r="AK18">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>29.12</v>
+        <v>20.36</v>
       </c>
       <c r="O19">
-        <v>11</v>
+        <v>12.7</v>
       </c>
       <c r="P19">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3575,10 +3575,10 @@
         <v>3.8</v>
       </c>
       <c r="P20">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q20">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R20">
         <v>2.6</v>
@@ -3587,7 +3587,7 @@
         <v>1.17</v>
       </c>
       <c r="T20">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="U20">
         <v>1.98</v>
@@ -3596,7 +3596,7 @@
         <v>1.73</v>
       </c>
       <c r="W20">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3608,25 +3608,25 @@
         <v>6.05</v>
       </c>
       <c r="AA20">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB20">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC20">
+        <v>1.85</v>
+      </c>
+      <c r="AD20">
         <v>1.9</v>
-      </c>
-      <c r="AD20">
-        <v>1.79</v>
       </c>
       <c r="AE20">
         <v>1.3</v>
       </c>
       <c r="AF20">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AG20">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.55</v>
+        <v>1.61</v>
       </c>
       <c r="O21">
+        <v>3.75</v>
+      </c>
+      <c r="P21">
+        <v>4.25</v>
+      </c>
+      <c r="Q21">
+        <v>2.1</v>
+      </c>
+      <c r="R21">
+        <v>2.3</v>
+      </c>
+      <c r="S21">
+        <v>1.25</v>
+      </c>
+      <c r="T21">
         <v>3.4</v>
       </c>
-      <c r="P21">
-        <v>2.3</v>
-      </c>
-      <c r="Q21">
-        <v>3.2</v>
-      </c>
-      <c r="R21">
-        <v>2.17</v>
-      </c>
-      <c r="S21">
-        <v>1.3</v>
-      </c>
-      <c r="T21">
-        <v>3.04</v>
-      </c>
       <c r="U21">
-        <v>2.46</v>
+        <v>2.31</v>
       </c>
       <c r="V21">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W21">
         <v>1.12</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z21">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="AA21">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AB21">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AC21">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD21">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE21">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF21">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG21">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.37</v>
+        <v>2.15</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="O22">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q22">
-        <v>2.16</v>
+        <v>3.2</v>
       </c>
       <c r="R22">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="U22">
-        <v>2.31</v>
+        <v>2.46</v>
       </c>
       <c r="V22">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z22">
         <v>4</v>
       </c>
       <c r="AA22">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB22">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AC22">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="AD22">
+        <v>1.32</v>
+      </c>
+      <c r="AE22">
+        <v>1.11</v>
+      </c>
+      <c r="AF22">
+        <v>1.57</v>
+      </c>
+      <c r="AG22">
+        <v>2.25</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>1.3</v>
+      </c>
+      <c r="AK22">
         <v>1.44</v>
-      </c>
-      <c r="AE22">
-        <v>1.2</v>
-      </c>
-      <c r="AF22">
-        <v>1.61</v>
-      </c>
-      <c r="AG22">
-        <v>2.15</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.18</v>
-      </c>
-      <c r="AK22">
-        <v>2.06</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,16 +4058,16 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O23">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="P23">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="Q23">
-        <v>3.92</v>
+        <v>3.97</v>
       </c>
       <c r="R23">
         <v>1.84</v>
@@ -4091,19 +4091,19 @@
         <v>1.06</v>
       </c>
       <c r="Y23">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="Z23">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AA23">
         <v>2.46</v>
       </c>
       <c r="AB23">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AC23">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AD23">
         <v>1.18</v>
@@ -4115,7 +4115,7 @@
         <v>1.99</v>
       </c>
       <c r="AG23">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AK23">
         <v>1.34</v>
@@ -4224,22 +4224,22 @@
         <v>2.16</v>
       </c>
       <c r="O24">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
       </c>
       <c r="R24">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="S24">
         <v>1.25</v>
       </c>
       <c r="T24">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U24">
         <v>2.25</v>
@@ -4263,16 +4263,16 @@
         <v>1.57</v>
       </c>
       <c r="AB24">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AC24">
         <v>2.55</v>
       </c>
       <c r="AD24">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE24">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF24">
         <v>1.5</v>
@@ -4294,7 +4294,7 @@
         <v>1.36</v>
       </c>
       <c r="AK24">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G25">
@@ -4387,61 +4387,61 @@
         <v>2.3</v>
       </c>
       <c r="O25">
-        <v>3.18</v>
+        <v>3.37</v>
       </c>
       <c r="P25">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="Q25">
+        <v>2.9</v>
+      </c>
+      <c r="R25">
+        <v>2.17</v>
+      </c>
+      <c r="S25">
+        <v>1.35</v>
+      </c>
+      <c r="T25">
         <v>2.95</v>
       </c>
-      <c r="R25">
-        <v>2.05</v>
-      </c>
-      <c r="S25">
-        <v>1.33</v>
-      </c>
-      <c r="T25">
-        <v>2.72</v>
-      </c>
       <c r="U25">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="V25">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z25">
-        <v>3.6</v>
+        <v>4.08</v>
       </c>
       <c r="AA25">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AB25">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AC25">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="AD25">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AE25">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AF25">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AG25">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AK25">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O26">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P26">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="Q26">
         <v>2.9</v>
       </c>
       <c r="R26">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S26">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
-        <v>2.99</v>
+        <v>2.71</v>
       </c>
       <c r="U26">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="V26">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
         <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z26">
-        <v>3.85</v>
+        <v>3.38</v>
       </c>
       <c r="AA26">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="AB26">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC26">
-        <v>2.72</v>
+        <v>2.99</v>
       </c>
       <c r="AD26">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE26">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AK26">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="O30">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P30">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q30">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="R30">
         <v>2</v>
       </c>
       <c r="S30">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T30">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="U30">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="V30">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W30">
+        <v>1.02</v>
+      </c>
+      <c r="X30">
+        <v>1.05</v>
+      </c>
+      <c r="Y30">
+        <v>1.4</v>
+      </c>
+      <c r="Z30">
+        <v>2.88</v>
+      </c>
+      <c r="AA30">
+        <v>2.2</v>
+      </c>
+      <c r="AB30">
+        <v>1.61</v>
+      </c>
+      <c r="AC30">
+        <v>4.2</v>
+      </c>
+      <c r="AD30">
+        <v>1.18</v>
+      </c>
+      <c r="AE30">
         <v>1.06</v>
       </c>
-      <c r="X30">
-        <v>1.03</v>
-      </c>
-      <c r="Y30">
-        <v>1.35</v>
-      </c>
-      <c r="Z30">
-        <v>2.74</v>
-      </c>
-      <c r="AA30">
-        <v>2.21</v>
-      </c>
-      <c r="AB30">
-        <v>1.63</v>
-      </c>
-      <c r="AC30">
-        <v>3.94</v>
-      </c>
-      <c r="AD30">
-        <v>1.22</v>
-      </c>
-      <c r="AE30">
-        <v>1.02</v>
-      </c>
       <c r="AF30">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG30">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK30">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5365,10 +5365,10 @@
         <v>2.25</v>
       </c>
       <c r="O31">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="Q31">
         <v>2.69</v>
@@ -5377,7 +5377,7 @@
         <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T31">
         <v>3.1</v>
@@ -5389,7 +5389,7 @@
         <v>1.5</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X31">
         <v>1.02</v>
@@ -5398,19 +5398,19 @@
         <v>1.2</v>
       </c>
       <c r="Z31">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA31">
         <v>1.67</v>
       </c>
       <c r="AB31">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AC31">
         <v>2.56</v>
       </c>
       <c r="AD31">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE31">
         <v>1.15</v>
@@ -5435,7 +5435,7 @@
         <v>1.44</v>
       </c>
       <c r="AK31">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P32">
         <v>3.1</v>
@@ -5537,49 +5537,49 @@
         <v>2.57</v>
       </c>
       <c r="R32">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="S32">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T32">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
         <v>2.3</v>
       </c>
       <c r="V32">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W32">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
+        <v>1.17</v>
+      </c>
+      <c r="Z32">
+        <v>4.4</v>
+      </c>
+      <c r="AA32">
+        <v>1.61</v>
+      </c>
+      <c r="AB32">
+        <v>2.14</v>
+      </c>
+      <c r="AC32">
+        <v>2.5</v>
+      </c>
+      <c r="AD32">
+        <v>1.47</v>
+      </c>
+      <c r="AE32">
         <v>1.16</v>
       </c>
-      <c r="Z32">
-        <v>4.1</v>
-      </c>
-      <c r="AA32">
-        <v>1.66</v>
-      </c>
-      <c r="AB32">
-        <v>2.16</v>
-      </c>
-      <c r="AC32">
-        <v>2.61</v>
-      </c>
-      <c r="AD32">
-        <v>1.42</v>
-      </c>
-      <c r="AE32">
-        <v>1.13</v>
-      </c>
       <c r="AF32">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG32">
         <v>2.28</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AK32">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="O34">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q34">
         <v>2.88</v>
@@ -5869,7 +5869,7 @@
         <v>1.22</v>
       </c>
       <c r="T34">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="U34">
         <v>2.05</v>
@@ -5878,37 +5878,37 @@
         <v>1.67</v>
       </c>
       <c r="W34">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
         <v>1.1</v>
       </c>
       <c r="Z34">
-        <v>5.15</v>
+        <v>5.05</v>
       </c>
       <c r="AA34">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB34">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AC34">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AD34">
         <v>1.65</v>
       </c>
       <c r="AE34">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF34">
         <v>1.38</v>
       </c>
       <c r="AG34">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AK34">
         <v>1.5</v>
@@ -6014,37 +6014,37 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="O35">
-        <v>3.27</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q35">
-        <v>3.76</v>
+        <v>2.77</v>
       </c>
       <c r="R35">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="S35">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T35">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U35">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="V35">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="W35">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
         <v>1.15</v>
@@ -6053,25 +6053,25 @@
         <v>4.2</v>
       </c>
       <c r="AA35">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="AB35">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="AC35">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="AD35">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AE35">
         <v>1.19</v>
       </c>
       <c r="AF35">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG35">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AK35">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6183,10 +6183,10 @@
         <v>3.6</v>
       </c>
       <c r="P36">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q36">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R36">
         <v>2.25</v>
@@ -6195,40 +6195,40 @@
         <v>1.32</v>
       </c>
       <c r="T36">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U36">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V36">
         <v>1.49</v>
       </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
         <v>1.05</v>
       </c>
       <c r="Y36">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z36">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AA36">
         <v>1.73</v>
       </c>
       <c r="AB36">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC36">
         <v>2.64</v>
       </c>
       <c r="AD36">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE36">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF36">
         <v>1.62</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="O37">
         <v>3.1</v>
       </c>
       <c r="P37">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="Q37">
+        <v>2.8</v>
+      </c>
+      <c r="R37">
+        <v>1.99</v>
+      </c>
+      <c r="S37">
+        <v>1.42</v>
+      </c>
+      <c r="T37">
+        <v>2.56</v>
+      </c>
+      <c r="U37">
+        <v>2.96</v>
+      </c>
+      <c r="V37">
+        <v>1.32</v>
+      </c>
+      <c r="W37">
+        <v>1.06</v>
+      </c>
+      <c r="X37">
+        <v>1.02</v>
+      </c>
+      <c r="Y37">
+        <v>1.33</v>
+      </c>
+      <c r="Z37">
         <v>2.97</v>
       </c>
-      <c r="R37">
+      <c r="AA37">
         <v>2.1</v>
       </c>
-      <c r="S37">
-        <v>1.43</v>
-      </c>
-      <c r="T37">
-        <v>2.9</v>
-      </c>
-      <c r="U37">
-        <v>2.98</v>
-      </c>
-      <c r="V37">
-        <v>1.37</v>
-      </c>
-      <c r="W37">
-        <v>1.04</v>
-      </c>
-      <c r="X37">
-        <v>1.03</v>
-      </c>
-      <c r="Y37">
-        <v>1.3</v>
-      </c>
-      <c r="Z37">
-        <v>3.05</v>
-      </c>
-      <c r="AA37">
-        <v>1.93</v>
-      </c>
       <c r="AB37">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AC37">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="AD37">
         <v>1.25</v>
       </c>
       <c r="AE37">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF37">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG37">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK37">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="O38">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P38">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="Q38">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="R38">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="S38">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="T38">
-        <v>2.8</v>
+        <v>2.41</v>
       </c>
       <c r="U38">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="V38">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W38">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X38">
         <v>1.04</v>
       </c>
       <c r="Y38">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z38">
-        <v>3.08</v>
+        <v>2.74</v>
       </c>
       <c r="AA38">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AB38">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AC38">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="AD38">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE38">
         <v>1.04</v>
       </c>
       <c r="AF38">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG38">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="O39">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P39">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="Q39">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R39">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
         <v>1.43</v>
@@ -6687,37 +6687,37 @@
         <v>2.53</v>
       </c>
       <c r="U39">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="V39">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W39">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z39">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA39">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="AB39">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AC39">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD39">
         <v>1.22</v>
       </c>
       <c r="AE39">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
         <v>1.78</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK39">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O40">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P40">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="Q40">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="R40">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S40">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T40">
-        <v>2.41</v>
+        <v>3.05</v>
       </c>
       <c r="U40">
+        <v>2.6</v>
+      </c>
+      <c r="V40">
+        <v>1.42</v>
+      </c>
+      <c r="W40">
+        <v>1.04</v>
+      </c>
+      <c r="X40">
+        <v>1.01</v>
+      </c>
+      <c r="Y40">
+        <v>1.24</v>
+      </c>
+      <c r="Z40">
+        <v>3.35</v>
+      </c>
+      <c r="AA40">
+        <v>1.86</v>
+      </c>
+      <c r="AB40">
+        <v>1.9</v>
+      </c>
+      <c r="AC40">
         <v>3.3</v>
       </c>
-      <c r="V40">
+      <c r="AD40">
         <v>1.29</v>
       </c>
-      <c r="W40">
-        <v>1.05</v>
-      </c>
-      <c r="X40">
-        <v>1.05</v>
-      </c>
-      <c r="Y40">
-        <v>1.35</v>
-      </c>
-      <c r="Z40">
-        <v>2.74</v>
-      </c>
-      <c r="AA40">
-        <v>2.14</v>
-      </c>
-      <c r="AB40">
-        <v>1.66</v>
-      </c>
-      <c r="AC40">
-        <v>3.72</v>
-      </c>
-      <c r="AD40">
-        <v>1.23</v>
-      </c>
       <c r="AE40">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF40">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AG40">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK40">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O41">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="P41">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q41">
         <v>2.9</v>
       </c>
       <c r="R41">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="S41">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T41">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="U41">
-        <v>2.9</v>
+        <v>3.06</v>
       </c>
       <c r="V41">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W41">
         <v>1.04</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y41">
         <v>1.32</v>
       </c>
       <c r="Z41">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="AA41">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AB41">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AC41">
-        <v>3.34</v>
+        <v>3.9</v>
       </c>
       <c r="AD41">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE41">
         <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG41">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
         <v>1.43</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,58 +7155,58 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O42">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P42">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q42">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="R42">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="S42">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T42">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="U42">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="V42">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W42">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z42">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="AA42">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AB42">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AC42">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AD42">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE42">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF42">
         <v>1.8</v>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK42">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="O43">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P43">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q43">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="R43">
         <v>2.1</v>
       </c>
       <c r="S43">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T43">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="U43">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="V43">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W43">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z43">
-        <v>3.63</v>
+        <v>3.25</v>
       </c>
       <c r="AA43">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AB43">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC43">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AD43">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE43">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF43">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AG43">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.37</v>
+        <v>1.99</v>
       </c>
       <c r="O44">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P44">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q44">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R44">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="S44">
         <v>1.4</v>
       </c>
       <c r="T44">
-        <v>2.81</v>
+        <v>2.86</v>
       </c>
       <c r="U44">
-        <v>2.97</v>
+        <v>3.06</v>
       </c>
       <c r="V44">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
+        <v>1.05</v>
+      </c>
+      <c r="X44">
+        <v>1.01</v>
+      </c>
+      <c r="Y44">
+        <v>1.33</v>
+      </c>
+      <c r="Z44">
+        <v>3.08</v>
+      </c>
+      <c r="AA44">
+        <v>2</v>
+      </c>
+      <c r="AB44">
+        <v>1.69</v>
+      </c>
+      <c r="AC44">
+        <v>3.9</v>
+      </c>
+      <c r="AD44">
+        <v>1.27</v>
+      </c>
+      <c r="AE44">
         <v>1.04</v>
       </c>
-      <c r="X44">
-        <v>1.04</v>
-      </c>
-      <c r="Y44">
-        <v>1.31</v>
-      </c>
-      <c r="Z44">
-        <v>2.92</v>
-      </c>
-      <c r="AA44">
-        <v>2.09</v>
-      </c>
-      <c r="AB44">
-        <v>1.72</v>
-      </c>
-      <c r="AC44">
-        <v>3.5</v>
-      </c>
-      <c r="AD44">
-        <v>1.26</v>
-      </c>
-      <c r="AE44">
-        <v>1.05</v>
-      </c>
       <c r="AF44">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AG44">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.45</v>
+        <v>1.69</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="O45">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P45">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q45">
-        <v>2.48</v>
+        <v>3.1</v>
       </c>
       <c r="R45">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S45">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T45">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="U45">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V45">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W45">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z45">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AA45">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AB45">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AC45">
-        <v>3.28</v>
+        <v>3.69</v>
       </c>
       <c r="AD45">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE45">
         <v>1.06</v>
       </c>
       <c r="AF45">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AG45">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AK45">
-        <v>1.84</v>
+        <v>1.4</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O48">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P48">
-        <v>3.45</v>
+        <v>2.92</v>
       </c>
       <c r="Q48">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="R48">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="S48">
         <v>1.3</v>
@@ -8154,10 +8154,10 @@
         <v>3.22</v>
       </c>
       <c r="U48">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="V48">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W48">
         <v>1.12</v>
@@ -8169,28 +8169,28 @@
         <v>1.2</v>
       </c>
       <c r="Z48">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA48">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB48">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AC48">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AD48">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF48">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AG48">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK48">
         <v>1.73</v>
@@ -8459,61 +8459,61 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O50">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="P50">
-        <v>3.75</v>
+        <v>4.62</v>
       </c>
       <c r="Q50">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R50">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="S50">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="T50">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="U50">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="V50">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W50">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X50">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Y50">
         <v>1.53</v>
       </c>
       <c r="Z50">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA50">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AB50">
         <v>1.44</v>
       </c>
       <c r="AC50">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AD50">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE50">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF50">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG50">
         <v>1.62</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AK50">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,43 +8622,43 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O51">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P51">
-        <v>5.67</v>
+        <v>6.11</v>
       </c>
       <c r="Q51">
         <v>2</v>
       </c>
       <c r="R51">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
         <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U51">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V51">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W51">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z51">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="AA51">
         <v>1.72</v>
@@ -8667,16 +8667,16 @@
         <v>2.1</v>
       </c>
       <c r="AC51">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD51">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE51">
         <v>1.15</v>
       </c>
       <c r="AF51">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG51">
         <v>1.93</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AK51">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9274,25 +9274,25 @@
         </is>
       </c>
       <c r="N55">
-        <v>3.46</v>
+        <v>3.7</v>
       </c>
       <c r="O55">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="P55">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Q55">
-        <v>4.2</v>
+        <v>4.65</v>
       </c>
       <c r="R55">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="S55">
         <v>1.64</v>
       </c>
       <c r="T55">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="U55">
         <v>3.96</v>
@@ -9307,19 +9307,19 @@
         <v>1.12</v>
       </c>
       <c r="Y55">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z55">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AA55">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="AB55">
         <v>1.4</v>
       </c>
       <c r="AC55">
-        <v>6.16</v>
+        <v>7</v>
       </c>
       <c r="AD55">
         <v>1.07</v>
@@ -9328,7 +9328,7 @@
         <v>1.03</v>
       </c>
       <c r="AF55">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG55">
         <v>1.6</v>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AK55">
         <v>1.25</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="O56">
-        <v>9.75</v>
+        <v>8.5</v>
       </c>
       <c r="P56">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Q56">
         <v>1.36</v>
       </c>
       <c r="R56">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="S56">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="T56">
         <v>5</v>
       </c>
       <c r="U56">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V56">
         <v>1.96</v>
       </c>
       <c r="W56">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X56">
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z56">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA56">
         <v>1.3</v>
       </c>
       <c r="AB56">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AC56">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AD56">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AE56">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AF56">
         <v>2.1</v>
       </c>
       <c r="AG56">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK56">
         <v>6.45</v>
@@ -9600,7 +9600,7 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="O57">
         <v>3.4</v>
@@ -9621,7 +9621,7 @@
         <v>3.32</v>
       </c>
       <c r="U57">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="V57">
         <v>1.5</v>
@@ -9630,7 +9630,7 @@
         <v>1.13</v>
       </c>
       <c r="X57">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y57">
         <v>1.2</v>
@@ -9639,25 +9639,25 @@
         <v>4.25</v>
       </c>
       <c r="AA57">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB57">
         <v>2.1</v>
       </c>
       <c r="AC57">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AD57">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE57">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF57">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG57">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9766,16 +9766,16 @@
         <v>2.45</v>
       </c>
       <c r="O58">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P58">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="Q58">
         <v>2.91</v>
       </c>
       <c r="R58">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S58">
         <v>1.26</v>
@@ -9793,13 +9793,13 @@
         <v>1.11</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z58">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA58">
         <v>1.54</v>
@@ -9811,13 +9811,13 @@
         <v>2.41</v>
       </c>
       <c r="AD58">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AE58">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AF58">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AG58">
         <v>2.45</v>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="AK58">
         <v>1.42</v>
@@ -9938,13 +9938,13 @@
         <v>2.26</v>
       </c>
       <c r="R59">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S59">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T59">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U59">
         <v>3.3</v>
@@ -9959,19 +9959,19 @@
         <v>1.05</v>
       </c>
       <c r="Y59">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z59">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="AA59">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AB59">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC59">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AD59">
         <v>1.17</v>
@@ -9980,10 +9980,10 @@
         <v>1.03</v>
       </c>
       <c r="AF59">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AG59">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10095,7 +10095,7 @@
         <v>2.95</v>
       </c>
       <c r="P60">
-        <v>3.59</v>
+        <v>3.55</v>
       </c>
       <c r="Q60">
         <v>2.72</v>
@@ -10116,10 +10116,10 @@
         <v>1.28</v>
       </c>
       <c r="W60">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X60">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y60">
         <v>1.36</v>
@@ -10128,25 +10128,25 @@
         <v>2.88</v>
       </c>
       <c r="AA60">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AB60">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AC60">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD60">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE60">
         <v>1.03</v>
       </c>
       <c r="AF60">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG60">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10255,16 +10255,16 @@
         <v>1.4</v>
       </c>
       <c r="O61">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P61">
-        <v>5.92</v>
+        <v>6</v>
       </c>
       <c r="Q61">
         <v>2</v>
       </c>
       <c r="R61">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="S61">
         <v>1.29</v>
@@ -10279,7 +10279,7 @@
         <v>1.5</v>
       </c>
       <c r="W61">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X61">
         <v>1.01</v>
@@ -10288,28 +10288,28 @@
         <v>1.17</v>
       </c>
       <c r="Z61">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA61">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AB61">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AC61">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AD61">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE61">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF61">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AG61">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK61">
         <v>2.5</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O62">
         <v>2.95</v>
       </c>
       <c r="P62">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="Q62">
         <v>3.02</v>
@@ -10445,25 +10445,25 @@
         <v>1.02</v>
       </c>
       <c r="X62">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y62">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z62">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AA62">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AB62">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AC62">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AD62">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE62">
         <v>1.03</v>
@@ -10472,7 +10472,7 @@
         <v>1.95</v>
       </c>
       <c r="AG62">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.34</v>
       </c>
       <c r="AK62">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10581,13 +10581,13 @@
         <v>2.25</v>
       </c>
       <c r="O63">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P63">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q63">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="R63">
         <v>2.38</v>
@@ -10605,16 +10605,16 @@
         <v>1.57</v>
       </c>
       <c r="W63">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X63">
         <v>1.03</v>
       </c>
       <c r="Y63">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z63">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA63">
         <v>1.62</v>
@@ -10623,19 +10623,19 @@
         <v>2.36</v>
       </c>
       <c r="AC63">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD63">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE63">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF63">
         <v>1.5</v>
       </c>
       <c r="AG63">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="O64">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="P64">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q64">
         <v>2.25</v>
@@ -10756,65 +10756,65 @@
         <v>2.3</v>
       </c>
       <c r="S64">
+        <v>1.3</v>
+      </c>
+      <c r="T64">
+        <v>3.25</v>
+      </c>
+      <c r="U64">
+        <v>2.4</v>
+      </c>
+      <c r="V64">
+        <v>1.5</v>
+      </c>
+      <c r="W64">
+        <v>1.08</v>
+      </c>
+      <c r="X64">
+        <v>1.02</v>
+      </c>
+      <c r="Y64">
+        <v>1.2</v>
+      </c>
+      <c r="Z64">
+        <v>4.15</v>
+      </c>
+      <c r="AA64">
+        <v>1.67</v>
+      </c>
+      <c r="AB64">
+        <v>2.08</v>
+      </c>
+      <c r="AC64">
+        <v>2.59</v>
+      </c>
+      <c r="AD64">
+        <v>1.39</v>
+      </c>
+      <c r="AE64">
+        <v>1.17</v>
+      </c>
+      <c r="AF64">
+        <v>1.62</v>
+      </c>
+      <c r="AG64">
+        <v>2.13</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
         <v>1.25</v>
       </c>
-      <c r="T64">
-        <v>3.5</v>
-      </c>
-      <c r="U64">
-        <v>2.31</v>
-      </c>
-      <c r="V64">
-        <v>1.53</v>
-      </c>
-      <c r="W64">
-        <v>1.09</v>
-      </c>
-      <c r="X64">
-        <v>1.03</v>
-      </c>
-      <c r="Y64">
-        <v>1.17</v>
-      </c>
-      <c r="Z64">
-        <v>4.65</v>
-      </c>
-      <c r="AA64">
-        <v>1.56</v>
-      </c>
-      <c r="AB64">
-        <v>2.3</v>
-      </c>
-      <c r="AC64">
-        <v>2.4</v>
-      </c>
-      <c r="AD64">
-        <v>1.53</v>
-      </c>
-      <c r="AE64">
-        <v>1.2</v>
-      </c>
-      <c r="AF64">
-        <v>1.5</v>
-      </c>
-      <c r="AG64">
-        <v>2.38</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>1.2</v>
-      </c>
       <c r="AK64">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="O65">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="P65">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q65">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="R65">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S65">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T65">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="U65">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V65">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="W65">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X65">
         <v>1.02</v>
       </c>
       <c r="Y65">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Z65">
-        <v>4.15</v>
+        <v>5.25</v>
       </c>
       <c r="AA65">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AB65">
-        <v>2.08</v>
+        <v>2.54</v>
       </c>
       <c r="AC65">
-        <v>2.59</v>
+        <v>2.21</v>
       </c>
       <c r="AD65">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="AE65">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AF65">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AG65">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="O66">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P66">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q66">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="R66">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="S66">
+        <v>1.18</v>
+      </c>
+      <c r="T66">
+        <v>4.33</v>
+      </c>
+      <c r="U66">
+        <v>1.86</v>
+      </c>
+      <c r="V66">
+        <v>1.85</v>
+      </c>
+      <c r="W66">
         <v>1.22</v>
       </c>
-      <c r="T66">
-        <v>3.8</v>
-      </c>
-      <c r="U66">
-        <v>2.1</v>
-      </c>
-      <c r="V66">
-        <v>1.65</v>
-      </c>
-      <c r="W66">
-        <v>1.13</v>
-      </c>
       <c r="X66">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z66">
-        <v>5.25</v>
+        <v>6.3</v>
       </c>
       <c r="AA66">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AB66">
-        <v>2.54</v>
+        <v>3.2</v>
       </c>
       <c r="AC66">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="AD66">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="AE66">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AF66">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG66">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK66">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="O67">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P67">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="Q67">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="R67">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="S67">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T67">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="U67">
-        <v>1.86</v>
+        <v>2.21</v>
       </c>
       <c r="V67">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="W67">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="X67">
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="Z67">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="AA67">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AB67">
-        <v>3.2</v>
+        <v>2.53</v>
       </c>
       <c r="AC67">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="AD67">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AE67">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AF67">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AG67">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK67">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="O69">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="P69">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q69">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="R69">
-        <v>2.69</v>
+        <v>2.3</v>
       </c>
       <c r="S69">
         <v>1.25</v>
       </c>
       <c r="T69">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U69">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="V69">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="W69">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y69">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z69">
-        <v>5.1</v>
+        <v>4.65</v>
       </c>
       <c r="AA69">
+        <v>1.56</v>
+      </c>
+      <c r="AB69">
+        <v>2.3</v>
+      </c>
+      <c r="AC69">
+        <v>2.4</v>
+      </c>
+      <c r="AD69">
+        <v>1.53</v>
+      </c>
+      <c r="AE69">
+        <v>1.2</v>
+      </c>
+      <c r="AF69">
         <v>1.5</v>
       </c>
-      <c r="AB69">
-        <v>2.53</v>
-      </c>
-      <c r="AC69">
-        <v>2.19</v>
-      </c>
-      <c r="AD69">
-        <v>1.61</v>
-      </c>
-      <c r="AE69">
-        <v>1.22</v>
-      </c>
-      <c r="AF69">
-        <v>1.6</v>
-      </c>
       <c r="AG69">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>1.2</v>
       </c>
       <c r="AK69">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,16 +11719,16 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="O70">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P70">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q70">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="R70">
         <v>2.1</v>
@@ -11740,43 +11740,43 @@
         <v>2.5</v>
       </c>
       <c r="U70">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="V70">
         <v>1.33</v>
       </c>
       <c r="W70">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X70">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y70">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z70">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="AA70">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB70">
         <v>1.67</v>
       </c>
       <c r="AC70">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="AD70">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE70">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF70">
         <v>2</v>
       </c>
       <c r="AG70">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>1.14</v>
       </c>
       <c r="AK70">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="O71">
         <v>7</v>
@@ -11894,22 +11894,22 @@
         <v>1.55</v>
       </c>
       <c r="R71">
-        <v>2.76</v>
+        <v>2.99</v>
       </c>
       <c r="S71">
         <v>1.19</v>
       </c>
       <c r="T71">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="U71">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="V71">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="W71">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X71">
         <v>1.01</v>
@@ -11918,22 +11918,22 @@
         <v>1.14</v>
       </c>
       <c r="Z71">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA71">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB71">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="AC71">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AD71">
         <v>1.62</v>
       </c>
       <c r="AE71">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF71">
         <v>2.08</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O72">
         <v>3.3</v>
       </c>
       <c r="P72">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q72">
         <v>3.1</v>
@@ -12069,40 +12069,40 @@
         <v>2.63</v>
       </c>
       <c r="V72">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W72">
         <v>1.06</v>
       </c>
       <c r="X72">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z72">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA72">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB72">
         <v>2.02</v>
       </c>
       <c r="AC72">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AD72">
         <v>1.33</v>
       </c>
       <c r="AE72">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF72">
         <v>1.6</v>
       </c>
       <c r="AG72">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK72">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12371,34 +12371,34 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O74">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P74">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q74">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R74">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S74">
         <v>1.28</v>
       </c>
       <c r="T74">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U74">
         <v>2.52</v>
       </c>
       <c r="V74">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W74">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X74">
         <v>1.03</v>
@@ -12407,13 +12407,13 @@
         <v>1.2</v>
       </c>
       <c r="Z74">
-        <v>4.15</v>
+        <v>4.69</v>
       </c>
       <c r="AA74">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AB74">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AC74">
         <v>2.65</v>
@@ -12422,10 +12422,10 @@
         <v>1.44</v>
       </c>
       <c r="AE74">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF74">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AG74">
         <v>2.06</v>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AK74">
         <v>2.19</v>
@@ -12860,31 +12860,31 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="O77">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="P77">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="Q77">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="R77">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="S77">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T77">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="U77">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="V77">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W77">
         <v>1.08</v>
@@ -12893,31 +12893,31 @@
         <v>1.03</v>
       </c>
       <c r="Y77">
+        <v>1.23</v>
+      </c>
+      <c r="Z77">
+        <v>3.44</v>
+      </c>
+      <c r="AA77">
+        <v>2.03</v>
+      </c>
+      <c r="AB77">
+        <v>1.81</v>
+      </c>
+      <c r="AC77">
+        <v>3.4</v>
+      </c>
+      <c r="AD77">
         <v>1.29</v>
       </c>
-      <c r="Z77">
-        <v>3.4</v>
-      </c>
-      <c r="AA77">
-        <v>1.89</v>
-      </c>
-      <c r="AB77">
-        <v>1.89</v>
-      </c>
-      <c r="AC77">
-        <v>3.49</v>
-      </c>
-      <c r="AD77">
-        <v>1.28</v>
-      </c>
       <c r="AE77">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF77">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG77">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK77">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,80 +13023,80 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="O78">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="P78">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q78">
-        <v>2.82</v>
+        <v>3.09</v>
       </c>
       <c r="R78">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S78">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T78">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="U78">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="V78">
+        <v>1.35</v>
+      </c>
+      <c r="W78">
+        <v>1.05</v>
+      </c>
+      <c r="X78">
+        <v>1.06</v>
+      </c>
+      <c r="Y78">
+        <v>1.3</v>
+      </c>
+      <c r="Z78">
+        <v>2.99</v>
+      </c>
+      <c r="AA78">
+        <v>2.1</v>
+      </c>
+      <c r="AB78">
+        <v>1.75</v>
+      </c>
+      <c r="AC78">
+        <v>3.44</v>
+      </c>
+      <c r="AD78">
+        <v>1.23</v>
+      </c>
+      <c r="AE78">
+        <v>1.07</v>
+      </c>
+      <c r="AF78">
+        <v>1.85</v>
+      </c>
+      <c r="AG78">
+        <v>1.85</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
         <v>1.33</v>
       </c>
-      <c r="W78">
-        <v>1.07</v>
-      </c>
-      <c r="X78">
-        <v>1.02</v>
-      </c>
-      <c r="Y78">
-        <v>1.31</v>
-      </c>
-      <c r="Z78">
-        <v>2.94</v>
-      </c>
-      <c r="AA78">
-        <v>2.07</v>
-      </c>
-      <c r="AB78">
-        <v>1.69</v>
-      </c>
-      <c r="AC78">
-        <v>3.75</v>
-      </c>
-      <c r="AD78">
-        <v>1.25</v>
-      </c>
-      <c r="AE78">
-        <v>1.05</v>
-      </c>
-      <c r="AF78">
-        <v>1.9</v>
-      </c>
-      <c r="AG78">
-        <v>1.86</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>1.3</v>
-      </c>
       <c r="AK78">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="O79">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="P79">
-        <v>5.55</v>
+        <v>3.1</v>
       </c>
       <c r="Q79">
+        <v>2.71</v>
+      </c>
+      <c r="R79">
+        <v>2.29</v>
+      </c>
+      <c r="S79">
+        <v>1.35</v>
+      </c>
+      <c r="T79">
+        <v>3.1</v>
+      </c>
+      <c r="U79">
+        <v>2.6</v>
+      </c>
+      <c r="V79">
+        <v>1.44</v>
+      </c>
+      <c r="W79">
+        <v>1.06</v>
+      </c>
+      <c r="X79">
+        <v>1.01</v>
+      </c>
+      <c r="Y79">
+        <v>1.25</v>
+      </c>
+      <c r="Z79">
+        <v>3.7</v>
+      </c>
+      <c r="AA79">
+        <v>1.78</v>
+      </c>
+      <c r="AB79">
         <v>2</v>
       </c>
-      <c r="R79">
-        <v>2.38</v>
-      </c>
-      <c r="S79">
-        <v>1.3</v>
-      </c>
-      <c r="T79">
-        <v>3.3</v>
-      </c>
-      <c r="U79">
-        <v>2.36</v>
-      </c>
-      <c r="V79">
-        <v>1.5</v>
-      </c>
-      <c r="W79">
-        <v>1.08</v>
-      </c>
-      <c r="X79">
-        <v>1.04</v>
-      </c>
-      <c r="Y79">
-        <v>1.14</v>
-      </c>
-      <c r="Z79">
-        <v>4.4</v>
-      </c>
-      <c r="AA79">
-        <v>1.6</v>
-      </c>
-      <c r="AB79">
-        <v>2.15</v>
-      </c>
       <c r="AC79">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AD79">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AE79">
         <v>1.14</v>
       </c>
       <c r="AF79">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG79">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AK79">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="O80">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P80">
-        <v>1.95</v>
+        <v>3.9</v>
       </c>
       <c r="Q80">
-        <v>3.93</v>
+        <v>2.31</v>
       </c>
       <c r="R80">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="S80">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="T80">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="U80">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="V80">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W80">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X80">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z80">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="AA80">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB80">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC80">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="AD80">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE80">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF80">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG80">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.74</v>
+        <v>1.3</v>
       </c>
       <c r="AK80">
-        <v>1.21</v>
+        <v>1.91</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,28 +13512,28 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="O81">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P81">
-        <v>3.1</v>
+        <v>4.36</v>
       </c>
       <c r="Q81">
-        <v>2.71</v>
+        <v>2.3</v>
       </c>
       <c r="R81">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S81">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T81">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U81">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="V81">
         <v>1.44</v>
@@ -13542,34 +13542,34 @@
         <v>1.06</v>
       </c>
       <c r="X81">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z81">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA81">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB81">
         <v>1.95</v>
       </c>
       <c r="AC81">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD81">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE81">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF81">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG81">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AK81">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,19 +13675,19 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="O82">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P82">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q82">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R82">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S82">
         <v>1.4</v>
@@ -13696,7 +13696,7 @@
         <v>2.85</v>
       </c>
       <c r="U82">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="V82">
         <v>1.4</v>
@@ -13705,7 +13705,7 @@
         <v>1.06</v>
       </c>
       <c r="X82">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y82">
         <v>1.25</v>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AK82">
         <v>1.44</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.71</v>
+        <v>3.6</v>
       </c>
       <c r="O83">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="P83">
-        <v>4.5</v>
+        <v>2.04</v>
       </c>
       <c r="Q83">
-        <v>2.31</v>
+        <v>4.49</v>
       </c>
       <c r="R83">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S83">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T83">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="U83">
-        <v>2.75</v>
+        <v>2.99</v>
       </c>
       <c r="V83">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W83">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X83">
         <v>1.05</v>
       </c>
       <c r="Y83">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="Z83">
+        <v>3.1</v>
+      </c>
+      <c r="AA83">
+        <v>2.1</v>
+      </c>
+      <c r="AB83">
+        <v>1.64</v>
+      </c>
+      <c r="AC83">
         <v>3.5</v>
       </c>
-      <c r="AA83">
-        <v>1.87</v>
-      </c>
-      <c r="AB83">
-        <v>1.9</v>
-      </c>
-      <c r="AC83">
-        <v>3.25</v>
-      </c>
       <c r="AD83">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE83">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF83">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AG83">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="AK83">
-        <v>1.96</v>
+        <v>1.21</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O84">
+        <v>3.55</v>
+      </c>
+      <c r="P84">
+        <v>4.2</v>
+      </c>
+      <c r="Q84">
+        <v>2.41</v>
+      </c>
+      <c r="R84">
+        <v>2.15</v>
+      </c>
+      <c r="S84">
+        <v>1.36</v>
+      </c>
+      <c r="T84">
+        <v>2.79</v>
+      </c>
+      <c r="U84">
+        <v>2.8</v>
+      </c>
+      <c r="V84">
+        <v>1.4</v>
+      </c>
+      <c r="W84">
+        <v>1.08</v>
+      </c>
+      <c r="X84">
+        <v>1.05</v>
+      </c>
+      <c r="Y84">
+        <v>1.33</v>
+      </c>
+      <c r="Z84">
         <v>3.4</v>
       </c>
-      <c r="P84">
-        <v>4.16</v>
-      </c>
-      <c r="Q84">
-        <v>2.44</v>
-      </c>
-      <c r="R84">
-        <v>2.06</v>
-      </c>
-      <c r="S84">
-        <v>1.35</v>
-      </c>
-      <c r="T84">
-        <v>2.81</v>
-      </c>
-      <c r="U84">
-        <v>3.07</v>
-      </c>
-      <c r="V84">
-        <v>1.35</v>
-      </c>
-      <c r="W84">
-        <v>1.04</v>
-      </c>
-      <c r="X84">
-        <v>1.01</v>
-      </c>
-      <c r="Y84">
-        <v>1.34</v>
-      </c>
-      <c r="Z84">
-        <v>3.05</v>
-      </c>
       <c r="AA84">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="AB84">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AC84">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="AD84">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE84">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF84">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG84">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK84">
         <v>1.95</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="O85">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P85">
-        <v>3.73</v>
+        <v>6.1</v>
       </c>
       <c r="Q85">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="R85">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="S85">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T85">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U85">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="V85">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W85">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X85">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y85">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z85">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA85">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="AB85">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="AC85">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="AD85">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AE85">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF85">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AG85">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14493,13 +14493,13 @@
         <v>1.5</v>
       </c>
       <c r="O87">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P87">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q87">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R87">
         <v>2.47</v>
@@ -14511,10 +14511,10 @@
         <v>3.25</v>
       </c>
       <c r="U87">
-        <v>2.31</v>
+        <v>2.12</v>
       </c>
       <c r="V87">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W87">
         <v>1.13</v>
@@ -14523,10 +14523,10 @@
         <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z87">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA87">
         <v>1.65</v>
@@ -14538,16 +14538,16 @@
         <v>2.55</v>
       </c>
       <c r="AD87">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE87">
         <v>1.14</v>
       </c>
       <c r="AF87">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG87">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK87">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,80 +14653,80 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="O88">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="P88">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="Q88">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="R88">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="S88">
+        <v>1.25</v>
+      </c>
+      <c r="T88">
+        <v>3.6</v>
+      </c>
+      <c r="U88">
+        <v>2.24</v>
+      </c>
+      <c r="V88">
+        <v>1.57</v>
+      </c>
+      <c r="W88">
+        <v>1.14</v>
+      </c>
+      <c r="X88">
+        <v>1.01</v>
+      </c>
+      <c r="Y88">
+        <v>1.14</v>
+      </c>
+      <c r="Z88">
+        <v>5.5</v>
+      </c>
+      <c r="AA88">
+        <v>1.48</v>
+      </c>
+      <c r="AB88">
+        <v>2.33</v>
+      </c>
+      <c r="AC88">
+        <v>2.27</v>
+      </c>
+      <c r="AD88">
+        <v>1.55</v>
+      </c>
+      <c r="AE88">
         <v>1.22</v>
       </c>
-      <c r="T88">
-        <v>3.75</v>
-      </c>
-      <c r="U88">
-        <v>2.2</v>
-      </c>
-      <c r="V88">
-        <v>1.59</v>
-      </c>
-      <c r="W88">
-        <v>1.15</v>
-      </c>
-      <c r="X88">
-        <v>1.02</v>
-      </c>
-      <c r="Y88">
+      <c r="AF88">
+        <v>1.57</v>
+      </c>
+      <c r="AG88">
+        <v>2.19</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ88">
         <v>1.13</v>
       </c>
-      <c r="Z88">
-        <v>4.9</v>
-      </c>
-      <c r="AA88">
-        <v>1.5</v>
-      </c>
-      <c r="AB88">
-        <v>2.4</v>
-      </c>
-      <c r="AC88">
-        <v>2.21</v>
-      </c>
-      <c r="AD88">
-        <v>1.62</v>
-      </c>
-      <c r="AE88">
-        <v>1.25</v>
-      </c>
-      <c r="AF88">
-        <v>1.52</v>
-      </c>
-      <c r="AG88">
-        <v>2.34</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ88">
-        <v>1.17</v>
-      </c>
       <c r="AK88">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,19 +14816,19 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="O89">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P89">
         <v>6</v>
       </c>
       <c r="Q89">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R89">
-        <v>2.51</v>
+        <v>2.29</v>
       </c>
       <c r="S89">
         <v>1.3</v>
@@ -14846,13 +14846,13 @@
         <v>1.08</v>
       </c>
       <c r="X89">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z89">
-        <v>4.19</v>
+        <v>3.5</v>
       </c>
       <c r="AA89">
         <v>1.71</v>
@@ -14861,10 +14861,10 @@
         <v>1.98</v>
       </c>
       <c r="AC89">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="AD89">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AE89">
         <v>1.13</v>
@@ -14979,7 +14979,7 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="O90">
         <v>6.1</v>
@@ -15000,7 +15000,7 @@
         <v>3.9</v>
       </c>
       <c r="U90">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="V90">
         <v>1.68</v>
@@ -15012,19 +15012,19 @@
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="Z90">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AA90">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AB90">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="AC90">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AD90">
         <v>1.68</v>
@@ -15033,10 +15033,10 @@
         <v>1.22</v>
       </c>
       <c r="AF90">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG90">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AK90">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15305,19 +15305,19 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="O92">
         <v>3</v>
       </c>
       <c r="P92">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q92">
-        <v>2.98</v>
+        <v>3.06</v>
       </c>
       <c r="R92">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S92">
         <v>1.5</v>
@@ -15326,13 +15326,13 @@
         <v>2.45</v>
       </c>
       <c r="U92">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="V92">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W92">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X92">
         <v>1.06</v>
@@ -15341,16 +15341,16 @@
         <v>1.47</v>
       </c>
       <c r="Z92">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="AA92">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AB92">
         <v>1.47</v>
       </c>
       <c r="AC92">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AD92">
         <v>1.13</v>
@@ -15359,7 +15359,7 @@
         <v>1.05</v>
       </c>
       <c r="AF92">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AG92">
         <v>1.7</v>
@@ -15471,28 +15471,28 @@
         <v>3.5</v>
       </c>
       <c r="O93">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P93">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q93">
-        <v>3.63</v>
+        <v>4.3</v>
       </c>
       <c r="R93">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S93">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T93">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U93">
         <v>2.8</v>
       </c>
       <c r="V93">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W93">
         <v>1.07</v>
@@ -15501,31 +15501,31 @@
         <v>1.03</v>
       </c>
       <c r="Y93">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z93">
+        <v>3.08</v>
+      </c>
+      <c r="AA93">
+        <v>1.95</v>
+      </c>
+      <c r="AB93">
+        <v>1.86</v>
+      </c>
+      <c r="AC93">
         <v>3.4</v>
       </c>
-      <c r="AA93">
-        <v>1.91</v>
-      </c>
-      <c r="AB93">
-        <v>1.85</v>
-      </c>
-      <c r="AC93">
-        <v>3.25</v>
-      </c>
       <c r="AD93">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE93">
         <v>1.09</v>
       </c>
       <c r="AF93">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG93">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
       <c r="AK93">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,10 +15631,10 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="O94">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P94">
         <v>2.65</v>
@@ -15643,13 +15643,13 @@
         <v>2.85</v>
       </c>
       <c r="R94">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S94">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="T94">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U94">
         <v>2.75</v>
@@ -15658,22 +15658,22 @@
         <v>1.4</v>
       </c>
       <c r="W94">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X94">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y94">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z94">
         <v>3.3</v>
       </c>
       <c r="AA94">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB94">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC94">
         <v>3.14</v>
@@ -15682,13 +15682,13 @@
         <v>1.29</v>
       </c>
       <c r="AE94">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF94">
         <v>1.7</v>
       </c>
       <c r="AG94">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>1.36</v>
       </c>
       <c r="AK94">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,61 +15794,61 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O95">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P95">
         <v>3</v>
       </c>
       <c r="Q95">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="R95">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="S95">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="T95">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U95">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="V95">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="W95">
         <v>1.03</v>
       </c>
       <c r="X95">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Y95">
         <v>1.79</v>
       </c>
       <c r="Z95">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AA95">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AB95">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AC95">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AD95">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AE95">
         <v>1.02</v>
       </c>
       <c r="AF95">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AG95">
         <v>1.44</v>
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="O96">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="P96">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="Q96">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="R96">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="S96">
         <v>1.38</v>
       </c>
       <c r="T96">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="U96">
         <v>2.65</v>
       </c>
       <c r="V96">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W96">
+        <v>1.04</v>
+      </c>
+      <c r="X96">
         <v>1.05</v>
       </c>
-      <c r="X96">
-        <v>1</v>
-      </c>
       <c r="Y96">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z96">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA96">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AB96">
         <v>1.93</v>
       </c>
       <c r="AC96">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD96">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE96">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF96">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG96">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK96">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="O98">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="P98">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="Q98">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R98">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="S98">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="T98">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="U98">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="V98">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="W98">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X98">
         <v>1</v>
       </c>
       <c r="Y98">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z98">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AA98">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AB98">
         <v>3.85</v>
       </c>
       <c r="AC98">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AD98">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AE98">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AF98">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG98">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>1.01</v>
       </c>
       <c r="AK98">
-        <v>6</v>
+        <v>5.45</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16449,31 +16449,31 @@
         <v>1.18</v>
       </c>
       <c r="O99">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="P99">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q99">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="R99">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="S99">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T99">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="U99">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V99">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="W99">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X99">
         <v>1.02</v>
@@ -16482,28 +16482,28 @@
         <v>1.2</v>
       </c>
       <c r="Z99">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="AA99">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AB99">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC99">
         <v>2.55</v>
       </c>
       <c r="AD99">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AE99">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF99">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AG99">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK99">
         <v>3.5</v>
@@ -16624,16 +16624,16 @@
         <v>2.19</v>
       </c>
       <c r="S100">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T100">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="U100">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="V100">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W100">
         <v>1.08</v>
@@ -16645,28 +16645,28 @@
         <v>1.22</v>
       </c>
       <c r="Z100">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="AA100">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AB100">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AC100">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="AD100">
         <v>1.33</v>
       </c>
       <c r="AE100">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF100">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG100">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK100">
         <v>1.8</v>
@@ -16772,43 +16772,43 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="O101">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="P101">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA101">
         <v>1.44</v>
@@ -16817,19 +16817,19 @@
         <v>2.62</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,80 +16935,80 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O102">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P102">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Q102">
+        <v>1.8</v>
+      </c>
+      <c r="R102">
+        <v>2.6</v>
+      </c>
+      <c r="S102">
+        <v>1.24</v>
+      </c>
+      <c r="T102">
+        <v>3.8</v>
+      </c>
+      <c r="U102">
+        <v>2.23</v>
+      </c>
+      <c r="V102">
+        <v>1.61</v>
+      </c>
+      <c r="W102">
+        <v>1.15</v>
+      </c>
+      <c r="X102">
+        <v>1.02</v>
+      </c>
+      <c r="Y102">
+        <v>1.14</v>
+      </c>
+      <c r="Z102">
+        <v>4.8</v>
+      </c>
+      <c r="AA102">
+        <v>1.55</v>
+      </c>
+      <c r="AB102">
+        <v>2.35</v>
+      </c>
+      <c r="AC102">
         <v>2.3</v>
       </c>
-      <c r="R102">
-        <v>2.28</v>
-      </c>
-      <c r="S102">
-        <v>1.25</v>
-      </c>
-      <c r="T102">
-        <v>3.6</v>
-      </c>
-      <c r="U102">
-        <v>2.34</v>
-      </c>
-      <c r="V102">
-        <v>1.52</v>
-      </c>
-      <c r="W102">
+      <c r="AD102">
+        <v>1.53</v>
+      </c>
+      <c r="AE102">
+        <v>1.19</v>
+      </c>
+      <c r="AF102">
+        <v>1.63</v>
+      </c>
+      <c r="AG102">
+        <v>1.97</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
         <v>1.11</v>
       </c>
-      <c r="X102">
-        <v>1.01</v>
-      </c>
-      <c r="Y102">
-        <v>1.15</v>
-      </c>
-      <c r="Z102">
-        <v>4.2</v>
-      </c>
-      <c r="AA102">
-        <v>1.61</v>
-      </c>
-      <c r="AB102">
-        <v>2.15</v>
-      </c>
-      <c r="AC102">
-        <v>2.49</v>
-      </c>
-      <c r="AD102">
-        <v>1.45</v>
-      </c>
-      <c r="AE102">
-        <v>1.14</v>
-      </c>
-      <c r="AF102">
-        <v>1.56</v>
-      </c>
-      <c r="AG102">
-        <v>2.18</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.2</v>
-      </c>
       <c r="AK102">
-        <v>1.84</v>
+        <v>2.78</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q103">
-        <v>1.81</v>
+        <v>2.45</v>
       </c>
       <c r="R103">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S103">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T103">
-        <v>3.42</v>
+        <v>3.02</v>
       </c>
       <c r="U103">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="V103">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="W103">
         <v>1.11</v>
       </c>
       <c r="X103">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y103">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z103">
-        <v>4.45</v>
+        <v>3.9</v>
       </c>
       <c r="AA103">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB103">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="AC103">
-        <v>2.53</v>
+        <v>2.74</v>
       </c>
       <c r="AD103">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AE103">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF103">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG103">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AK103">
-        <v>2.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="O104">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="P104">
-        <v>2.8</v>
+        <v>4.05</v>
       </c>
       <c r="Q104">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="R104">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="S104">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T104">
-        <v>3.02</v>
+        <v>3.6</v>
       </c>
       <c r="U104">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="V104">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W104">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X104">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y104">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z104">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="AA104">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB104">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AC104">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="AD104">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE104">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF104">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG104">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK104">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AL104">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="O2">
         <v>3.25</v>
       </c>
       <c r="P2">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="Q2">
         <v>2.54</v>
@@ -650,46 +650,46 @@
         <v>2.15</v>
       </c>
       <c r="S2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T2">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="U2">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="V2">
         <v>1.41</v>
       </c>
       <c r="W2">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
         <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z2">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AA2">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB2">
         <v>2</v>
       </c>
       <c r="AC2">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE2">
         <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG2">
         <v>2.2</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AK2">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="O5">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
-        <v>5.13</v>
+        <v>2</v>
       </c>
       <c r="Q5">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="R5">
-        <v>2.96</v>
+        <v>2.45</v>
       </c>
       <c r="S5">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>4.8</v>
+        <v>3.36</v>
       </c>
       <c r="U5">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="V5">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="W5">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z5">
-        <v>6.82</v>
+        <v>4.5</v>
       </c>
       <c r="AA5">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AB5">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC5">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AD5">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AE5">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AF5">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG5">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P6">
-        <v>2</v>
+        <v>5.13</v>
       </c>
       <c r="Q6">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="R6">
-        <v>2.45</v>
+        <v>2.96</v>
       </c>
       <c r="S6">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T6">
-        <v>3.36</v>
+        <v>4.8</v>
       </c>
       <c r="U6">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="V6">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z6">
-        <v>4.5</v>
+        <v>6.82</v>
       </c>
       <c r="AA6">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AB6">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="AC6">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AD6">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AE6">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AF6">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG6">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="P11">
-        <v>4.89</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q11">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="R11">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="T11">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="U11">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V11">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="Z11">
-        <v>2.97</v>
+        <v>2.62</v>
       </c>
       <c r="AA11">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB11">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AC11">
-        <v>3.54</v>
+        <v>4.33</v>
       </c>
       <c r="AD11">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AE11">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="AG11">
-        <v>1.77</v>
+        <v>1.42</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK11">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-08-14 12:00:00</t>
+          <t>2026-08-14 11:30:00</t>
         </is>
       </c>
     </row>
@@ -2223,22 +2223,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.38</v>
+        <v>1.72</v>
       </c>
       <c r="O12">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>2.95</v>
+        <v>4.89</v>
       </c>
       <c r="Q12">
-        <v>3.35</v>
+        <v>2.32</v>
       </c>
       <c r="R12">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="S12">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="T12">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="U12">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="V12">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="W12">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="Z12">
-        <v>2.43</v>
+        <v>2.97</v>
       </c>
       <c r="AA12">
-        <v>2.53</v>
+        <v>2.1</v>
       </c>
       <c r="AB12">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AC12">
-        <v>4.86</v>
+        <v>3.54</v>
       </c>
       <c r="AD12">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AE12">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AF12">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AG12">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.36</v>
+        <v>2.64</v>
       </c>
       <c r="O13">
-        <v>3.85</v>
+        <v>2.94</v>
       </c>
       <c r="P13">
-        <v>8.550000000000001</v>
+        <v>2.98</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="O17">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P17">
         <v>3.1</v>
@@ -3113,10 +3113,10 @@
         <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="Z17">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA17">
         <v>2.1</v>
@@ -3131,7 +3131,7 @@
         <v>1.22</v>
       </c>
       <c r="AE17">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
         <v>1.83</v>
@@ -3153,7 +3153,7 @@
         <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.61</v>
+        <v>2.45</v>
       </c>
       <c r="O21">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="P21">
-        <v>4.25</v>
+        <v>2.62</v>
       </c>
       <c r="Q21">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,49 +3895,49 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.5</v>
+        <v>1.27</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="P22">
-        <v>2.3</v>
+        <v>11</v>
       </c>
       <c r="Q22">
-        <v>3.2</v>
+        <v>1.67</v>
       </c>
       <c r="R22">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T22">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="U22">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W22">
         <v>1.06</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z22">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="AA22">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AB22">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AC22">
         <v>2.88</v>
@@ -3946,29 +3946,29 @@
         <v>1.32</v>
       </c>
       <c r="AE22">
+        <v>1.1</v>
+      </c>
+      <c r="AF22">
+        <v>2.4</v>
+      </c>
+      <c r="AG22">
+        <v>1.5</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
         <v>1.11</v>
       </c>
-      <c r="AF22">
-        <v>1.57</v>
-      </c>
-      <c r="AG22">
-        <v>2.25</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.3</v>
-      </c>
       <c r="AK22">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>3</v>
+        <v>1.61</v>
       </c>
       <c r="O23">
-        <v>2.93</v>
+        <v>3.75</v>
       </c>
       <c r="P23">
-        <v>2.32</v>
+        <v>4.25</v>
       </c>
       <c r="Q23">
-        <v>3.97</v>
+        <v>2.1</v>
       </c>
       <c r="R23">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.56</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
+        <v>3.4</v>
+      </c>
+      <c r="U23">
         <v>2.31</v>
       </c>
-      <c r="U23">
-        <v>3.36</v>
-      </c>
       <c r="V23">
+        <v>1.5</v>
+      </c>
+      <c r="W23">
+        <v>1.12</v>
+      </c>
+      <c r="X23">
+        <v>1.02</v>
+      </c>
+      <c r="Y23">
+        <v>1.2</v>
+      </c>
+      <c r="Z23">
+        <v>4</v>
+      </c>
+      <c r="AA23">
+        <v>1.67</v>
+      </c>
+      <c r="AB23">
+        <v>2.17</v>
+      </c>
+      <c r="AC23">
+        <v>2.63</v>
+      </c>
+      <c r="AD23">
+        <v>1.44</v>
+      </c>
+      <c r="AE23">
+        <v>1.17</v>
+      </c>
+      <c r="AF23">
+        <v>1.62</v>
+      </c>
+      <c r="AG23">
+        <v>2.15</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
         <v>1.25</v>
       </c>
-      <c r="W23">
-        <v>1</v>
-      </c>
-      <c r="X23">
-        <v>1.06</v>
-      </c>
-      <c r="Y23">
-        <v>1.42</v>
-      </c>
-      <c r="Z23">
-        <v>2.73</v>
-      </c>
-      <c r="AA23">
-        <v>2.46</v>
-      </c>
-      <c r="AB23">
-        <v>1.54</v>
-      </c>
-      <c r="AC23">
-        <v>4.7</v>
-      </c>
-      <c r="AD23">
-        <v>1.18</v>
-      </c>
-      <c r="AE23">
-        <v>1.01</v>
-      </c>
-      <c r="AF23">
-        <v>1.99</v>
-      </c>
-      <c r="AG23">
-        <v>1.73</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.36</v>
-      </c>
       <c r="AK23">
-        <v>1.34</v>
+        <v>2.15</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-08-14 13:30:00</t>
+          <t>2026-08-14 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,65 +4221,65 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P24">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="Q24">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="R24">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S24">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U24">
+        <v>2.46</v>
+      </c>
+      <c r="V24">
+        <v>1.44</v>
+      </c>
+      <c r="W24">
+        <v>1.06</v>
+      </c>
+      <c r="X24">
+        <v>1</v>
+      </c>
+      <c r="Y24">
+        <v>1.17</v>
+      </c>
+      <c r="Z24">
+        <v>4</v>
+      </c>
+      <c r="AA24">
+        <v>1.65</v>
+      </c>
+      <c r="AB24">
+        <v>2.11</v>
+      </c>
+      <c r="AC24">
+        <v>2.88</v>
+      </c>
+      <c r="AD24">
+        <v>1.32</v>
+      </c>
+      <c r="AE24">
+        <v>1.11</v>
+      </c>
+      <c r="AF24">
+        <v>1.57</v>
+      </c>
+      <c r="AG24">
         <v>2.25</v>
       </c>
-      <c r="V24">
-        <v>1.53</v>
-      </c>
-      <c r="W24">
-        <v>1.1</v>
-      </c>
-      <c r="X24">
-        <v>1.03</v>
-      </c>
-      <c r="Y24">
-        <v>1.14</v>
-      </c>
-      <c r="Z24">
-        <v>4.5</v>
-      </c>
-      <c r="AA24">
-        <v>1.57</v>
-      </c>
-      <c r="AB24">
-        <v>2.34</v>
-      </c>
-      <c r="AC24">
-        <v>2.55</v>
-      </c>
-      <c r="AD24">
-        <v>1.53</v>
-      </c>
-      <c r="AE24">
-        <v>1.15</v>
-      </c>
-      <c r="AF24">
-        <v>1.5</v>
-      </c>
-      <c r="AG24">
-        <v>2.42</v>
-      </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-08-14 13:30:00</t>
+          <t>2026-08-14 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.3</v>
+        <v>2.99</v>
       </c>
       <c r="O25">
-        <v>3.37</v>
+        <v>2.9</v>
       </c>
       <c r="P25">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="Q25">
-        <v>2.9</v>
+        <v>3.92</v>
       </c>
       <c r="R25">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="S25">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="T25">
-        <v>2.95</v>
+        <v>2.33</v>
       </c>
       <c r="U25">
-        <v>2.38</v>
+        <v>3.36</v>
       </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="Z25">
-        <v>4.08</v>
+        <v>2.75</v>
       </c>
       <c r="AA25">
-        <v>1.8</v>
+        <v>2.46</v>
       </c>
       <c r="AB25">
-        <v>1.96</v>
+        <v>1.54</v>
       </c>
       <c r="AC25">
-        <v>2.7</v>
+        <v>4.75</v>
       </c>
       <c r="AD25">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="AE25">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AF25">
-        <v>1.6</v>
+        <v>1.97</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AK25">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,80 +4547,80 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="O26">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="Q26">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="R26">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="S26">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T26">
-        <v>2.71</v>
+        <v>3.5</v>
       </c>
       <c r="U26">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="Z26">
-        <v>3.38</v>
+        <v>4.5</v>
       </c>
       <c r="AA26">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="AB26">
-        <v>1.94</v>
+        <v>2.34</v>
       </c>
       <c r="AC26">
-        <v>2.99</v>
+        <v>2.55</v>
       </c>
       <c r="AD26">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF26">
+        <v>1.5</v>
+      </c>
+      <c r="AG26">
+        <v>2.42</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>1.36</v>
+      </c>
+      <c r="AK26">
         <v>1.67</v>
-      </c>
-      <c r="AG26">
-        <v>2.1</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.31</v>
-      </c>
-      <c r="AK26">
-        <v>1.5</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="O27">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="P27">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.27</v>
+        <v>2.3</v>
       </c>
       <c r="O28">
-        <v>4.7</v>
+        <v>3.37</v>
       </c>
       <c r="P28">
-        <v>11</v>
+        <v>2.8</v>
       </c>
       <c r="Q28">
-        <v>1.77</v>
+        <v>2.9</v>
       </c>
       <c r="R28">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="S28">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T28">
+        <v>2.95</v>
+      </c>
+      <c r="U28">
+        <v>2.38</v>
+      </c>
+      <c r="V28">
+        <v>1.44</v>
+      </c>
+      <c r="W28">
+        <v>1.11</v>
+      </c>
+      <c r="X28">
+        <v>1.04</v>
+      </c>
+      <c r="Y28">
+        <v>1.21</v>
+      </c>
+      <c r="Z28">
+        <v>4.08</v>
+      </c>
+      <c r="AA28">
+        <v>1.8</v>
+      </c>
+      <c r="AB28">
+        <v>1.96</v>
+      </c>
+      <c r="AC28">
         <v>2.7</v>
       </c>
-      <c r="U28">
-        <v>2.62</v>
-      </c>
-      <c r="V28">
-        <v>1.4</v>
-      </c>
-      <c r="W28">
-        <v>1.06</v>
-      </c>
-      <c r="X28">
-        <v>1.02</v>
-      </c>
-      <c r="Y28">
-        <v>1.25</v>
-      </c>
-      <c r="Z28">
-        <v>3.28</v>
-      </c>
-      <c r="AA28">
-        <v>1.82</v>
-      </c>
-      <c r="AB28">
-        <v>1.88</v>
-      </c>
-      <c r="AC28">
-        <v>2.88</v>
-      </c>
       <c r="AD28">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AE28">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF28">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="AG28">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AK28">
-        <v>3.18</v>
+        <v>1.53</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.58</v>
+        <v>3.43</v>
       </c>
       <c r="O29">
+        <v>3.04</v>
+      </c>
+      <c r="P29">
+        <v>2.1</v>
+      </c>
+      <c r="Q29">
         <v>3.9</v>
       </c>
-      <c r="P29">
-        <v>4.98</v>
-      </c>
-      <c r="Q29">
-        <v>2.14</v>
-      </c>
       <c r="R29">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="S29">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="T29">
-        <v>2.96</v>
+        <v>2.38</v>
       </c>
       <c r="U29">
+        <v>3.25</v>
+      </c>
+      <c r="V29">
+        <v>1.28</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>1.45</v>
+      </c>
+      <c r="Z29">
+        <v>2.55</v>
+      </c>
+      <c r="AA29">
         <v>2.45</v>
       </c>
-      <c r="V29">
-        <v>1.48</v>
-      </c>
-      <c r="W29">
-        <v>1.05</v>
-      </c>
-      <c r="X29">
-        <v>1.05</v>
-      </c>
-      <c r="Y29">
-        <v>1.22</v>
-      </c>
-      <c r="Z29">
-        <v>3.5</v>
-      </c>
-      <c r="AA29">
-        <v>1.75</v>
-      </c>
       <c r="AB29">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AC29">
-        <v>2.92</v>
+        <v>4.5</v>
       </c>
       <c r="AD29">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AE29">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG29">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK29">
-        <v>2.12</v>
+        <v>1.3</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-08-14 13:50:00</t>
+          <t>2026-08-14 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
+        <v>2.6</v>
+      </c>
+      <c r="O30">
+        <v>2.75</v>
+      </c>
+      <c r="P30">
+        <v>2.7</v>
+      </c>
+      <c r="Q30">
+        <v>3.54</v>
+      </c>
+      <c r="R30">
+        <v>1.77</v>
+      </c>
+      <c r="S30">
+        <v>1.63</v>
+      </c>
+      <c r="T30">
         <v>2.13</v>
       </c>
-      <c r="O30">
-        <v>3.1</v>
-      </c>
-      <c r="P30">
-        <v>3.15</v>
-      </c>
-      <c r="Q30">
-        <v>2.89</v>
-      </c>
-      <c r="R30">
-        <v>2</v>
-      </c>
-      <c r="S30">
-        <v>1.45</v>
-      </c>
-      <c r="T30">
-        <v>2.55</v>
-      </c>
       <c r="U30">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="V30">
+        <v>1.2</v>
+      </c>
+      <c r="W30">
+        <v>1.03</v>
+      </c>
+      <c r="X30">
+        <v>1.08</v>
+      </c>
+      <c r="Y30">
+        <v>1.65</v>
+      </c>
+      <c r="Z30">
+        <v>2.11</v>
+      </c>
+      <c r="AA30">
+        <v>2.97</v>
+      </c>
+      <c r="AB30">
         <v>1.3</v>
       </c>
-      <c r="W30">
+      <c r="AC30">
+        <v>6.55</v>
+      </c>
+      <c r="AD30">
+        <v>1.05</v>
+      </c>
+      <c r="AE30">
         <v>1.02</v>
       </c>
-      <c r="X30">
-        <v>1.05</v>
-      </c>
-      <c r="Y30">
-        <v>1.4</v>
-      </c>
-      <c r="Z30">
-        <v>2.88</v>
-      </c>
-      <c r="AA30">
-        <v>2.2</v>
-      </c>
-      <c r="AB30">
-        <v>1.61</v>
-      </c>
-      <c r="AC30">
-        <v>4.2</v>
-      </c>
-      <c r="AD30">
-        <v>1.18</v>
-      </c>
-      <c r="AE30">
-        <v>1.06</v>
-      </c>
       <c r="AF30">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AG30">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AK30">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-08-14 14:00:00</t>
+          <t>2026-08-14 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5315,27 +5315,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.21</v>
       </c>
       <c r="P31">
-        <v>2.62</v>
+        <v>4.64</v>
       </c>
       <c r="Q31">
-        <v>2.69</v>
+        <v>2.35</v>
       </c>
       <c r="R31">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S31">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="T31">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="U31">
-        <v>2.44</v>
+        <v>3.2</v>
       </c>
       <c r="V31">
+        <v>1.28</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>1.45</v>
+      </c>
+      <c r="Z31">
+        <v>2.6</v>
+      </c>
+      <c r="AA31">
+        <v>2.45</v>
+      </c>
+      <c r="AB31">
         <v>1.5</v>
       </c>
-      <c r="W31">
-        <v>1.11</v>
-      </c>
-      <c r="X31">
-        <v>1.02</v>
-      </c>
-      <c r="Y31">
-        <v>1.2</v>
-      </c>
-      <c r="Z31">
-        <v>4.2</v>
-      </c>
-      <c r="AA31">
-        <v>1.67</v>
-      </c>
-      <c r="AB31">
-        <v>2.07</v>
-      </c>
       <c r="AC31">
-        <v>2.56</v>
+        <v>4.5</v>
       </c>
       <c r="AD31">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="AE31">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>1.53</v>
+        <v>2.15</v>
       </c>
       <c r="AG31">
-        <v>2.35</v>
+        <v>1.57</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-08-14 14:00:00</t>
+          <t>2026-08-14 13:45:00</t>
         </is>
       </c>
     </row>
@@ -5478,27 +5478,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.12</v>
+        <v>1.58</v>
       </c>
       <c r="O32">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="P32">
-        <v>3.1</v>
+        <v>4.98</v>
       </c>
       <c r="Q32">
-        <v>2.57</v>
+        <v>2.14</v>
       </c>
       <c r="R32">
         <v>2.22</v>
       </c>
       <c r="S32">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T32">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="U32">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V32">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="W32">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
+        <v>1.22</v>
+      </c>
+      <c r="Z32">
+        <v>3.5</v>
+      </c>
+      <c r="AA32">
+        <v>1.75</v>
+      </c>
+      <c r="AB32">
+        <v>1.9</v>
+      </c>
+      <c r="AC32">
+        <v>2.92</v>
+      </c>
+      <c r="AD32">
+        <v>1.31</v>
+      </c>
+      <c r="AE32">
+        <v>1.12</v>
+      </c>
+      <c r="AF32">
+        <v>1.75</v>
+      </c>
+      <c r="AG32">
+        <v>1.9</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
         <v>1.17</v>
       </c>
-      <c r="Z32">
-        <v>4.4</v>
-      </c>
-      <c r="AA32">
-        <v>1.61</v>
-      </c>
-      <c r="AB32">
-        <v>2.14</v>
-      </c>
-      <c r="AC32">
-        <v>2.5</v>
-      </c>
-      <c r="AD32">
-        <v>1.47</v>
-      </c>
-      <c r="AE32">
-        <v>1.16</v>
-      </c>
-      <c r="AF32">
-        <v>1.53</v>
-      </c>
-      <c r="AG32">
-        <v>2.28</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.31</v>
-      </c>
       <c r="AK32">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-08-14 14:00:00</t>
+          <t>2026-08-14 13:50:00</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Würzburger Kickers</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
-        <v>2.65</v>
+        <v>3.34</v>
       </c>
       <c r="Q33">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="R33">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S33">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="T33">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U33">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="V33">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X33">
         <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="Z33">
-        <v>3.95</v>
+        <v>2.8</v>
       </c>
       <c r="AA33">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB33">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AC33">
-        <v>2.62</v>
+        <v>4.2</v>
       </c>
       <c r="AD33">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="AE33">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AG33">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK33">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
+        <v>2.62</v>
+      </c>
+      <c r="Q34">
+        <v>2.69</v>
+      </c>
+      <c r="R34">
         <v>2.3</v>
       </c>
-      <c r="Q34">
-        <v>2.88</v>
-      </c>
-      <c r="R34">
-        <v>2.4</v>
-      </c>
       <c r="S34">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="U34">
-        <v>2.05</v>
+        <v>2.44</v>
       </c>
       <c r="V34">
+        <v>1.5</v>
+      </c>
+      <c r="W34">
+        <v>1.11</v>
+      </c>
+      <c r="X34">
+        <v>1.02</v>
+      </c>
+      <c r="Y34">
+        <v>1.2</v>
+      </c>
+      <c r="Z34">
+        <v>4.2</v>
+      </c>
+      <c r="AA34">
         <v>1.67</v>
       </c>
-      <c r="W34">
+      <c r="AB34">
+        <v>2.07</v>
+      </c>
+      <c r="AC34">
+        <v>2.56</v>
+      </c>
+      <c r="AD34">
+        <v>1.47</v>
+      </c>
+      <c r="AE34">
         <v>1.15</v>
       </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
-      <c r="Y34">
-        <v>1.1</v>
-      </c>
-      <c r="Z34">
-        <v>5.05</v>
-      </c>
-      <c r="AA34">
-        <v>1.45</v>
-      </c>
-      <c r="AB34">
-        <v>2.55</v>
-      </c>
-      <c r="AC34">
-        <v>2.15</v>
-      </c>
-      <c r="AD34">
-        <v>1.65</v>
-      </c>
-      <c r="AE34">
-        <v>1.23</v>
-      </c>
       <c r="AF34">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AG34">
-        <v>2.64</v>
+        <v>2.35</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AK34">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P35">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q35">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="R35">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="S35">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T35">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U35">
+        <v>2.3</v>
+      </c>
+      <c r="V35">
+        <v>1.57</v>
+      </c>
+      <c r="W35">
+        <v>1.14</v>
+      </c>
+      <c r="X35">
+        <v>1.03</v>
+      </c>
+      <c r="Y35">
+        <v>1.17</v>
+      </c>
+      <c r="Z35">
+        <v>4.4</v>
+      </c>
+      <c r="AA35">
+        <v>1.61</v>
+      </c>
+      <c r="AB35">
         <v>2.14</v>
       </c>
-      <c r="V35">
-        <v>1.65</v>
-      </c>
-      <c r="W35">
-        <v>1.15</v>
-      </c>
-      <c r="X35">
-        <v>1.02</v>
-      </c>
-      <c r="Y35">
-        <v>1.15</v>
-      </c>
-      <c r="Z35">
-        <v>4.2</v>
-      </c>
-      <c r="AA35">
-        <v>1.43</v>
-      </c>
-      <c r="AB35">
-        <v>2.46</v>
-      </c>
       <c r="AC35">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AD35">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AE35">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF35">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AG35">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AK35">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Würzburger Kickers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="O36">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="Q36">
+        <v>2.8</v>
+      </c>
+      <c r="R36">
         <v>2.3</v>
       </c>
-      <c r="R36">
-        <v>2.25</v>
-      </c>
       <c r="S36">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="U36">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V36">
         <v>1.49</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
         <v>1.05</v>
       </c>
       <c r="Y36">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z36">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="AA36">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AB36">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AC36">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="AD36">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE36">
         <v>1.12</v>
       </c>
       <c r="AF36">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG36">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6298,22 +6298,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>La Roche VF</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="O37">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P37">
-        <v>2.69</v>
+        <v>2.3</v>
       </c>
       <c r="Q37">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R37">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="S37">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>2.56</v>
+        <v>3.8</v>
       </c>
       <c r="U37">
-        <v>2.96</v>
+        <v>2.05</v>
       </c>
       <c r="V37">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="Z37">
-        <v>2.97</v>
+        <v>5.05</v>
       </c>
       <c r="AA37">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AB37">
-        <v>1.69</v>
+        <v>2.55</v>
       </c>
       <c r="AC37">
-        <v>3.65</v>
+        <v>2.15</v>
       </c>
       <c r="AD37">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AE37">
-        <v>1.05</v>
+        <v>1.23</v>
       </c>
       <c r="AF37">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="AG37">
-        <v>1.85</v>
+        <v>2.64</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AK37">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6461,22 +6461,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O38">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P38">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="Q38">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="R38">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="S38">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="T38">
-        <v>2.41</v>
+        <v>3.2</v>
       </c>
       <c r="U38">
-        <v>2.9</v>
+        <v>2.14</v>
       </c>
       <c r="V38">
-        <v>1.35</v>
+        <v>1.65</v>
       </c>
       <c r="W38">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X38">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="Z38">
-        <v>2.74</v>
+        <v>4.2</v>
       </c>
       <c r="AA38">
-        <v>2.22</v>
+        <v>1.43</v>
       </c>
       <c r="AB38">
-        <v>1.63</v>
+        <v>2.46</v>
       </c>
       <c r="AC38">
-        <v>3.72</v>
+        <v>2.19</v>
       </c>
       <c r="AD38">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AE38">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AF38">
-        <v>1.84</v>
+        <v>1.4</v>
       </c>
       <c r="AG38">
-        <v>1.83</v>
+        <v>2.48</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AK38">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="O39">
+        <v>3.6</v>
+      </c>
+      <c r="P39">
+        <v>4</v>
+      </c>
+      <c r="Q39">
+        <v>2.3</v>
+      </c>
+      <c r="R39">
+        <v>2.25</v>
+      </c>
+      <c r="S39">
+        <v>1.32</v>
+      </c>
+      <c r="T39">
         <v>3.1</v>
       </c>
-      <c r="P39">
-        <v>2.6</v>
-      </c>
-      <c r="Q39">
-        <v>2.9</v>
-      </c>
-      <c r="R39">
+      <c r="U39">
+        <v>2.55</v>
+      </c>
+      <c r="V39">
+        <v>1.49</v>
+      </c>
+      <c r="W39">
+        <v>1.08</v>
+      </c>
+      <c r="X39">
+        <v>1.05</v>
+      </c>
+      <c r="Y39">
+        <v>1.18</v>
+      </c>
+      <c r="Z39">
+        <v>3.92</v>
+      </c>
+      <c r="AA39">
+        <v>1.73</v>
+      </c>
+      <c r="AB39">
         <v>2.1</v>
       </c>
-      <c r="S39">
-        <v>1.43</v>
-      </c>
-      <c r="T39">
-        <v>2.53</v>
-      </c>
-      <c r="U39">
-        <v>2.87</v>
-      </c>
-      <c r="V39">
-        <v>1.35</v>
-      </c>
-      <c r="W39">
-        <v>1.03</v>
-      </c>
-      <c r="X39">
-        <v>1.03</v>
-      </c>
-      <c r="Y39">
-        <v>1.34</v>
-      </c>
-      <c r="Z39">
-        <v>3.2</v>
-      </c>
-      <c r="AA39">
+      <c r="AC39">
+        <v>2.64</v>
+      </c>
+      <c r="AD39">
+        <v>1.44</v>
+      </c>
+      <c r="AE39">
+        <v>1.12</v>
+      </c>
+      <c r="AF39">
+        <v>1.62</v>
+      </c>
+      <c r="AG39">
         <v>2.14</v>
       </c>
-      <c r="AB39">
-        <v>1.71</v>
-      </c>
-      <c r="AC39">
-        <v>3.8</v>
-      </c>
-      <c r="AD39">
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
         <v>1.22</v>
       </c>
-      <c r="AE39">
-        <v>1.05</v>
-      </c>
-      <c r="AF39">
-        <v>1.78</v>
-      </c>
-      <c r="AG39">
-        <v>1.91</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.4</v>
-      </c>
       <c r="AK39">
-        <v>1.42</v>
+        <v>1.93</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>La Roche VF</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O40">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P40">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="Q40">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R40">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S40">
+        <v>1.42</v>
+      </c>
+      <c r="T40">
+        <v>2.59</v>
+      </c>
+      <c r="U40">
+        <v>2.91</v>
+      </c>
+      <c r="V40">
         <v>1.33</v>
       </c>
-      <c r="T40">
-        <v>3.05</v>
-      </c>
-      <c r="U40">
-        <v>2.6</v>
-      </c>
-      <c r="V40">
-        <v>1.42</v>
-      </c>
       <c r="W40">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z40">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="AA40">
-        <v>1.86</v>
+        <v>2.11</v>
       </c>
       <c r="AB40">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC40">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD40">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE40">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF40">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG40">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK40">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,65 +6992,65 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="O41">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="P41">
+        <v>3.1</v>
+      </c>
+      <c r="Q41">
         <v>2.75</v>
       </c>
-      <c r="Q41">
-        <v>2.9</v>
-      </c>
       <c r="R41">
+        <v>2.1</v>
+      </c>
+      <c r="S41">
+        <v>1.37</v>
+      </c>
+      <c r="T41">
+        <v>3.07</v>
+      </c>
+      <c r="U41">
+        <v>2.78</v>
+      </c>
+      <c r="V41">
+        <v>1.36</v>
+      </c>
+      <c r="W41">
+        <v>1.08</v>
+      </c>
+      <c r="X41">
+        <v>1.01</v>
+      </c>
+      <c r="Y41">
+        <v>1.24</v>
+      </c>
+      <c r="Z41">
+        <v>3.34</v>
+      </c>
+      <c r="AA41">
+        <v>1.88</v>
+      </c>
+      <c r="AB41">
+        <v>1.91</v>
+      </c>
+      <c r="AC41">
+        <v>3.3</v>
+      </c>
+      <c r="AD41">
+        <v>1.29</v>
+      </c>
+      <c r="AE41">
+        <v>1.06</v>
+      </c>
+      <c r="AF41">
+        <v>1.65</v>
+      </c>
+      <c r="AG41">
         <v>2.05</v>
       </c>
-      <c r="S41">
-        <v>1.4</v>
-      </c>
-      <c r="T41">
-        <v>2.47</v>
-      </c>
-      <c r="U41">
-        <v>3.06</v>
-      </c>
-      <c r="V41">
-        <v>1.31</v>
-      </c>
-      <c r="W41">
-        <v>1.04</v>
-      </c>
-      <c r="X41">
-        <v>1.06</v>
-      </c>
-      <c r="Y41">
-        <v>1.32</v>
-      </c>
-      <c r="Z41">
-        <v>3</v>
-      </c>
-      <c r="AA41">
-        <v>2.04</v>
-      </c>
-      <c r="AB41">
-        <v>1.68</v>
-      </c>
-      <c r="AC41">
-        <v>3.9</v>
-      </c>
-      <c r="AD41">
-        <v>1.22</v>
-      </c>
-      <c r="AE41">
-        <v>1.05</v>
-      </c>
-      <c r="AF41">
-        <v>1.75</v>
-      </c>
-      <c r="AG41">
-        <v>1.91</v>
-      </c>
       <c r="AH41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="O42">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="P42">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q42">
-        <v>2.36</v>
+        <v>3.17</v>
       </c>
       <c r="R42">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="S42">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T42">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="U42">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="V42">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W42">
         <v>1.04</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
+        <v>1.33</v>
+      </c>
+      <c r="Z42">
+        <v>3</v>
+      </c>
+      <c r="AA42">
+        <v>2.1</v>
+      </c>
+      <c r="AB42">
+        <v>1.65</v>
+      </c>
+      <c r="AC42">
+        <v>3.68</v>
+      </c>
+      <c r="AD42">
         <v>1.28</v>
       </c>
-      <c r="Z42">
-        <v>3.05</v>
-      </c>
-      <c r="AA42">
-        <v>1.99</v>
-      </c>
-      <c r="AB42">
-        <v>1.77</v>
-      </c>
-      <c r="AC42">
-        <v>3.28</v>
-      </c>
-      <c r="AD42">
-        <v>1.25</v>
-      </c>
       <c r="AE42">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF42">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG42">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7321,28 +7321,28 @@
         <v>1.82</v>
       </c>
       <c r="O43">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P43">
         <v>3.9</v>
       </c>
       <c r="Q43">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R43">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="S43">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T43">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="U43">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="V43">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W43">
         <v>1.08</v>
@@ -7360,10 +7360,10 @@
         <v>1.93</v>
       </c>
       <c r="AB43">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC43">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD43">
         <v>1.3</v>
@@ -7372,10 +7372,10 @@
         <v>1.07</v>
       </c>
       <c r="AF43">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AG43">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,65 +7481,65 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.99</v>
+        <v>2.6</v>
       </c>
       <c r="O44">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P44">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="Q44">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R44">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S44">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T44">
-        <v>2.86</v>
+        <v>2.53</v>
       </c>
       <c r="U44">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="V44">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W44">
         <v>1.05</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z44">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA44">
+        <v>1.97</v>
+      </c>
+      <c r="AB44">
+        <v>1.74</v>
+      </c>
+      <c r="AC44">
+        <v>3.72</v>
+      </c>
+      <c r="AD44">
+        <v>1.25</v>
+      </c>
+      <c r="AE44">
+        <v>1.06</v>
+      </c>
+      <c r="AF44">
+        <v>1.73</v>
+      </c>
+      <c r="AG44">
         <v>2</v>
       </c>
-      <c r="AB44">
-        <v>1.69</v>
-      </c>
-      <c r="AC44">
-        <v>3.9</v>
-      </c>
-      <c r="AD44">
-        <v>1.27</v>
-      </c>
-      <c r="AE44">
-        <v>1.04</v>
-      </c>
-      <c r="AF44">
-        <v>1.81</v>
-      </c>
-      <c r="AG44">
-        <v>1.85</v>
-      </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK44">
-        <v>1.69</v>
+        <v>1.36</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O45">
         <v>3.1</v>
       </c>
       <c r="P45">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q45">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R45">
         <v>2.1</v>
       </c>
       <c r="S45">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T45">
         <v>2.5</v>
       </c>
       <c r="U45">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="V45">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W45">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X45">
         <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z45">
-        <v>2.97</v>
+        <v>3.22</v>
       </c>
       <c r="AA45">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AB45">
         <v>1.71</v>
       </c>
       <c r="AC45">
-        <v>3.69</v>
+        <v>3.8</v>
       </c>
       <c r="AD45">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE45">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF45">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG45">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AK45">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.43</v>
+        <v>1.74</v>
       </c>
       <c r="O46">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P46">
+        <v>4.4</v>
+      </c>
+      <c r="Q46">
+        <v>2.5</v>
+      </c>
+      <c r="R46">
         <v>2.1</v>
       </c>
-      <c r="Q46">
-        <v>0</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O47">
+        <v>3.2</v>
+      </c>
+      <c r="P47">
+        <v>3.3</v>
+      </c>
+      <c r="Q47">
+        <v>2.36</v>
+      </c>
+      <c r="R47">
+        <v>2.03</v>
+      </c>
+      <c r="S47">
+        <v>1.36</v>
+      </c>
+      <c r="T47">
         <v>2.8</v>
       </c>
-      <c r="P47">
+      <c r="U47">
         <v>2.7</v>
       </c>
-      <c r="Q47">
-        <v>3.54</v>
-      </c>
-      <c r="R47">
+      <c r="V47">
+        <v>1.36</v>
+      </c>
+      <c r="W47">
+        <v>1.05</v>
+      </c>
+      <c r="X47">
+        <v>1.01</v>
+      </c>
+      <c r="Y47">
+        <v>1.28</v>
+      </c>
+      <c r="Z47">
+        <v>3.08</v>
+      </c>
+      <c r="AA47">
+        <v>1.99</v>
+      </c>
+      <c r="AB47">
         <v>1.77</v>
       </c>
-      <c r="S47">
-        <v>1.63</v>
-      </c>
-      <c r="T47">
-        <v>2.13</v>
-      </c>
-      <c r="U47">
-        <v>4.2</v>
-      </c>
-      <c r="V47">
-        <v>1.16</v>
-      </c>
-      <c r="W47">
-        <v>1.03</v>
-      </c>
-      <c r="X47">
-        <v>1.08</v>
-      </c>
-      <c r="Y47">
-        <v>1.65</v>
-      </c>
-      <c r="Z47">
-        <v>2.11</v>
-      </c>
-      <c r="AA47">
-        <v>2.97</v>
-      </c>
-      <c r="AB47">
-        <v>1.3</v>
-      </c>
       <c r="AC47">
-        <v>6.55</v>
+        <v>3.52</v>
       </c>
       <c r="AD47">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="AE47">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AF47">
-        <v>2.34</v>
+        <v>1.75</v>
       </c>
       <c r="AG47">
-        <v>1.52</v>
+        <v>1.86</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="AK47">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="O48">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="P48">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="Q48">
-        <v>2.49</v>
+        <v>3.01</v>
       </c>
       <c r="R48">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="S48">
+        <v>1.45</v>
+      </c>
+      <c r="T48">
+        <v>2.41</v>
+      </c>
+      <c r="U48">
+        <v>3.3</v>
+      </c>
+      <c r="V48">
+        <v>1.29</v>
+      </c>
+      <c r="W48">
+        <v>1.04</v>
+      </c>
+      <c r="X48">
+        <v>1.05</v>
+      </c>
+      <c r="Y48">
+        <v>1.36</v>
+      </c>
+      <c r="Z48">
+        <v>3.06</v>
+      </c>
+      <c r="AA48">
+        <v>2.23</v>
+      </c>
+      <c r="AB48">
+        <v>1.62</v>
+      </c>
+      <c r="AC48">
+        <v>3.74</v>
+      </c>
+      <c r="AD48">
+        <v>1.17</v>
+      </c>
+      <c r="AE48">
+        <v>1.03</v>
+      </c>
+      <c r="AF48">
+        <v>1.86</v>
+      </c>
+      <c r="AG48">
+        <v>1.83</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
         <v>1.3</v>
       </c>
-      <c r="T48">
-        <v>3.22</v>
-      </c>
-      <c r="U48">
-        <v>2.38</v>
-      </c>
-      <c r="V48">
-        <v>1.53</v>
-      </c>
-      <c r="W48">
-        <v>1.12</v>
-      </c>
-      <c r="X48">
-        <v>1.04</v>
-      </c>
-      <c r="Y48">
-        <v>1.2</v>
-      </c>
-      <c r="Z48">
-        <v>4.25</v>
-      </c>
-      <c r="AA48">
-        <v>1.62</v>
-      </c>
-      <c r="AB48">
-        <v>2.2</v>
-      </c>
-      <c r="AC48">
-        <v>2.5</v>
-      </c>
-      <c r="AD48">
-        <v>1.44</v>
-      </c>
-      <c r="AE48">
-        <v>1.16</v>
-      </c>
-      <c r="AF48">
-        <v>1.55</v>
-      </c>
-      <c r="AG48">
-        <v>2.4</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.28</v>
-      </c>
       <c r="AK48">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="O49">
-        <v>3.21</v>
+        <v>3.65</v>
       </c>
       <c r="P49">
-        <v>4.64</v>
+        <v>2.92</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-08-14 14:15:00</t>
+          <t>2026-08-14 14:00:00</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8791,7 @@
         <v>3.2</v>
       </c>
       <c r="P52">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q52">
         <v>2.75</v>
@@ -8818,16 +8818,16 @@
         <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z52">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="AA52">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB52">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC52">
         <v>3.84</v>
@@ -8836,7 +8836,7 @@
         <v>1.22</v>
       </c>
       <c r="AE52">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF52">
         <v>1.85</v>
@@ -8858,7 +8858,7 @@
         <v>1.26</v>
       </c>
       <c r="AK52">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="O56">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="P56">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q56">
         <v>1.36</v>
@@ -9452,49 +9452,49 @@
         <v>3.5</v>
       </c>
       <c r="S56">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T56">
         <v>5</v>
       </c>
       <c r="U56">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="V56">
         <v>1.96</v>
       </c>
       <c r="W56">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X56">
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="Z56">
         <v>7.5</v>
       </c>
       <c r="AA56">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AB56">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="AC56">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AD56">
         <v>1.97</v>
       </c>
       <c r="AE56">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AF56">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AG56">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.01</v>
       </c>
       <c r="AK56">
-        <v>6.45</v>
+        <v>6.1</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -12371,28 +12371,28 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="O74">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P74">
-        <v>4.8</v>
+        <v>4.92</v>
       </c>
       <c r="Q74">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="R74">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S74">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T74">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U74">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="V74">
         <v>1.51</v>
@@ -12401,34 +12401,34 @@
         <v>1.1</v>
       </c>
       <c r="X74">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y74">
         <v>1.2</v>
       </c>
       <c r="Z74">
-        <v>4.69</v>
+        <v>4.33</v>
       </c>
       <c r="AA74">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB74">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC74">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AD74">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE74">
         <v>1.17</v>
       </c>
       <c r="AF74">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG74">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12706,16 +12706,16 @@
         <v>3.17</v>
       </c>
       <c r="Q76">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="R76">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="S76">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T76">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="U76">
         <v>3.05</v>
@@ -12730,13 +12730,13 @@
         <v>1.04</v>
       </c>
       <c r="Y76">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z76">
         <v>2.88</v>
       </c>
       <c r="AA76">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB76">
         <v>1.67</v>
@@ -12748,10 +12748,10 @@
         <v>1.2</v>
       </c>
       <c r="AE76">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF76">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG76">
         <v>1.85</v>
@@ -12770,7 +12770,7 @@
         <v>1.3</v>
       </c>
       <c r="AK76">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="O84">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P84">
-        <v>4.2</v>
+        <v>6.1</v>
       </c>
       <c r="Q84">
-        <v>2.41</v>
+        <v>2</v>
       </c>
       <c r="R84">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="S84">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T84">
-        <v>2.79</v>
+        <v>3.25</v>
       </c>
       <c r="U84">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="V84">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="W84">
         <v>1.08</v>
       </c>
       <c r="X84">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y84">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="Z84">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="AA84">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AB84">
-        <v>1.82</v>
+        <v>2.18</v>
       </c>
       <c r="AC84">
-        <v>3.35</v>
+        <v>2.45</v>
       </c>
       <c r="AD84">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="AE84">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF84">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AG84">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK84">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="O85">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="P85">
-        <v>6.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q85">
-        <v>2</v>
+        <v>2.41</v>
       </c>
       <c r="R85">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="S85">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T85">
-        <v>3.25</v>
+        <v>2.79</v>
       </c>
       <c r="U85">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="V85">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="W85">
         <v>1.08</v>
       </c>
       <c r="X85">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y85">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="Z85">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA85">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AB85">
-        <v>2.18</v>
+        <v>1.82</v>
       </c>
       <c r="AC85">
-        <v>2.45</v>
+        <v>3.35</v>
       </c>
       <c r="AD85">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AE85">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF85">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AG85">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK85">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -15151,22 +15151,22 @@
         <v>2.8</v>
       </c>
       <c r="Q91">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="R91">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S91">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T91">
         <v>2.6</v>
       </c>
       <c r="U91">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="V91">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W91">
         <v>1.06</v>
@@ -15175,31 +15175,31 @@
         <v>1.08</v>
       </c>
       <c r="Y91">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z91">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AA91">
         <v>2.25</v>
       </c>
       <c r="AB91">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AC91">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AD91">
         <v>1.17</v>
       </c>
       <c r="AE91">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF91">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG91">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK91">
         <v>1.43</v>
@@ -16449,31 +16449,31 @@
         <v>1.18</v>
       </c>
       <c r="O99">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="P99">
-        <v>13</v>
+        <v>11.28</v>
       </c>
       <c r="Q99">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="R99">
+        <v>2.55</v>
+      </c>
+      <c r="S99">
+        <v>1.2</v>
+      </c>
+      <c r="T99">
         <v>2.7</v>
       </c>
-      <c r="S99">
-        <v>1.22</v>
-      </c>
-      <c r="T99">
-        <v>2.63</v>
-      </c>
       <c r="U99">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="V99">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="W99">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X99">
         <v>1.02</v>
@@ -16482,28 +16482,28 @@
         <v>1.2</v>
       </c>
       <c r="Z99">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA99">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB99">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC99">
         <v>2.55</v>
       </c>
       <c r="AD99">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE99">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF99">
         <v>2.38</v>
       </c>
       <c r="AG99">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="O103">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="P103">
-        <v>2.95</v>
+        <v>4.05</v>
       </c>
       <c r="Q103">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="R103">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S103">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T103">
-        <v>3.02</v>
+        <v>3.6</v>
       </c>
       <c r="U103">
-        <v>2.06</v>
+        <v>2.35</v>
       </c>
       <c r="V103">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W103">
         <v>1.11</v>
       </c>
       <c r="X103">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z103">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="AA103">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB103">
-        <v>2.01</v>
+        <v>2.14</v>
       </c>
       <c r="AC103">
-        <v>2.74</v>
+        <v>2.51</v>
       </c>
       <c r="AD103">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE103">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF103">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG103">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AK103">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="O104">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="P104">
-        <v>4.05</v>
+        <v>2.95</v>
       </c>
       <c r="Q104">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="R104">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S104">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T104">
-        <v>3.6</v>
+        <v>3.02</v>
       </c>
       <c r="U104">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="V104">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W104">
         <v>1.11</v>
       </c>
       <c r="X104">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y104">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z104">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="AA104">
+        <v>1.7</v>
+      </c>
+      <c r="AB104">
+        <v>2.01</v>
+      </c>
+      <c r="AC104">
+        <v>2.74</v>
+      </c>
+      <c r="AD104">
+        <v>1.38</v>
+      </c>
+      <c r="AE104">
+        <v>1.1</v>
+      </c>
+      <c r="AF104">
         <v>1.62</v>
       </c>
-      <c r="AB104">
-        <v>2.14</v>
-      </c>
-      <c r="AC104">
-        <v>2.51</v>
-      </c>
-      <c r="AD104">
-        <v>1.44</v>
-      </c>
-      <c r="AE104">
-        <v>1.13</v>
-      </c>
-      <c r="AF104">
-        <v>1.57</v>
-      </c>
       <c r="AG104">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AK104">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AL104">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -615,13 +615,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -631,7 +631,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -701,7 +701,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "32"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,51 +775,51 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>3.75</v>
+        <v>4.32</v>
       </c>
       <c r="O3">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="Q3">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R3">
         <v>2</v>
       </c>
       <c r="S3">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="T3">
         <v>2.6</v>
       </c>
       <c r="U3">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="V3">
         <v>1.3</v>
@@ -828,77 +828,77 @@
         <v>1.02</v>
       </c>
       <c r="X3">
+        <v>1.03</v>
+      </c>
+      <c r="Y3">
+        <v>1.37</v>
+      </c>
+      <c r="Z3">
+        <v>2.68</v>
+      </c>
+      <c r="AA3">
+        <v>2.21</v>
+      </c>
+      <c r="AB3">
+        <v>1.56</v>
+      </c>
+      <c r="AC3">
+        <v>4.45</v>
+      </c>
+      <c r="AD3">
+        <v>1.18</v>
+      </c>
+      <c r="AE3">
         <v>1.04</v>
       </c>
-      <c r="Y3">
-        <v>1.4</v>
-      </c>
-      <c r="Z3">
-        <v>2.65</v>
-      </c>
-      <c r="AA3">
-        <v>2.33</v>
-      </c>
-      <c r="AB3">
-        <v>1.57</v>
-      </c>
-      <c r="AC3">
-        <v>4.71</v>
-      </c>
-      <c r="AD3">
-        <v>1.17</v>
-      </c>
-      <c r="AE3">
-        <v>1.02</v>
-      </c>
       <c r="AF3">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AG3">
         <v>1.73</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "65", "82"]</t>
         </is>
       </c>
       <c r="AJ3">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="O5">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P5">
-        <v>2</v>
+        <v>5.13</v>
       </c>
       <c r="Q5">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="R5">
-        <v>2.45</v>
+        <v>2.96</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T5">
-        <v>3.36</v>
+        <v>4.8</v>
       </c>
       <c r="U5">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="V5">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z5">
-        <v>4.5</v>
+        <v>6.82</v>
       </c>
       <c r="AA5">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AB5">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="AC5">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AD5">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AE5">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AF5">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG5">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK5">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="O6">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>5.13</v>
+        <v>2</v>
       </c>
       <c r="Q6">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="R6">
-        <v>2.96</v>
+        <v>2.45</v>
       </c>
       <c r="S6">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>4.8</v>
+        <v>3.36</v>
       </c>
       <c r="U6">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="V6">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="W6">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>6.82</v>
+        <v>4.5</v>
       </c>
       <c r="AA6">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AB6">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC6">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AD6">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AE6">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AF6">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AG6">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
+        <v>2.5</v>
+      </c>
+      <c r="O41">
+        <v>3</v>
+      </c>
+      <c r="P41">
+        <v>2.55</v>
+      </c>
+      <c r="Q41">
+        <v>3.17</v>
+      </c>
+      <c r="R41">
+        <v>1.96</v>
+      </c>
+      <c r="S41">
+        <v>1.4</v>
+      </c>
+      <c r="T41">
+        <v>2.54</v>
+      </c>
+      <c r="U41">
+        <v>3.05</v>
+      </c>
+      <c r="V41">
+        <v>1.31</v>
+      </c>
+      <c r="W41">
+        <v>1.04</v>
+      </c>
+      <c r="X41">
+        <v>1.03</v>
+      </c>
+      <c r="Y41">
+        <v>1.33</v>
+      </c>
+      <c r="Z41">
+        <v>3</v>
+      </c>
+      <c r="AA41">
         <v>2.1</v>
       </c>
-      <c r="O41">
-        <v>3.25</v>
-      </c>
-      <c r="P41">
-        <v>3.1</v>
-      </c>
-      <c r="Q41">
-        <v>2.75</v>
-      </c>
-      <c r="R41">
-        <v>2.1</v>
-      </c>
-      <c r="S41">
-        <v>1.37</v>
-      </c>
-      <c r="T41">
-        <v>3.07</v>
-      </c>
-      <c r="U41">
-        <v>2.78</v>
-      </c>
-      <c r="V41">
-        <v>1.36</v>
-      </c>
-      <c r="W41">
-        <v>1.08</v>
-      </c>
-      <c r="X41">
-        <v>1.01</v>
-      </c>
-      <c r="Y41">
-        <v>1.24</v>
-      </c>
-      <c r="Z41">
-        <v>3.34</v>
-      </c>
-      <c r="AA41">
-        <v>1.88</v>
-      </c>
       <c r="AB41">
+        <v>1.65</v>
+      </c>
+      <c r="AC41">
+        <v>3.68</v>
+      </c>
+      <c r="AD41">
+        <v>1.28</v>
+      </c>
+      <c r="AE41">
+        <v>1.04</v>
+      </c>
+      <c r="AF41">
+        <v>1.75</v>
+      </c>
+      <c r="AG41">
         <v>1.91</v>
-      </c>
-      <c r="AC41">
-        <v>3.3</v>
-      </c>
-      <c r="AD41">
-        <v>1.29</v>
-      </c>
-      <c r="AE41">
-        <v>1.06</v>
-      </c>
-      <c r="AF41">
-        <v>1.65</v>
-      </c>
-      <c r="AG41">
-        <v>2.05</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.29</v>
       </c>
       <c r="AK41">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O42">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P42">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q42">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="R42">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="S42">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T42">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="U42">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="V42">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W42">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X42">
         <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z42">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AA42">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB42">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AC42">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="AD42">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE42">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF42">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG42">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK42">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.82</v>
+        <v>2.65</v>
       </c>
       <c r="O43">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P43">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q43">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="R43">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="S43">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T43">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U43">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="V43">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="W43">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X43">
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="Z43">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="AA43">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AB43">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AC43">
-        <v>3.14</v>
+        <v>3.8</v>
       </c>
       <c r="AD43">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE43">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF43">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG43">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AK43">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="O44">
         <v>3.1</v>
       </c>
       <c r="P44">
-        <v>2.45</v>
+        <v>2.87</v>
       </c>
       <c r="Q44">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="R44">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S44">
+        <v>1.45</v>
+      </c>
+      <c r="T44">
+        <v>2.41</v>
+      </c>
+      <c r="U44">
+        <v>3.3</v>
+      </c>
+      <c r="V44">
+        <v>1.29</v>
+      </c>
+      <c r="W44">
+        <v>1.04</v>
+      </c>
+      <c r="X44">
+        <v>1.05</v>
+      </c>
+      <c r="Y44">
         <v>1.36</v>
       </c>
-      <c r="T44">
-        <v>2.53</v>
-      </c>
-      <c r="U44">
-        <v>2.88</v>
-      </c>
-      <c r="V44">
-        <v>1.34</v>
-      </c>
-      <c r="W44">
-        <v>1.05</v>
-      </c>
-      <c r="X44">
+      <c r="Z44">
+        <v>3.06</v>
+      </c>
+      <c r="AA44">
+        <v>2.23</v>
+      </c>
+      <c r="AB44">
+        <v>1.62</v>
+      </c>
+      <c r="AC44">
+        <v>3.74</v>
+      </c>
+      <c r="AD44">
+        <v>1.17</v>
+      </c>
+      <c r="AE44">
         <v>1.03</v>
       </c>
-      <c r="Y44">
-        <v>1.29</v>
-      </c>
-      <c r="Z44">
-        <v>3.2</v>
-      </c>
-      <c r="AA44">
-        <v>1.97</v>
-      </c>
-      <c r="AB44">
-        <v>1.74</v>
-      </c>
-      <c r="AC44">
-        <v>3.72</v>
-      </c>
-      <c r="AD44">
-        <v>1.25</v>
-      </c>
-      <c r="AE44">
-        <v>1.06</v>
-      </c>
       <c r="AF44">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AG44">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="O45">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P45">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q45">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="R45">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="S45">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T45">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="U45">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="V45">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W45">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z45">
-        <v>3.22</v>
+        <v>3.08</v>
       </c>
       <c r="AA45">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AB45">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AC45">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="AD45">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE45">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF45">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG45">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AK45">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="O46">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P46">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q46">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R46">
         <v>2.1</v>
       </c>
       <c r="S46">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T46">
-        <v>2.7</v>
+        <v>3.07</v>
       </c>
       <c r="U46">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="V46">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W46">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X46">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z46">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AA46">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AB46">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AC46">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AD46">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE46">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF46">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AG46">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK46">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,52 +7970,52 @@
         </is>
       </c>
       <c r="N47">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="O47">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P47">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q47">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="R47">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="S47">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T47">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U47">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="V47">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W47">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y47">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z47">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA47">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AB47">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AC47">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="AD47">
         <v>1.28</v>
@@ -8024,10 +8024,10 @@
         <v>1.1</v>
       </c>
       <c r="AF47">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG47">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="O48">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="P48">
-        <v>2.87</v>
+        <v>3.9</v>
       </c>
       <c r="Q48">
-        <v>3.01</v>
+        <v>2.4</v>
       </c>
       <c r="R48">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="S48">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T48">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="U48">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="V48">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="W48">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z48">
-        <v>3.06</v>
+        <v>3.25</v>
       </c>
       <c r="AA48">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="AB48">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AC48">
-        <v>3.74</v>
+        <v>3.14</v>
       </c>
       <c r="AD48">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AE48">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF48">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AG48">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK48">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="O68">
-        <v>4.45</v>
+        <v>3.7</v>
       </c>
       <c r="P68">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q68">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="R68">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S68">
+        <v>1.25</v>
+      </c>
+      <c r="T68">
+        <v>3.5</v>
+      </c>
+      <c r="U68">
+        <v>2.31</v>
+      </c>
+      <c r="V68">
+        <v>1.53</v>
+      </c>
+      <c r="W68">
+        <v>1.09</v>
+      </c>
+      <c r="X68">
+        <v>1.03</v>
+      </c>
+      <c r="Y68">
+        <v>1.17</v>
+      </c>
+      <c r="Z68">
+        <v>4.65</v>
+      </c>
+      <c r="AA68">
+        <v>1.56</v>
+      </c>
+      <c r="AB68">
+        <v>2.3</v>
+      </c>
+      <c r="AC68">
+        <v>2.4</v>
+      </c>
+      <c r="AD68">
+        <v>1.53</v>
+      </c>
+      <c r="AE68">
         <v>1.2</v>
       </c>
-      <c r="T68">
-        <v>3.9</v>
-      </c>
-      <c r="U68">
-        <v>2.18</v>
-      </c>
-      <c r="V68">
-        <v>1.64</v>
-      </c>
-      <c r="W68">
-        <v>1.15</v>
-      </c>
-      <c r="X68">
-        <v>1.02</v>
-      </c>
-      <c r="Y68">
-        <v>1.1</v>
-      </c>
-      <c r="Z68">
-        <v>5.1</v>
-      </c>
-      <c r="AA68">
-        <v>1.42</v>
-      </c>
-      <c r="AB68">
-        <v>2.49</v>
-      </c>
-      <c r="AC68">
-        <v>2.14</v>
-      </c>
-      <c r="AD68">
-        <v>1.67</v>
-      </c>
-      <c r="AE68">
-        <v>1.25</v>
-      </c>
       <c r="AF68">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG68">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK68">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,80 +11556,80 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="O69">
-        <v>3.7</v>
+        <v>4.45</v>
       </c>
       <c r="P69">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="Q69">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="R69">
+        <v>2.5</v>
+      </c>
+      <c r="S69">
+        <v>1.2</v>
+      </c>
+      <c r="T69">
+        <v>3.9</v>
+      </c>
+      <c r="U69">
+        <v>2.18</v>
+      </c>
+      <c r="V69">
+        <v>1.64</v>
+      </c>
+      <c r="W69">
+        <v>1.15</v>
+      </c>
+      <c r="X69">
+        <v>1.02</v>
+      </c>
+      <c r="Y69">
+        <v>1.1</v>
+      </c>
+      <c r="Z69">
+        <v>5.1</v>
+      </c>
+      <c r="AA69">
+        <v>1.42</v>
+      </c>
+      <c r="AB69">
+        <v>2.49</v>
+      </c>
+      <c r="AC69">
+        <v>2.14</v>
+      </c>
+      <c r="AD69">
+        <v>1.67</v>
+      </c>
+      <c r="AE69">
+        <v>1.25</v>
+      </c>
+      <c r="AF69">
+        <v>1.55</v>
+      </c>
+      <c r="AG69">
         <v>2.3</v>
       </c>
-      <c r="S69">
-        <v>1.25</v>
-      </c>
-      <c r="T69">
-        <v>3.5</v>
-      </c>
-      <c r="U69">
-        <v>2.31</v>
-      </c>
-      <c r="V69">
-        <v>1.53</v>
-      </c>
-      <c r="W69">
-        <v>1.09</v>
-      </c>
-      <c r="X69">
-        <v>1.03</v>
-      </c>
-      <c r="Y69">
-        <v>1.17</v>
-      </c>
-      <c r="Z69">
-        <v>4.65</v>
-      </c>
-      <c r="AA69">
-        <v>1.56</v>
-      </c>
-      <c r="AB69">
-        <v>2.3</v>
-      </c>
-      <c r="AC69">
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
+        <v>1.16</v>
+      </c>
+      <c r="AK69">
         <v>2.4</v>
-      </c>
-      <c r="AD69">
-        <v>1.53</v>
-      </c>
-      <c r="AE69">
-        <v>1.2</v>
-      </c>
-      <c r="AF69">
-        <v>1.5</v>
-      </c>
-      <c r="AG69">
-        <v>2.38</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>1.2</v>
-      </c>
-      <c r="AK69">
-        <v>1.95</v>
       </c>
       <c r="AL69">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -950,118 +950,118 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="O4">
         <v>3.9</v>
       </c>
       <c r="P4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Q4">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="R4">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="S4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="U4">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="V4">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
         <v>1.2</v>
       </c>
       <c r="Z4">
-        <v>4.33</v>
+        <v>3.58</v>
       </c>
       <c r="AA4">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB4">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC4">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AD4">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG4">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["49", "67"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50"]</t>
         </is>
       </c>
       <c r="AJ4">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK4">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,57 +1101,57 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="O5">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="P5">
-        <v>5.13</v>
+        <v>5.85</v>
       </c>
       <c r="Q5">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="R5">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="S5">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T5">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="U5">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V5">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="W5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X5">
         <v>1.01</v>
@@ -1160,71 +1160,71 @@
         <v>1.11</v>
       </c>
       <c r="Z5">
-        <v>6.82</v>
+        <v>7.12</v>
       </c>
       <c r="AA5">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB5">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AC5">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AD5">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AE5">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF5">
         <v>1.5</v>
       </c>
       <c r="AG5">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "12", "65"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13"]</t>
         </is>
       </c>
       <c r="AJ5">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AK5">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,130 +1264,130 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>3.2</v>
+        <v>2.43</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P6">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q6">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="R6">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S6">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T6">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="U6">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V6">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z6">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA6">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AB6">
+        <v>2.4</v>
+      </c>
+      <c r="AC6">
         <v>2.3</v>
       </c>
-      <c r="AC6">
+      <c r="AD6">
+        <v>1.57</v>
+      </c>
+      <c r="AE6">
+        <v>1.19</v>
+      </c>
+      <c r="AF6">
+        <v>1.44</v>
+      </c>
+      <c r="AG6">
         <v>2.4</v>
       </c>
-      <c r="AD6">
-        <v>1.53</v>
-      </c>
-      <c r="AE6">
-        <v>1.16</v>
-      </c>
-      <c r="AF6">
-        <v>1.45</v>
-      </c>
-      <c r="AG6">
-        <v>2.5</v>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "75"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50", "55", "59"]</t>
         </is>
       </c>
       <c r="AJ6">
         <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1446,111 +1446,111 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O7">
+        <v>2.95</v>
+      </c>
+      <c r="P7">
+        <v>3.7</v>
+      </c>
+      <c r="Q7">
+        <v>2.79</v>
+      </c>
+      <c r="R7">
+        <v>1.9</v>
+      </c>
+      <c r="S7">
+        <v>1.5</v>
+      </c>
+      <c r="T7">
+        <v>2.39</v>
+      </c>
+      <c r="U7">
         <v>3.35</v>
       </c>
-      <c r="P7">
-        <v>2.8</v>
-      </c>
-      <c r="Q7">
-        <v>2.63</v>
-      </c>
-      <c r="R7">
-        <v>2.05</v>
-      </c>
-      <c r="S7">
-        <v>1.38</v>
-      </c>
-      <c r="T7">
-        <v>2.99</v>
-      </c>
-      <c r="U7">
-        <v>2.81</v>
-      </c>
       <c r="V7">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="W7">
         <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
+        <v>1.39</v>
+      </c>
+      <c r="Z7">
+        <v>2.5</v>
+      </c>
+      <c r="AA7">
+        <v>2.25</v>
+      </c>
+      <c r="AB7">
+        <v>1.53</v>
+      </c>
+      <c r="AC7">
+        <v>4.2</v>
+      </c>
+      <c r="AD7">
+        <v>1.14</v>
+      </c>
+      <c r="AE7">
+        <v>1.11</v>
+      </c>
+      <c r="AF7">
+        <v>2</v>
+      </c>
+      <c r="AG7">
+        <v>1.75</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7">
         <v>1.25</v>
       </c>
-      <c r="Z7">
-        <v>3.4</v>
-      </c>
-      <c r="AA7">
-        <v>1.95</v>
-      </c>
-      <c r="AB7">
-        <v>1.8</v>
-      </c>
-      <c r="AC7">
-        <v>3.35</v>
-      </c>
-      <c r="AD7">
-        <v>1.26</v>
-      </c>
-      <c r="AE7">
-        <v>1.12</v>
-      </c>
-      <c r="AF7">
-        <v>1.75</v>
-      </c>
-      <c r="AG7">
-        <v>2</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7">
-        <v>1.3</v>
-      </c>
       <c r="AK7">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1616,46 +1616,46 @@
         <v>1.36</v>
       </c>
       <c r="O8">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="P8">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="Q8">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="R8">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S8">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
         <v>3.25</v>
       </c>
       <c r="U8">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="V8">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z8">
         <v>3.84</v>
       </c>
       <c r="AA8">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB8">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC8">
         <v>2.78</v>
@@ -1664,13 +1664,13 @@
         <v>1.41</v>
       </c>
       <c r="AE8">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
         <v>1.95</v>
       </c>
       <c r="AG8">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.06</v>
       </c>
       <c r="AK8">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1753,130 +1753,130 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>2.96</v>
+        <v>2.85</v>
       </c>
       <c r="O9">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P9">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="Q9">
-        <v>3.84</v>
+        <v>3.68</v>
       </c>
       <c r="R9">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S9">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T9">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="U9">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="V9">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W9">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z9">
-        <v>4.21</v>
+        <v>3.68</v>
       </c>
       <c r="AA9">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AB9">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AC9">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AD9">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE9">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF9">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG9">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["62"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3"]</t>
         </is>
       </c>
       <c r="AJ9">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AK9">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -2105,61 +2105,61 @@
         <v>1.36</v>
       </c>
       <c r="O11">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P11">
-        <v>8.550000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="Q11">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S11">
         <v>1.48</v>
       </c>
       <c r="T11">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U11">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="V11">
         <v>1.28</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z11">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AA11">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AB11">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AC11">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AD11">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF11">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="AG11">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK11">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
-        <v>4.89</v>
+        <v>3.4</v>
       </c>
       <c r="Q12">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="R12">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S12">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T12">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U12">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="V12">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z12">
-        <v>2.97</v>
+        <v>3.24</v>
       </c>
       <c r="AA12">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB12">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AC12">
-        <v>3.54</v>
+        <v>3.31</v>
       </c>
       <c r="AD12">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE12">
         <v>1.07</v>
       </c>
       <c r="AF12">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG12">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2594,58 +2594,58 @@
         <v>1.95</v>
       </c>
       <c r="O14">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>3.62</v>
+        <v>3.95</v>
       </c>
       <c r="Q14">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R14">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="S14">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T14">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U14">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V14">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W14">
         <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
         <v>1.4</v>
       </c>
       <c r="Z14">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="AA14">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB14">
         <v>1.6</v>
       </c>
       <c r="AC14">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AD14">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE14">
         <v>1.04</v>
       </c>
       <c r="AF14">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG14">
         <v>1.75</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK14">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2766,19 +2766,19 @@
         <v>2.4</v>
       </c>
       <c r="R15">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S15">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T15">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="U15">
         <v>3.2</v>
       </c>
       <c r="V15">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W15">
         <v>1.05</v>
@@ -2787,31 +2787,31 @@
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z15">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="AA15">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AB15">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AC15">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="AD15">
         <v>1.18</v>
       </c>
       <c r="AE15">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AG15">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.12</v>
       </c>
       <c r="AK15">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O18">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P18">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q18">
         <v>2.25</v>
       </c>
       <c r="R18">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U18">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="V18">
         <v>1.62</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA18">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB18">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AC18">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AD18">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF18">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AG18">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="O21">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="P21">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="O22">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="P22">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Q22">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="R22">
         <v>2.24</v>
       </c>
       <c r="S22">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T22">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="U22">
         <v>2.62</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK22">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,55 +4058,55 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="O23">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P23">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q23">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R23">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S23">
         <v>1.25</v>
       </c>
       <c r="T23">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="U23">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="V23">
         <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z23">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AA23">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB23">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AC23">
         <v>2.63</v>
       </c>
       <c r="AD23">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE23">
         <v>1.17</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK23">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O24">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q24">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="R24">
         <v>2.3</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U24">
-        <v>2.46</v>
+        <v>2.39</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
         <v>1</v>
       </c>
       <c r="Y24">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z24">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA24">
         <v>1.65</v>
       </c>
       <c r="AB24">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AC24">
         <v>2.88</v>
       </c>
       <c r="AD24">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF24">
         <v>1.57</v>
       </c>
       <c r="AG24">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK24">
         <v>1.44</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>3.43</v>
+        <v>3.6</v>
       </c>
       <c r="O29">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="P29">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q29">
         <v>3.9</v>
@@ -5199,28 +5199,28 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O30">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="P30">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q30">
-        <v>3.54</v>
+        <v>3.45</v>
       </c>
       <c r="R30">
         <v>1.77</v>
       </c>
       <c r="S30">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="T30">
         <v>2.13</v>
       </c>
       <c r="U30">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="V30">
         <v>1.2</v>
@@ -5241,7 +5241,7 @@
         <v>2.97</v>
       </c>
       <c r="AB30">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC30">
         <v>6.55</v>
@@ -5253,10 +5253,10 @@
         <v>1.02</v>
       </c>
       <c r="AF30">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AG30">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK30">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O31">
-        <v>3.21</v>
+        <v>2.9</v>
       </c>
       <c r="P31">
-        <v>4.64</v>
+        <v>4.45</v>
       </c>
       <c r="Q31">
         <v>2.35</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="O32">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P32">
-        <v>4.98</v>
+        <v>4.6</v>
       </c>
       <c r="Q32">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R32">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S32">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="U32">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="V32">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W32">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
         <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z32">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA32">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB32">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC32">
         <v>2.92</v>
       </c>
       <c r="AD32">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE32">
         <v>1.12</v>
       </c>
       <c r="AF32">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG32">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,65 +7481,65 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="O44">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P44">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="Q44">
-        <v>3.01</v>
+        <v>2.36</v>
       </c>
       <c r="R44">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="S44">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T44">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="U44">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="V44">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X44">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z44">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="AA44">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="AB44">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AC44">
-        <v>3.74</v>
+        <v>3.52</v>
       </c>
       <c r="AD44">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AE44">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF44">
+        <v>1.75</v>
+      </c>
+      <c r="AG44">
         <v>1.86</v>
       </c>
-      <c r="AG44">
-        <v>1.83</v>
-      </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK44">
-        <v>1.49</v>
+        <v>1.77</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="O45">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P45">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q45">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R45">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="S45">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T45">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U45">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="V45">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W45">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z45">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA45">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AB45">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AC45">
-        <v>3.52</v>
+        <v>3.14</v>
       </c>
       <c r="AD45">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE45">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF45">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG45">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="O46">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P46">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="Q46">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="R46">
         <v>2.1</v>
       </c>
       <c r="S46">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T46">
-        <v>3.07</v>
+        <v>2.7</v>
       </c>
       <c r="U46">
-        <v>2.78</v>
+        <v>2.91</v>
       </c>
       <c r="V46">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W46">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y46">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z46">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AA46">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AB46">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AC46">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AD46">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE46">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF46">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AG46">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK46">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="O47">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P47">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q47">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R47">
         <v>2.1</v>
       </c>
       <c r="S47">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T47">
-        <v>2.7</v>
+        <v>3.07</v>
       </c>
       <c r="U47">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="V47">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W47">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z47">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AA47">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AB47">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AC47">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AD47">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE47">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF47">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AG47">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK47">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="O48">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P48">
-        <v>3.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q48">
-        <v>2.4</v>
+        <v>3.01</v>
       </c>
       <c r="R48">
+        <v>2.05</v>
+      </c>
+      <c r="S48">
+        <v>1.45</v>
+      </c>
+      <c r="T48">
+        <v>2.41</v>
+      </c>
+      <c r="U48">
+        <v>3.3</v>
+      </c>
+      <c r="V48">
+        <v>1.29</v>
+      </c>
+      <c r="W48">
+        <v>1.04</v>
+      </c>
+      <c r="X48">
+        <v>1.05</v>
+      </c>
+      <c r="Y48">
+        <v>1.36</v>
+      </c>
+      <c r="Z48">
+        <v>3.06</v>
+      </c>
+      <c r="AA48">
         <v>2.23</v>
       </c>
-      <c r="S48">
-        <v>1.4</v>
-      </c>
-      <c r="T48">
-        <v>2.62</v>
-      </c>
-      <c r="U48">
-        <v>2.65</v>
-      </c>
-      <c r="V48">
-        <v>1.4</v>
-      </c>
-      <c r="W48">
-        <v>1.08</v>
-      </c>
-      <c r="X48">
+      <c r="AB48">
+        <v>1.62</v>
+      </c>
+      <c r="AC48">
+        <v>3.74</v>
+      </c>
+      <c r="AD48">
+        <v>1.17</v>
+      </c>
+      <c r="AE48">
         <v>1.03</v>
       </c>
-      <c r="Y48">
-        <v>1.25</v>
-      </c>
-      <c r="Z48">
-        <v>3.25</v>
-      </c>
-      <c r="AA48">
-        <v>1.93</v>
-      </c>
-      <c r="AB48">
+      <c r="AF48">
+        <v>1.86</v>
+      </c>
+      <c r="AG48">
         <v>1.83</v>
       </c>
-      <c r="AC48">
-        <v>3.14</v>
-      </c>
-      <c r="AD48">
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
         <v>1.3</v>
       </c>
-      <c r="AE48">
-        <v>1.07</v>
-      </c>
-      <c r="AF48">
-        <v>1.78</v>
-      </c>
-      <c r="AG48">
-        <v>1.95</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.22</v>
-      </c>
       <c r="AK48">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,31 +8296,31 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="O49">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P49">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="Q49">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="R49">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T49">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="U49">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="V49">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="W49">
         <v>1.12</v>
@@ -8329,31 +8329,31 @@
         <v>1.04</v>
       </c>
       <c r="Y49">
+        <v>1.14</v>
+      </c>
+      <c r="Z49">
+        <v>4.8</v>
+      </c>
+      <c r="AA49">
+        <v>1.55</v>
+      </c>
+      <c r="AB49">
+        <v>2.38</v>
+      </c>
+      <c r="AC49">
+        <v>2.38</v>
+      </c>
+      <c r="AD49">
+        <v>1.5</v>
+      </c>
+      <c r="AE49">
         <v>1.2</v>
       </c>
-      <c r="Z49">
-        <v>4.25</v>
-      </c>
-      <c r="AA49">
-        <v>1.62</v>
-      </c>
-      <c r="AB49">
-        <v>2.2</v>
-      </c>
-      <c r="AC49">
-        <v>2.5</v>
-      </c>
-      <c r="AD49">
-        <v>1.44</v>
-      </c>
-      <c r="AE49">
-        <v>1.16</v>
-      </c>
       <c r="AF49">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG49">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,34 +8459,34 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O50">
         <v>3</v>
       </c>
       <c r="P50">
-        <v>4.62</v>
+        <v>3.75</v>
       </c>
       <c r="Q50">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R50">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S50">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="T50">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="U50">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="V50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W50">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X50">
         <v>1.09</v>
@@ -8495,16 +8495,16 @@
         <v>1.53</v>
       </c>
       <c r="Z50">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AA50">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB50">
         <v>1.44</v>
       </c>
       <c r="AC50">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD50">
         <v>1.14</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.13</v>
+        <v>1.94</v>
       </c>
       <c r="O53">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>15</v>
+        <v>3.2</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA53">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="AB53">
-        <v>3.6</v>
+        <v>2.23</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.94</v>
+        <v>1.09</v>
       </c>
       <c r="O54">
-        <v>3.7</v>
+        <v>9</v>
       </c>
       <c r="P54">
-        <v>3.55</v>
+        <v>12</v>
       </c>
       <c r="Q54">
-        <v>2.4</v>
+        <v>1.41</v>
       </c>
       <c r="R54">
-        <v>2.49</v>
+        <v>3.22</v>
       </c>
       <c r="S54">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="T54">
-        <v>3.28</v>
+        <v>4.7</v>
       </c>
       <c r="U54">
-        <v>2.24</v>
+        <v>1.88</v>
       </c>
       <c r="V54">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="W54">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="X54">
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z54">
-        <v>4.6</v>
+        <v>7.3</v>
       </c>
       <c r="AA54">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="AB54">
-        <v>2.25</v>
+        <v>3.35</v>
       </c>
       <c r="AC54">
-        <v>2.42</v>
+        <v>1.77</v>
       </c>
       <c r="AD54">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AE54">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AF54">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AG54">
-        <v>2.45</v>
+        <v>1.82</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="AK54">
-        <v>1.83</v>
+        <v>5.5</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O59">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P59">
-        <v>5.37</v>
+        <v>5.6</v>
       </c>
       <c r="Q59">
-        <v>2.26</v>
+        <v>2.11</v>
       </c>
       <c r="R59">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S59">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T59">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="U59">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="V59">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W59">
         <v>1.03</v>
       </c>
       <c r="X59">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y59">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z59">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AA59">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AB59">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC59">
         <v>4.5</v>
       </c>
       <c r="AD59">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AE59">
         <v>1.03</v>
       </c>
       <c r="AF59">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AG59">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>1.22</v>
       </c>
       <c r="AK59">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O60">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P60">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="Q60">
-        <v>2.72</v>
+        <v>2.49</v>
       </c>
       <c r="R60">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="S60">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T60">
         <v>2.5</v>
       </c>
       <c r="U60">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="V60">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W60">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X60">
         <v>1.05</v>
       </c>
       <c r="Y60">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z60">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AA60">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AB60">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC60">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD60">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AE60">
         <v>1.03</v>
       </c>
       <c r="AF60">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AG60">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AK60">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="O61">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P61">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="Q61">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="R61">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="S61">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T61">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="U61">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="V61">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W61">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X61">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z61">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA61">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB61">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AC61">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AD61">
         <v>1.44</v>
       </c>
       <c r="AE61">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF61">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG61">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK61">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O62">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="P62">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q62">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="R62">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="S62">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T62">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="U62">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="V62">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="W62">
         <v>1.02</v>
       </c>
       <c r="X62">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y62">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="Z62">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AA62">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB62">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AC62">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AD62">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AE62">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF62">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG62">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK62">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O63">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="P63">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="Q63">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
       <c r="R63">
         <v>2.38</v>
       </c>
       <c r="S63">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T63">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="U63">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="V63">
         <v>1.57</v>
       </c>
       <c r="W63">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X63">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y63">
+        <v>1.15</v>
+      </c>
+      <c r="Z63">
+        <v>4.8</v>
+      </c>
+      <c r="AA63">
+        <v>1.59</v>
+      </c>
+      <c r="AB63">
+        <v>2.42</v>
+      </c>
+      <c r="AC63">
+        <v>2.29</v>
+      </c>
+      <c r="AD63">
+        <v>1.49</v>
+      </c>
+      <c r="AE63">
         <v>1.18</v>
-      </c>
-      <c r="Z63">
-        <v>4.6</v>
-      </c>
-      <c r="AA63">
-        <v>1.62</v>
-      </c>
-      <c r="AB63">
-        <v>2.36</v>
-      </c>
-      <c r="AC63">
-        <v>2.4</v>
-      </c>
-      <c r="AD63">
-        <v>1.48</v>
-      </c>
-      <c r="AE63">
-        <v>1.22</v>
       </c>
       <c r="AF63">
         <v>1.5</v>
       </c>
       <c r="AG63">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O64">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="P64">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="Q64">
         <v>2.25</v>
       </c>
       <c r="R64">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="S64">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T64">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="U64">
         <v>2.4</v>
       </c>
       <c r="V64">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W64">
         <v>1.08</v>
       </c>
       <c r="X64">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y64">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z64">
-        <v>4.15</v>
+        <v>3.82</v>
       </c>
       <c r="AA64">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AB64">
         <v>2.08</v>
       </c>
       <c r="AC64">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD64">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE64">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AF64">
         <v>1.62</v>
       </c>
       <c r="AG64">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>1.25</v>
       </c>
       <c r="AK64">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="O65">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P65">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q65">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
       <c r="R65">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S65">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T65">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="U65">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V65">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="W65">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z65">
-        <v>5.25</v>
+        <v>4.59</v>
       </c>
       <c r="AA65">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AB65">
-        <v>2.54</v>
+        <v>2.28</v>
       </c>
       <c r="AC65">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="AD65">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AE65">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF65">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG65">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK65">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,19 +11067,19 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="O66">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P66">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q66">
         <v>2.1</v>
       </c>
       <c r="R66">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S66">
         <v>1.18</v>
@@ -11088,13 +11088,13 @@
         <v>4.33</v>
       </c>
       <c r="U66">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V66">
         <v>1.85</v>
       </c>
       <c r="W66">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X66">
         <v>1.01</v>
@@ -11103,28 +11103,28 @@
         <v>1.06</v>
       </c>
       <c r="Z66">
-        <v>6.3</v>
+        <v>6.25</v>
       </c>
       <c r="AA66">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB66">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AC66">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AD66">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AE66">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AF66">
         <v>1.36</v>
       </c>
       <c r="AG66">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.18</v>
       </c>
       <c r="AK66">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="O67">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="P67">
-        <v>5.7</v>
+        <v>6.25</v>
       </c>
       <c r="Q67">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R67">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="S67">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T67">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="U67">
-        <v>2.21</v>
+        <v>1.93</v>
       </c>
       <c r="V67">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="W67">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X67">
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="Z67">
-        <v>5.1</v>
+        <v>6.73</v>
       </c>
       <c r="AA67">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AB67">
-        <v>2.53</v>
+        <v>3.1</v>
       </c>
       <c r="AC67">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AD67">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="AE67">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AF67">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AG67">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK67">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="O68">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P68">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="Q68">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="R68">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S68">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T68">
         <v>3.5</v>
       </c>
       <c r="U68">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="V68">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W68">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X68">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z68">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="AA68">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AB68">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AC68">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AD68">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE68">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF68">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AG68">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK68">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11559,52 +11559,52 @@
         <v>1.51</v>
       </c>
       <c r="O69">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="P69">
-        <v>5.2</v>
+        <v>4.79</v>
       </c>
       <c r="Q69">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="R69">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="S69">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T69">
         <v>3.9</v>
       </c>
       <c r="U69">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V69">
         <v>1.64</v>
       </c>
       <c r="W69">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X69">
         <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z69">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA69">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AB69">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="AC69">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AD69">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AE69">
         <v>1.25</v>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK69">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="O70">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P70">
-        <v>4.4</v>
+        <v>4.09</v>
       </c>
       <c r="Q70">
         <v>2.33</v>
@@ -11743,7 +11743,7 @@
         <v>2.99</v>
       </c>
       <c r="V70">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W70">
         <v>1.03</v>
@@ -11761,10 +11761,10 @@
         <v>2.05</v>
       </c>
       <c r="AB70">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC70">
-        <v>3.91</v>
+        <v>3.94</v>
       </c>
       <c r="AD70">
         <v>1.2</v>
@@ -11776,7 +11776,7 @@
         <v>2</v>
       </c>
       <c r="AG70">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="O71">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="P71">
-        <v>13.39</v>
+        <v>9.5</v>
       </c>
       <c r="Q71">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="R71">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="S71">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="T71">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U71">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V71">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="W71">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y71">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z71">
-        <v>5.75</v>
+        <v>4.25</v>
       </c>
       <c r="AA71">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB71">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="AC71">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AD71">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AE71">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AF71">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AG71">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK71">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>3.18</v>
+        <v>3.75</v>
       </c>
       <c r="O73">
+        <v>3.6</v>
+      </c>
+      <c r="P73">
+        <v>1.75</v>
+      </c>
+      <c r="Q73">
         <v>3.9</v>
       </c>
-      <c r="P73">
-        <v>1.87</v>
-      </c>
-      <c r="Q73">
-        <v>3.75</v>
-      </c>
       <c r="R73">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S73">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T73">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="U73">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="V73">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W73">
         <v>1.1</v>
       </c>
       <c r="X73">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y73">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z73">
-        <v>4.63</v>
+        <v>3.95</v>
       </c>
       <c r="AA73">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB73">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AC73">
         <v>2.6</v>
       </c>
       <c r="AD73">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE73">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF73">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG73">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AK73">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12534,28 +12534,28 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="O75">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
         <v>3.75</v>
       </c>
       <c r="Q75">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="R75">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S75">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T75">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="U75">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="V75">
         <v>1.44</v>
@@ -12564,25 +12564,25 @@
         <v>1.08</v>
       </c>
       <c r="X75">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y75">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z75">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AA75">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB75">
         <v>1.83</v>
       </c>
       <c r="AC75">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AD75">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE75">
         <v>1.07</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AK75">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="O83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P83">
-        <v>2.04</v>
+        <v>6.1</v>
       </c>
       <c r="Q83">
-        <v>4.49</v>
+        <v>2</v>
       </c>
       <c r="R83">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="S83">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="T83">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="U83">
-        <v>2.99</v>
+        <v>2.3</v>
       </c>
       <c r="V83">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="W83">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X83">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y83">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="Z83">
-        <v>3.1</v>
+        <v>4.25</v>
       </c>
       <c r="AA83">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="AB83">
-        <v>1.64</v>
+        <v>2.18</v>
       </c>
       <c r="AC83">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="AD83">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="AE83">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF83">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AG83">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.74</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>1.21</v>
+        <v>2.38</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="O84">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P84">
-        <v>6.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q84">
-        <v>2</v>
+        <v>4.49</v>
       </c>
       <c r="R84">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S84">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="T84">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="U84">
-        <v>2.3</v>
+        <v>2.99</v>
       </c>
       <c r="V84">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="W84">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X84">
+        <v>1.05</v>
+      </c>
+      <c r="Y84">
+        <v>1.36</v>
+      </c>
+      <c r="Z84">
+        <v>3.1</v>
+      </c>
+      <c r="AA84">
+        <v>2.1</v>
+      </c>
+      <c r="AB84">
+        <v>1.64</v>
+      </c>
+      <c r="AC84">
+        <v>3.5</v>
+      </c>
+      <c r="AD84">
+        <v>1.29</v>
+      </c>
+      <c r="AE84">
         <v>1.04</v>
       </c>
-      <c r="Y84">
-        <v>1.14</v>
-      </c>
-      <c r="Z84">
-        <v>4.25</v>
-      </c>
-      <c r="AA84">
-        <v>1.58</v>
-      </c>
-      <c r="AB84">
-        <v>2.18</v>
-      </c>
-      <c r="AC84">
-        <v>2.45</v>
-      </c>
-      <c r="AD84">
-        <v>1.48</v>
-      </c>
-      <c r="AE84">
-        <v>1.14</v>
-      </c>
       <c r="AF84">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="AG84">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.22</v>
+        <v>1.74</v>
       </c>
       <c r="AK84">
-        <v>2.38</v>
+        <v>1.21</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.18</v>
+        <v>2.48</v>
       </c>
       <c r="O86">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P86">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14490,34 +14490,34 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="O87">
-        <v>4.1</v>
+        <v>4.45</v>
       </c>
       <c r="P87">
         <v>5</v>
       </c>
       <c r="Q87">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="R87">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="S87">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T87">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U87">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="V87">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W87">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X87">
         <v>1.01</v>
@@ -14529,7 +14529,7 @@
         <v>4.4</v>
       </c>
       <c r="AA87">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB87">
         <v>2.23</v>
@@ -14541,29 +14541,29 @@
         <v>1.5</v>
       </c>
       <c r="AE87">
+        <v>1.18</v>
+      </c>
+      <c r="AF87">
+        <v>1.7</v>
+      </c>
+      <c r="AG87">
+        <v>2.05</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ87">
         <v>1.14</v>
       </c>
-      <c r="AF87">
-        <v>1.67</v>
-      </c>
-      <c r="AG87">
-        <v>2.04</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ87">
-        <v>1.2</v>
-      </c>
       <c r="AK87">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -15142,61 +15142,61 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="O91">
         <v>3</v>
       </c>
       <c r="P91">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q91">
-        <v>3.16</v>
+        <v>3.64</v>
       </c>
       <c r="R91">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="S91">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T91">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="U91">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="V91">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W91">
         <v>1.06</v>
       </c>
       <c r="X91">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y91">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z91">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AA91">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AB91">
         <v>1.6</v>
       </c>
       <c r="AC91">
-        <v>3.95</v>
+        <v>3.84</v>
       </c>
       <c r="AD91">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE91">
         <v>1.06</v>
       </c>
       <c r="AF91">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG91">
         <v>1.85</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="AK91">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AL91">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -1590,26 +1590,26 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "19", "61", "89"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39", "52", "70"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1928,14 +1928,14 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,14 +2000,14 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
+          <t>["83"]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ10">
         <v>0</v>
       </c>
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34", "45+12"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2242,26 +2242,26 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63", "75"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "80"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2408,13 +2408,13 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -2424,35 +2424,35 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>2.64</v>
+        <v>2.92</v>
       </c>
       <c r="O13">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="P13">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="Q13">
-        <v>3.35</v>
+        <v>3.64</v>
       </c>
       <c r="R13">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="S13">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T13">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="U13">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="V13">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W13">
         <v>1.02</v>
@@ -2461,31 +2461,31 @@
         <v>1.06</v>
       </c>
       <c r="Y13">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Z13">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AA13">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AB13">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AC13">
-        <v>4.91</v>
+        <v>4.94</v>
       </c>
       <c r="AD13">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE13">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AG13">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2494,41 +2494,41 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "23"]</t>
         </is>
       </c>
       <c r="AJ13">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK13">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2568,13 +2568,13 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36"]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,13 +2731,13 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "34"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,13 +2894,13 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2909,85 +2909,85 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O16">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="Q16">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="R16">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
         <v>3.2</v>
       </c>
       <c r="U16">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="V16">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="AA16">
         <v>1.72</v>
       </c>
       <c r="AB16">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AC16">
         <v>2.88</v>
       </c>
       <c r="AD16">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE16">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF16">
         <v>1.58</v>
       </c>
       <c r="AG16">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["78", "90+7"]</t>
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AK16">
         <v>1.44</v>
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,36 +3057,36 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="O17">
+        <v>3.1</v>
+      </c>
+      <c r="P17">
         <v>3</v>
-      </c>
-      <c r="P17">
-        <v>3.1</v>
       </c>
       <c r="Q17">
         <v>2.7</v>
@@ -3107,19 +3107,19 @@
         <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="AA17">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AB17">
         <v>1.67</v>
@@ -3131,7 +3131,7 @@
         <v>1.22</v>
       </c>
       <c r="AE17">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF17">
         <v>1.83</v>
@@ -3141,46 +3141,46 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "71"]</t>
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK17">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3709,26 +3709,26 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["80"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29"]</t>
         </is>
       </c>
       <c r="AJ21">
@@ -3872,26 +3872,26 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2", "60", "90", "90+1"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
@@ -4035,13 +4035,13 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4050,11 +4050,11 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66", "89", "90+2"]</t>
         </is>
       </c>
       <c r="AJ23">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,26 +4198,26 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31"]</t>
         </is>
       </c>
       <c r="AJ24">
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4384,25 +4384,25 @@
         </is>
       </c>
       <c r="N25">
+        <v>3.2</v>
+      </c>
+      <c r="O25">
         <v>2.99</v>
       </c>
-      <c r="O25">
-        <v>2.9</v>
-      </c>
       <c r="P25">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="Q25">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="R25">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="S25">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T25">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="U25">
         <v>3.36</v>
@@ -4414,16 +4414,16 @@
         <v>1</v>
       </c>
       <c r="X25">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y25">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Z25">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="AA25">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AB25">
         <v>1.54</v>
@@ -4432,16 +4432,16 @@
         <v>4.75</v>
       </c>
       <c r="AD25">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE25">
         <v>1.01</v>
       </c>
       <c r="AF25">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AG25">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AK25">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,34 +4547,34 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="O26">
+        <v>3.7</v>
+      </c>
+      <c r="P26">
+        <v>2.5</v>
+      </c>
+      <c r="Q26">
+        <v>2.76</v>
+      </c>
+      <c r="R26">
+        <v>2.5</v>
+      </c>
+      <c r="S26">
+        <v>1.22</v>
+      </c>
+      <c r="T26">
         <v>3.6</v>
       </c>
-      <c r="P26">
-        <v>2.78</v>
-      </c>
-      <c r="Q26">
-        <v>2.62</v>
-      </c>
-      <c r="R26">
-        <v>2.38</v>
-      </c>
-      <c r="S26">
-        <v>1.25</v>
-      </c>
-      <c r="T26">
-        <v>3.5</v>
-      </c>
       <c r="U26">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="V26">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X26">
         <v>1.03</v>
@@ -4583,28 +4583,28 @@
         <v>1.14</v>
       </c>
       <c r="Z26">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA26">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB26">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="AC26">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AD26">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AE26">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF26">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG26">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK26">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O27">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P27">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="Q27">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R27">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S27">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="U27">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="V27">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
         <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z27">
-        <v>3.38</v>
+        <v>3.95</v>
       </c>
       <c r="AA27">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AB27">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AC27">
-        <v>2.99</v>
+        <v>2.64</v>
       </c>
       <c r="AD27">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE27">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF27">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG27">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AK27">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,28 +4873,28 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O28">
         <v>3.37</v>
       </c>
       <c r="P28">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="Q28">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R28">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="S28">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T28">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="U28">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V28">
         <v>1.44</v>
@@ -4903,31 +4903,31 @@
         <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
-        <v>4.08</v>
+        <v>3.9</v>
       </c>
       <c r="AA28">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AB28">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="AC28">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD28">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE28">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF28">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG28">
         <v>2.15</v>
@@ -4946,7 +4946,7 @@
         <v>1.44</v>
       </c>
       <c r="AK28">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5697,49 +5697,49 @@
         <v>3.34</v>
       </c>
       <c r="Q33">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R33">
         <v>2</v>
       </c>
       <c r="S33">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T33">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U33">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="V33">
         <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X33">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y33">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z33">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AA33">
         <v>2.2</v>
       </c>
       <c r="AB33">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC33">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD33">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF33">
         <v>1.91</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK33">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6180,40 +6180,40 @@
         <v>2.4</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P36">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q36">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R36">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S36">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="U36">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="V36">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X36">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
         <v>1.19</v>
       </c>
       <c r="Z36">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AA36">
         <v>1.7</v>
@@ -6222,35 +6222,35 @@
         <v>2.03</v>
       </c>
       <c r="AC36">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AD36">
+        <v>1.39</v>
+      </c>
+      <c r="AE36">
+        <v>1.17</v>
+      </c>
+      <c r="AF36">
+        <v>1.57</v>
+      </c>
+      <c r="AG36">
+        <v>2.3</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
         <v>1.38</v>
       </c>
-      <c r="AE36">
-        <v>1.12</v>
-      </c>
-      <c r="AF36">
-        <v>1.53</v>
-      </c>
-      <c r="AG36">
-        <v>2.25</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.25</v>
-      </c>
       <c r="AK36">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6835,55 +6835,55 @@
         <v>3.1</v>
       </c>
       <c r="P40">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="Q40">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="R40">
         <v>1.99</v>
       </c>
       <c r="S40">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T40">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="U40">
-        <v>2.91</v>
+        <v>3.12</v>
       </c>
       <c r="V40">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W40">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X40">
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z40">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA40">
         <v>2.11</v>
       </c>
       <c r="AB40">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC40">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD40">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE40">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF40">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG40">
         <v>1.85</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK40">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O41">
         <v>3</v>
       </c>
       <c r="P41">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="Q41">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="R41">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="S41">
         <v>1.4</v>
       </c>
       <c r="T41">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="U41">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V41">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W41">
+        <v>1.07</v>
+      </c>
+      <c r="X41">
         <v>1.04</v>
       </c>
-      <c r="X41">
-        <v>1.03</v>
-      </c>
       <c r="Y41">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z41">
-        <v>3</v>
+        <v>3.39</v>
       </c>
       <c r="AA41">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB41">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AC41">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="AD41">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE41">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF41">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG41">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,52 +7155,52 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="O42">
         <v>3.1</v>
       </c>
       <c r="P42">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="Q42">
         <v>3.1</v>
       </c>
       <c r="R42">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S42">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T42">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="U42">
         <v>2.88</v>
       </c>
       <c r="V42">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W42">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X42">
         <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z42">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA42">
         <v>1.97</v>
       </c>
       <c r="AB42">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC42">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="AD42">
         <v>1.25</v>
@@ -7209,7 +7209,7 @@
         <v>1.06</v>
       </c>
       <c r="AF42">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG42">
         <v>2</v>
@@ -7228,7 +7228,7 @@
         <v>1.26</v>
       </c>
       <c r="AK42">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="O43">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="P43">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="Q43">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="R43">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S43">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="T43">
-        <v>2.5</v>
+        <v>3.07</v>
       </c>
       <c r="U43">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="V43">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W43">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z43">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="AA43">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AB43">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AC43">
-        <v>3.8</v>
+        <v>3.08</v>
       </c>
       <c r="AD43">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE43">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF43">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AG43">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK43">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,80 +7481,80 @@
         </is>
       </c>
       <c r="N44">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O44">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P44">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q44">
-        <v>2.36</v>
+        <v>2.79</v>
       </c>
       <c r="R44">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="S44">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T44">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U44">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="V44">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W44">
+        <v>1.03</v>
+      </c>
+      <c r="X44">
+        <v>1.04</v>
+      </c>
+      <c r="Y44">
+        <v>1.35</v>
+      </c>
+      <c r="Z44">
+        <v>2.74</v>
+      </c>
+      <c r="AA44">
+        <v>2.15</v>
+      </c>
+      <c r="AB44">
+        <v>1.65</v>
+      </c>
+      <c r="AC44">
+        <v>3.7</v>
+      </c>
+      <c r="AD44">
+        <v>1.22</v>
+      </c>
+      <c r="AE44">
         <v>1.05</v>
       </c>
-      <c r="X44">
-        <v>1.01</v>
-      </c>
-      <c r="Y44">
+      <c r="AF44">
+        <v>1.83</v>
+      </c>
+      <c r="AG44">
+        <v>1.8</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
         <v>1.28</v>
       </c>
-      <c r="Z44">
-        <v>3.08</v>
-      </c>
-      <c r="AA44">
-        <v>1.99</v>
-      </c>
-      <c r="AB44">
-        <v>1.77</v>
-      </c>
-      <c r="AC44">
-        <v>3.52</v>
-      </c>
-      <c r="AD44">
-        <v>1.28</v>
-      </c>
-      <c r="AE44">
-        <v>1.1</v>
-      </c>
-      <c r="AF44">
-        <v>1.75</v>
-      </c>
-      <c r="AG44">
-        <v>1.86</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.21</v>
-      </c>
       <c r="AK44">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,61 +7644,61 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.82</v>
+        <v>2.62</v>
       </c>
       <c r="O45">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P45">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q45">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R45">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="S45">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T45">
         <v>2.62</v>
       </c>
       <c r="U45">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="V45">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W45">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X45">
         <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z45">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA45">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AB45">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AC45">
-        <v>3.14</v>
+        <v>3.8</v>
       </c>
       <c r="AD45">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE45">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF45">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG45">
         <v>1.95</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AK45">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="O46">
+        <v>3.35</v>
+      </c>
+      <c r="P46">
+        <v>3.8</v>
+      </c>
+      <c r="Q46">
+        <v>2.48</v>
+      </c>
+      <c r="R46">
+        <v>2.01</v>
+      </c>
+      <c r="S46">
+        <v>1.36</v>
+      </c>
+      <c r="T46">
+        <v>2.88</v>
+      </c>
+      <c r="U46">
+        <v>2.78</v>
+      </c>
+      <c r="V46">
+        <v>1.36</v>
+      </c>
+      <c r="W46">
+        <v>1.07</v>
+      </c>
+      <c r="X46">
+        <v>1.03</v>
+      </c>
+      <c r="Y46">
+        <v>1.29</v>
+      </c>
+      <c r="Z46">
         <v>3.4</v>
       </c>
-      <c r="P46">
-        <v>4.4</v>
-      </c>
-      <c r="Q46">
-        <v>2.5</v>
-      </c>
-      <c r="R46">
-        <v>2.1</v>
-      </c>
-      <c r="S46">
-        <v>1.4</v>
-      </c>
-      <c r="T46">
-        <v>2.7</v>
-      </c>
-      <c r="U46">
-        <v>2.91</v>
-      </c>
-      <c r="V46">
-        <v>1.33</v>
-      </c>
-      <c r="W46">
-        <v>1.03</v>
-      </c>
-      <c r="X46">
-        <v>1</v>
-      </c>
-      <c r="Y46">
-        <v>1.33</v>
-      </c>
-      <c r="Z46">
-        <v>3.14</v>
-      </c>
       <c r="AA46">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AB46">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AC46">
-        <v>3.7</v>
+        <v>3.08</v>
       </c>
       <c r="AD46">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE46">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF46">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG46">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="O47">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P47">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q47">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="R47">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S47">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T47">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="U47">
-        <v>2.78</v>
+        <v>3.01</v>
       </c>
       <c r="V47">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y47">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Z47">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AA47">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AB47">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AC47">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AD47">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE47">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF47">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG47">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="O48">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P48">
-        <v>2.87</v>
+        <v>3.45</v>
       </c>
       <c r="Q48">
-        <v>3.01</v>
+        <v>2.7</v>
       </c>
       <c r="R48">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S48">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="T48">
-        <v>2.41</v>
+        <v>2.95</v>
       </c>
       <c r="U48">
-        <v>3.3</v>
+        <v>2.78</v>
       </c>
       <c r="V48">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="W48">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X48">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z48">
-        <v>3.06</v>
+        <v>3.4</v>
       </c>
       <c r="AA48">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="AB48">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AC48">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="AD48">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AE48">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF48">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AG48">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK48">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8273,26 +8273,26 @@
         </is>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49">
         <v>0</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N49">
@@ -8357,12 +8357,12 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "60"]</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31"]</t>
         </is>
       </c>
       <c r="AJ49">
@@ -8375,28 +8375,28 @@
         <v>0</v>
       </c>
       <c r="AM49">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN49">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO49">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP49">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AR49">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AS49">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT49">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="O51">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="P51">
-        <v>6.11</v>
+        <v>5.5</v>
       </c>
       <c r="Q51">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T51">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U51">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="V51">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X51">
         <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z51">
-        <v>3.98</v>
+        <v>4.4</v>
       </c>
       <c r="AA51">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AB51">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AC51">
-        <v>2.75</v>
+        <v>2.41</v>
       </c>
       <c r="AD51">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF51">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG51">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.09</v>
       </c>
       <c r="AK51">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,34 +8785,34 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="O52">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P52">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q52">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R52">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="S52">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T52">
         <v>2.56</v>
       </c>
       <c r="U52">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="V52">
         <v>1.3</v>
       </c>
       <c r="W52">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
         <v>1.03</v>
@@ -8833,7 +8833,7 @@
         <v>3.84</v>
       </c>
       <c r="AD52">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE52">
         <v>1.06</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AK52">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9437,31 +9437,31 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="O56">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="P56">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q56">
         <v>1.36</v>
       </c>
       <c r="R56">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="S56">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T56">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="U56">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="V56">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="W56">
         <v>1.2</v>
@@ -9473,28 +9473,28 @@
         <v>1.11</v>
       </c>
       <c r="Z56">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA56">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AB56">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="AC56">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AD56">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AE56">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AF56">
         <v>2.38</v>
       </c>
       <c r="AG56">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.01</v>
       </c>
       <c r="AK56">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,49 +9600,49 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="O57">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P57">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="Q57">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="R57">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S57">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T57">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U57">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="V57">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W57">
         <v>1.13</v>
       </c>
       <c r="X57">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z57">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA57">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB57">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC57">
         <v>2.56</v>
@@ -9651,13 +9651,13 @@
         <v>1.4</v>
       </c>
       <c r="AE57">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF57">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG57">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.25</v>
       </c>
       <c r="AK57">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="O58">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P58">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q58">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="R58">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S58">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T58">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U58">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="V58">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W58">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X58">
         <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z58">
         <v>4.6</v>
       </c>
       <c r="AA58">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AB58">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="AC58">
         <v>2.41</v>
       </c>
       <c r="AD58">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE58">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AF58">
         <v>1.5</v>
       </c>
       <c r="AG58">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="AK58">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9903,26 +9903,26 @@
         </is>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59">
         <v>0</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59">
         <v>0</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N59">
@@ -9987,12 +9987,12 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54", "80"]</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11"]</t>
         </is>
       </c>
       <c r="AJ59">
@@ -10005,28 +10005,28 @@
         <v>0</v>
       </c>
       <c r="AM59">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN59">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO59">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP59">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ59">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AR59">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AS59">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT59">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>0</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -10081,11 +10081,11 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N60">
@@ -10155,7 +10155,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48"]</t>
         </is>
       </c>
       <c r="AJ60">
@@ -10168,28 +10168,28 @@
         <v>0</v>
       </c>
       <c r="AM60">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN60">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO60">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP60">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ60">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AR60">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AS60">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT60">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
@@ -10229,26 +10229,26 @@
         </is>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I61">
         <v>0</v>
       </c>
       <c r="J61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N61">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["60", "82"]</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33", "50", "53", "64"]</t>
         </is>
       </c>
       <c r="AJ61">
@@ -10331,28 +10331,28 @@
         <v>0</v>
       </c>
       <c r="AM61">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN61">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO61">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP61">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ61">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AR61">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS61">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AT61">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
@@ -10392,26 +10392,26 @@
         </is>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62">
         <v>0</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N62">
@@ -10476,12 +10476,12 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "53"]</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81", "89", "90+3"]</t>
         </is>
       </c>
       <c r="AJ62">
@@ -10494,28 +10494,28 @@
         <v>0</v>
       </c>
       <c r="AM62">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN62">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO62">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP62">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ62">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AR62">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS62">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT62">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
@@ -10718,26 +10718,26 @@
         </is>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64">
         <v>0</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N64">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37", "53"]</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33"]</t>
         </is>
       </c>
       <c r="AJ64">
@@ -10820,28 +10820,28 @@
         <v>0</v>
       </c>
       <c r="AM64">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN64">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO64">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP64">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ64">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR64">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AS64">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT64">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
@@ -11370,26 +11370,26 @@
         </is>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I68">
         <v>0</v>
       </c>
       <c r="J68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N68">
@@ -11454,12 +11454,12 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50", "90+1"]</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "73"]</t>
         </is>
       </c>
       <c r="AJ68">
@@ -11472,28 +11472,28 @@
         <v>0</v>
       </c>
       <c r="AM68">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN68">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO68">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP68">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ68">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR68">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS68">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT68">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
@@ -12045,16 +12045,16 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O72">
+        <v>3.25</v>
+      </c>
+      <c r="P72">
+        <v>2.2</v>
+      </c>
+      <c r="Q72">
         <v>3.3</v>
-      </c>
-      <c r="P72">
-        <v>2.3</v>
-      </c>
-      <c r="Q72">
-        <v>3.1</v>
       </c>
       <c r="R72">
         <v>2.2</v>
@@ -12069,25 +12069,25 @@
         <v>2.63</v>
       </c>
       <c r="V72">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W72">
         <v>1.06</v>
       </c>
       <c r="X72">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y72">
         <v>1.25</v>
       </c>
       <c r="Z72">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA72">
         <v>1.86</v>
       </c>
       <c r="AB72">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AC72">
         <v>2.9</v>
@@ -12099,10 +12099,10 @@
         <v>1.15</v>
       </c>
       <c r="AF72">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG72">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK72">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="O74">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P74">
-        <v>4.92</v>
+        <v>5.77</v>
       </c>
       <c r="Q74">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R74">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S74">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T74">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U74">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="V74">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W74">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X74">
         <v>1.04</v>
       </c>
       <c r="Y74">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z74">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="AA74">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AB74">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AC74">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AD74">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE74">
         <v>1.17</v>
       </c>
       <c r="AF74">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG74">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK74">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O76">
         <v>3.2</v>
@@ -12706,19 +12706,19 @@
         <v>3.17</v>
       </c>
       <c r="Q76">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="R76">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="S76">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="T76">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="U76">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="V76">
         <v>1.32</v>
@@ -12733,25 +12733,25 @@
         <v>1.37</v>
       </c>
       <c r="Z76">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA76">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AB76">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC76">
         <v>4.1</v>
       </c>
       <c r="AD76">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE76">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF76">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG76">
         <v>1.85</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK76">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="O77">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="P77">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q77">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="R77">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S77">
         <v>1.36</v>
       </c>
       <c r="T77">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="U77">
         <v>2.77</v>
       </c>
       <c r="V77">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W77">
         <v>1.08</v>
       </c>
       <c r="X77">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y77">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z77">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="AA77">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AB77">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AC77">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="AD77">
         <v>1.29</v>
       </c>
       <c r="AE77">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF77">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG77">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AK77">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,80 +13023,80 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="O78">
+        <v>3.03</v>
+      </c>
+      <c r="P78">
+        <v>3.15</v>
+      </c>
+      <c r="Q78">
+        <v>2.75</v>
+      </c>
+      <c r="R78">
+        <v>2.05</v>
+      </c>
+      <c r="S78">
+        <v>1.4</v>
+      </c>
+      <c r="T78">
+        <v>2.73</v>
+      </c>
+      <c r="U78">
         <v>3</v>
       </c>
-      <c r="P78">
-        <v>3.1</v>
-      </c>
-      <c r="Q78">
-        <v>3.09</v>
-      </c>
-      <c r="R78">
-        <v>2.1</v>
-      </c>
-      <c r="S78">
-        <v>1.45</v>
-      </c>
-      <c r="T78">
-        <v>2.72</v>
-      </c>
-      <c r="U78">
-        <v>2.94</v>
-      </c>
       <c r="V78">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W78">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X78">
+        <v>1.07</v>
+      </c>
+      <c r="Y78">
+        <v>1.33</v>
+      </c>
+      <c r="Z78">
+        <v>3</v>
+      </c>
+      <c r="AA78">
+        <v>2.05</v>
+      </c>
+      <c r="AB78">
+        <v>1.7</v>
+      </c>
+      <c r="AC78">
+        <v>3.75</v>
+      </c>
+      <c r="AD78">
+        <v>1.25</v>
+      </c>
+      <c r="AE78">
         <v>1.06</v>
       </c>
-      <c r="Y78">
+      <c r="AF78">
+        <v>1.77</v>
+      </c>
+      <c r="AG78">
+        <v>1.92</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
         <v>1.3</v>
       </c>
-      <c r="Z78">
-        <v>2.99</v>
-      </c>
-      <c r="AA78">
-        <v>2.1</v>
-      </c>
-      <c r="AB78">
-        <v>1.75</v>
-      </c>
-      <c r="AC78">
-        <v>3.44</v>
-      </c>
-      <c r="AD78">
-        <v>1.23</v>
-      </c>
-      <c r="AE78">
-        <v>1.07</v>
-      </c>
-      <c r="AF78">
-        <v>1.85</v>
-      </c>
-      <c r="AG78">
-        <v>1.85</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>1.33</v>
-      </c>
       <c r="AK78">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,16 +13186,16 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O79">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P79">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="Q79">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="R79">
         <v>2.29</v>
@@ -13204,13 +13204,13 @@
         <v>1.35</v>
       </c>
       <c r="T79">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="U79">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V79">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W79">
         <v>1.06</v>
@@ -13219,25 +13219,25 @@
         <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z79">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA79">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB79">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC79">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="AD79">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE79">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF79">
         <v>1.67</v>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK79">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="O80">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P80">
-        <v>3.9</v>
+        <v>3.33</v>
       </c>
       <c r="Q80">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="R80">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S80">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T80">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U80">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="V80">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W80">
         <v>1.04</v>
       </c>
       <c r="X80">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y80">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z80">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="AA80">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AB80">
         <v>1.72</v>
       </c>
       <c r="AC80">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="AD80">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE80">
         <v>1.06</v>
       </c>
       <c r="AF80">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG80">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>1.3</v>
       </c>
       <c r="AK80">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,55 +13512,55 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="O81">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P81">
-        <v>4.36</v>
+        <v>2.5</v>
       </c>
       <c r="Q81">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="R81">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S81">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T81">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="U81">
-        <v>2.62</v>
+        <v>3.02</v>
       </c>
       <c r="V81">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W81">
         <v>1.06</v>
       </c>
       <c r="X81">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z81">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA81">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AB81">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC81">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AD81">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE81">
         <v>1.1</v>
@@ -13569,7 +13569,7 @@
         <v>1.7</v>
       </c>
       <c r="AG81">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="AK81">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.66</v>
+        <v>3.75</v>
       </c>
       <c r="O82">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P82">
-        <v>2.42</v>
+        <v>2.03</v>
       </c>
       <c r="Q82">
-        <v>3</v>
+        <v>4.53</v>
       </c>
       <c r="R82">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S82">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T82">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="U82">
-        <v>2.97</v>
+        <v>2.82</v>
       </c>
       <c r="V82">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W82">
+        <v>1.04</v>
+      </c>
+      <c r="X82">
+        <v>1.03</v>
+      </c>
+      <c r="Y82">
+        <v>1.3</v>
+      </c>
+      <c r="Z82">
+        <v>3.25</v>
+      </c>
+      <c r="AA82">
+        <v>2</v>
+      </c>
+      <c r="AB82">
+        <v>1.82</v>
+      </c>
+      <c r="AC82">
+        <v>3.61</v>
+      </c>
+      <c r="AD82">
+        <v>1.3</v>
+      </c>
+      <c r="AE82">
         <v>1.06</v>
       </c>
-      <c r="X82">
-        <v>1.04</v>
-      </c>
-      <c r="Y82">
-        <v>1.25</v>
-      </c>
-      <c r="Z82">
-        <v>3.3</v>
-      </c>
-      <c r="AA82">
-        <v>1.89</v>
-      </c>
-      <c r="AB82">
-        <v>1.83</v>
-      </c>
-      <c r="AC82">
-        <v>3.05</v>
-      </c>
-      <c r="AD82">
-        <v>1.29</v>
-      </c>
-      <c r="AE82">
-        <v>1.1</v>
-      </c>
       <c r="AF82">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AG82">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AK82">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="O83">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="P83">
-        <v>6.1</v>
+        <v>4.45</v>
       </c>
       <c r="Q83">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="R83">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S83">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T83">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U83">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="V83">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="W83">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X83">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y83">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="Z83">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA83">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="AB83">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="AC83">
-        <v>2.45</v>
+        <v>3.19</v>
       </c>
       <c r="AD83">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AE83">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF83">
         <v>1.69</v>
       </c>
       <c r="AG83">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>3.6</v>
+        <v>1.79</v>
       </c>
       <c r="O84">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P84">
-        <v>2.04</v>
+        <v>4.6</v>
       </c>
       <c r="Q84">
-        <v>4.49</v>
+        <v>2.4</v>
       </c>
       <c r="R84">
         <v>2.1</v>
       </c>
       <c r="S84">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T84">
-        <v>2.62</v>
+        <v>2.86</v>
       </c>
       <c r="U84">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="V84">
+        <v>1.4</v>
+      </c>
+      <c r="W84">
+        <v>1.05</v>
+      </c>
+      <c r="X84">
+        <v>1.07</v>
+      </c>
+      <c r="Y84">
         <v>1.33</v>
-      </c>
-      <c r="W84">
-        <v>1.03</v>
-      </c>
-      <c r="X84">
-        <v>1.05</v>
-      </c>
-      <c r="Y84">
-        <v>1.36</v>
       </c>
       <c r="Z84">
         <v>3.1</v>
       </c>
       <c r="AA84">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB84">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AC84">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AD84">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE84">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF84">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AG84">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.74</v>
+        <v>1.3</v>
       </c>
       <c r="AK84">
-        <v>1.21</v>
+        <v>2.02</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="O85">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="P85">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="Q85">
-        <v>2.41</v>
+        <v>1.91</v>
       </c>
       <c r="R85">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="S85">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T85">
-        <v>2.79</v>
+        <v>3.3</v>
       </c>
       <c r="U85">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="V85">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W85">
         <v>1.08</v>
       </c>
       <c r="X85">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Z85">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA85">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AB85">
-        <v>1.82</v>
+        <v>2.16</v>
       </c>
       <c r="AC85">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="AD85">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AE85">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF85">
         <v>1.85</v>
       </c>
       <c r="AG85">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK85">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14653,52 +14653,52 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="O88">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="P88">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="Q88">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R88">
         <v>2.5</v>
       </c>
       <c r="S88">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T88">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="U88">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V88">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W88">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z88">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA88">
         <v>1.48</v>
       </c>
       <c r="AB88">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AC88">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AD88">
         <v>1.55</v>
@@ -14707,10 +14707,10 @@
         <v>1.22</v>
       </c>
       <c r="AF88">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AG88">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK88">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="O89">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="P89">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q89">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="R89">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="S89">
+        <v>1.35</v>
+      </c>
+      <c r="T89">
+        <v>2.88</v>
+      </c>
+      <c r="U89">
+        <v>2.65</v>
+      </c>
+      <c r="V89">
+        <v>1.36</v>
+      </c>
+      <c r="W89">
+        <v>1.06</v>
+      </c>
+      <c r="X89">
+        <v>1</v>
+      </c>
+      <c r="Y89">
         <v>1.3</v>
       </c>
-      <c r="T89">
-        <v>3.1</v>
-      </c>
-      <c r="U89">
-        <v>2.45</v>
-      </c>
-      <c r="V89">
-        <v>1.45</v>
-      </c>
-      <c r="W89">
-        <v>1.08</v>
-      </c>
-      <c r="X89">
-        <v>1.02</v>
-      </c>
-      <c r="Y89">
-        <v>1.24</v>
-      </c>
       <c r="Z89">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="AA89">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AB89">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AC89">
-        <v>2.89</v>
+        <v>3.43</v>
       </c>
       <c r="AD89">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AE89">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF89">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG89">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK89">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="O90">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="P90">
-        <v>12.5</v>
+        <v>7.74</v>
       </c>
       <c r="Q90">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="R90">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="S90">
         <v>1.22</v>
       </c>
       <c r="T90">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U90">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="V90">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="W90">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Z90">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA90">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB90">
-        <v>2.69</v>
+        <v>2.24</v>
       </c>
       <c r="AC90">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="AD90">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AE90">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AF90">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG90">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK90">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.12</v>
+        <v>3.65</v>
       </c>
       <c r="O92">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="P92">
+        <v>2</v>
+      </c>
+      <c r="Q92">
+        <v>3.63</v>
+      </c>
+      <c r="R92">
+        <v>2.08</v>
+      </c>
+      <c r="S92">
+        <v>1.37</v>
+      </c>
+      <c r="T92">
+        <v>2.69</v>
+      </c>
+      <c r="U92">
         <v>2.8</v>
       </c>
-      <c r="Q92">
-        <v>3.06</v>
-      </c>
-      <c r="R92">
-        <v>2.02</v>
-      </c>
-      <c r="S92">
-        <v>1.5</v>
-      </c>
-      <c r="T92">
-        <v>2.45</v>
-      </c>
-      <c r="U92">
-        <v>3.3</v>
-      </c>
       <c r="V92">
+        <v>1.38</v>
+      </c>
+      <c r="W92">
+        <v>1.08</v>
+      </c>
+      <c r="X92">
+        <v>1.02</v>
+      </c>
+      <c r="Y92">
+        <v>1.33</v>
+      </c>
+      <c r="Z92">
+        <v>3.5</v>
+      </c>
+      <c r="AA92">
+        <v>1.95</v>
+      </c>
+      <c r="AB92">
+        <v>1.73</v>
+      </c>
+      <c r="AC92">
+        <v>3.6</v>
+      </c>
+      <c r="AD92">
         <v>1.26</v>
       </c>
-      <c r="W92">
-        <v>1.03</v>
-      </c>
-      <c r="X92">
+      <c r="AE92">
         <v>1.06</v>
       </c>
-      <c r="Y92">
-        <v>1.47</v>
-      </c>
-      <c r="Z92">
-        <v>2.59</v>
-      </c>
-      <c r="AA92">
-        <v>2.35</v>
-      </c>
-      <c r="AB92">
-        <v>1.47</v>
-      </c>
-      <c r="AC92">
-        <v>4.5</v>
-      </c>
-      <c r="AD92">
-        <v>1.13</v>
-      </c>
-      <c r="AE92">
-        <v>1.05</v>
-      </c>
       <c r="AF92">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="AG92">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AK92">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>3.5</v>
+        <v>2.12</v>
       </c>
       <c r="O93">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="P93">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q93">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="R93">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S93">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T93">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="U93">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="V93">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="W93">
+        <v>1</v>
+      </c>
+      <c r="X93">
         <v>1.07</v>
       </c>
-      <c r="X93">
-        <v>1.03</v>
-      </c>
       <c r="Y93">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="Z93">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="AA93">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AB93">
-        <v>1.86</v>
+        <v>1.49</v>
       </c>
       <c r="AC93">
-        <v>3.4</v>
+        <v>5.11</v>
       </c>
       <c r="AD93">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AE93">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF93">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG93">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AK93">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15963,31 +15963,31 @@
         <v>3.7</v>
       </c>
       <c r="P96">
-        <v>5.2</v>
+        <v>4.35</v>
       </c>
       <c r="Q96">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R96">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="S96">
+        <v>1.39</v>
+      </c>
+      <c r="T96">
+        <v>2.68</v>
+      </c>
+      <c r="U96">
+        <v>2.7</v>
+      </c>
+      <c r="V96">
         <v>1.38</v>
       </c>
-      <c r="T96">
-        <v>2.72</v>
-      </c>
-      <c r="U96">
-        <v>2.65</v>
-      </c>
-      <c r="V96">
-        <v>1.39</v>
-      </c>
       <c r="W96">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X96">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y96">
         <v>1.24</v>
@@ -15996,26 +15996,26 @@
         <v>3.34</v>
       </c>
       <c r="AA96">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB96">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC96">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="AD96">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE96">
         <v>1.11</v>
       </c>
       <c r="AF96">
+        <v>1.86</v>
+      </c>
+      <c r="AG96">
         <v>1.84</v>
       </c>
-      <c r="AG96">
-        <v>1.86</v>
-      </c>
       <c r="AH96" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK96">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16283,46 +16283,46 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="O98">
         <v>8</v>
       </c>
       <c r="P98">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Q98">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R98">
         <v>3.6</v>
       </c>
       <c r="S98">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="T98">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="U98">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="V98">
-        <v>1.94</v>
+        <v>2.13</v>
       </c>
       <c r="W98">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X98">
         <v>1</v>
       </c>
       <c r="Y98">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Z98">
         <v>10</v>
       </c>
       <c r="AA98">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AB98">
         <v>3.85</v>
@@ -16331,16 +16331,16 @@
         <v>1.5</v>
       </c>
       <c r="AD98">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AE98">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AF98">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AG98">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>1.01</v>
       </c>
       <c r="AK98">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AL98">
         <v>0</v>

--- a/jogos_2026-08-14.xlsx
+++ b/jogos_2026-08-14.xlsx
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -3232,14 +3232,14 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90"]</t>
         </is>
       </c>
       <c r="AJ18">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,36 +3383,36 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
-        <v>20.36</v>
+        <v>41</v>
       </c>
       <c r="O19">
-        <v>12.7</v>
+        <v>13</v>
       </c>
       <c r="P19">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3467,12 +3467,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["77"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "40", "68", "86"]</t>
         </is>
       </c>
       <c r="AJ19">
@@ -3485,28 +3485,28 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -3561,73 +3561,73 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="O20">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="P20">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="Q20">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R20">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="S20">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="U20">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="V20">
         <v>1.73</v>
       </c>
       <c r="W20">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z20">
-        <v>6.05</v>
+        <v>5.65</v>
       </c>
       <c r="AA20">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB20">
+        <v>2.85</v>
+      </c>
+      <c r="AC20">
+        <v>2.06</v>
+      </c>
+      <c r="AD20">
+        <v>1.78</v>
+      </c>
+      <c r="AE20">
+        <v>1.27</v>
+      </c>
+      <c r="AF20">
+        <v>1.36</v>
+      </c>
+      <c r="AG20">
         <v>2.9</v>
       </c>
-      <c r="AC20">
-        <v>1.85</v>
-      </c>
-      <c r="AD20">
-        <v>1.9</v>
-      </c>
-      <c r="AE20">
-        <v>1.3</v>
-      </c>
-      <c r="AF20">
-        <v>1.32</v>
-      </c>
-      <c r="AG20">
-        <v>2.98</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3635,41 +3635,41 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76"]</t>
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -4524,26 +4524,26 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["55"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "81"]</t>
         </is>
       </c>
       <c r="AJ26">
@@ -4626,28 +4626,28 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4690,13 +4690,13 @@
         <v>0</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18"]</t>
         </is>
       </c>
       <c r="AJ27">
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4850,26 +4850,26 @@
         </is>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56", "88"]</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["32", "45+3"]</t>
         </is>
       </c>
       <c r="AJ28">
@@ -4952,28 +4952,28 @@
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>0</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -5028,11 +5028,11 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76", "90+6"]</t>
         </is>
       </c>
       <c r="AJ29">
@@ -5179,23 +5179,23 @@
         <v>0</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30">
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "90+2"]</t>
         </is>
       </c>
       <c r="AJ30">
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -5351,14 +5351,14 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31">
         <v>0</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y31">
         <v>1.45</v>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90"]</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
@@ -5502,13 +5502,13 @@
         </is>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -5517,11 +5517,11 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
@@ -5586,12 +5586,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "36"]</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75"]</t>
         </is>
       </c>
       <c r="AJ32">
@@ -5604,28 +5604,28 @@
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5665,13 +5665,13 @@
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36"]</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
@@ -5767,28 +5767,28 @@
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN33">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP33">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -5828,130 +5828,130 @@
         </is>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34">
         <v>0</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N34">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O34">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="P34">
-        <v>2.62</v>
+        <v>2.99</v>
       </c>
       <c r="Q34">
-        <v>2.69</v>
+        <v>2.92</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="U34">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="V34">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z34">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA34">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AB34">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="AC34">
-        <v>2.56</v>
+        <v>3.08</v>
       </c>
       <c r="AD34">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AE34">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF34">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG34">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51"]</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2"]</t>
         </is>
       </c>
       <c r="AJ34">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK34">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL34">
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP34">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -5991,48 +5991,48 @@
         </is>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="O35">
-        <v>3.65</v>
+        <v>3.74</v>
       </c>
       <c r="P35">
-        <v>3.1</v>
+        <v>3.76</v>
       </c>
       <c r="Q35">
-        <v>2.57</v>
+        <v>2.31</v>
       </c>
       <c r="R35">
-        <v>2.22</v>
+        <v>2.43</v>
       </c>
       <c r="S35">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T35">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U35">
         <v>2.3</v>
@@ -6041,28 +6041,28 @@
         <v>1.57</v>
       </c>
       <c r="W35">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
         <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z35">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA35">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB35">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AC35">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AD35">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AE35">
         <v>1.16</v>
@@ -6071,50 +6071,50 @@
         <v>1.53</v>
       </c>
       <c r="AG35">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "54", "81"]</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "60", "90+3"]</t>
         </is>
       </c>
       <c r="AJ35">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AL35">
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6154,26 +6154,26 @@
         </is>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H36">
         <v>0</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36">
         <v>0</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N36">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "38", "77", "84"]</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
@@ -6256,28 +6256,28 @@
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN36">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
@@ -6317,130 +6317,130 @@
         </is>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N37">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O37">
         <v>3.6</v>
       </c>
       <c r="P37">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="Q37">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R37">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S37">
         <v>1.22</v>
       </c>
       <c r="T37">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U37">
         <v>2.05</v>
       </c>
       <c r="V37">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W37">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z37">
-        <v>5.05</v>
+        <v>5.35</v>
       </c>
       <c r="AA37">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB37">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AC37">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD37">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AE37">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF37">
         <v>1.38</v>
       </c>
       <c r="AG37">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "90+5"]</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AJ37">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL37">
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN37">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO37">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -6480,130 +6480,130 @@
         </is>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I38">
         <v>0</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N38">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="O38">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P38">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q38">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="R38">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S38">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="T38">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="U38">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V38">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="W38">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z38">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AA38">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB38">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AC38">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="AD38">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE38">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF38">
         <v>1.4</v>
       </c>
       <c r="AG38">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54", "66"]</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "22", "89"]</t>
         </is>
       </c>
       <c r="AJ38">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AL38">
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP38">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -6643,78 +6643,78 @@
         </is>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39">
         <v>0</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N39">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P39">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="Q39">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="R39">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S39">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T39">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U39">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V39">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X39">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z39">
-        <v>3.92</v>
+        <v>4.35</v>
       </c>
       <c r="AA39">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB39">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AC39">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="AD39">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE39">
         <v>1.12</v>
@@ -6723,50 +6723,50 @@
         <v>1.62</v>
       </c>
       <c r="AG39">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
+          <t>["18", "72", "77"]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ39">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK39">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AL39">
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN39">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO39">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
@@ -6809,13 +6809,13 @@
         <v>0</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N40">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41"]</t>
         </is>
       </c>
       <c r="AJ40">
@@ -6908,28 +6908,28 @@
         <v>0</v>
       </c>
       <c r="AM40">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN40">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
@@ -6972,13 +6972,13 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N41">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29"]</t>
         </is>
       </c>
       <c r="AJ41">
@@ -7089,10 +7089,10 @@
         <v>0</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
@@ -7132,26 +7132,26 @@
         </is>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I42">
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N42">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["68"]</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "76"]</t>
         </is>
       </c>
       <c r="AJ42">
@@ -7234,28 +7234,28 @@
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN42">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO42">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP42">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
@@ -7286,22 +7286,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -7314,111 +7314,111 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N43">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O43">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="P43">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="Q43">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="R43">
+        <v>1.93</v>
+      </c>
+      <c r="S43">
+        <v>1.42</v>
+      </c>
+      <c r="T43">
+        <v>2.62</v>
+      </c>
+      <c r="U43">
+        <v>2.9</v>
+      </c>
+      <c r="V43">
+        <v>1.35</v>
+      </c>
+      <c r="W43">
+        <v>1.03</v>
+      </c>
+      <c r="X43">
+        <v>1.04</v>
+      </c>
+      <c r="Y43">
+        <v>1.35</v>
+      </c>
+      <c r="Z43">
+        <v>2.74</v>
+      </c>
+      <c r="AA43">
         <v>2.15</v>
       </c>
-      <c r="S43">
-        <v>1.37</v>
-      </c>
-      <c r="T43">
-        <v>3.07</v>
-      </c>
-      <c r="U43">
-        <v>2.74</v>
-      </c>
-      <c r="V43">
-        <v>1.37</v>
-      </c>
-      <c r="W43">
+      <c r="AB43">
+        <v>1.65</v>
+      </c>
+      <c r="AC43">
+        <v>3.7</v>
+      </c>
+      <c r="AD43">
+        <v>1.22</v>
+      </c>
+      <c r="AE43">
+        <v>1.05</v>
+      </c>
+      <c r="AF43">
+        <v>1.83</v>
+      </c>
+      <c r="AG43">
+        <v>1.8</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>["17", "30"]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43">
+        <v>1.28</v>
+      </c>
+      <c r="AK43">
+        <v>1.58</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>5</v>
+      </c>
+      <c r="AN43">
+        <v>3</v>
+      </c>
+      <c r="AO43">
+        <v>11</v>
+      </c>
+      <c r="AP43">
+        <v>7</v>
+      </c>
+      <c r="AQ43">
+        <v>1.39</v>
+      </c>
+      <c r="AR43">
         <v>1.08</v>
       </c>
-      <c r="X43">
-        <v>1.01</v>
-      </c>
-      <c r="Y43">
-        <v>1.3</v>
-      </c>
-      <c r="Z43">
-        <v>3.4</v>
-      </c>
-      <c r="AA43">
-        <v>1.86</v>
-      </c>
-      <c r="AB43">
-        <v>1.91</v>
-      </c>
-      <c r="AC43">
-        <v>3.08</v>
-      </c>
-      <c r="AD43">
-        <v>1.28</v>
-      </c>
-      <c r="AE43">
-        <v>1.06</v>
-      </c>
-      <c r="AF43">
-        <v>1.68</v>
-      </c>
-      <c r="AG43">
-        <v>2.04</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ43">
-        <v>1.26</v>
-      </c>
-      <c r="AK43">
-        <v>1.65</v>
-      </c>
-      <c r="AL43">
-        <v>0</v>
-      </c>
-      <c r="AM43">
-        <v>-1</v>
-      </c>
-      <c r="AN43">
-        <v>-1</v>
-      </c>
-      <c r="AO43">
-        <v>-1</v>
-      </c>
-      <c r="AP43">
-        <v>-1</v>
-      </c>
-      <c r="AQ43">
-        <v>0</v>
-      </c>
-      <c r="AR43">
-        <v>0</v>
-      </c>
       <c r="AS43">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT43">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
@@ -7449,139 +7449,139 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N44">
+        <v>2.05</v>
+      </c>
+      <c r="O44">
+        <v>3.2</v>
+      </c>
+      <c r="P44">
+        <v>3.45</v>
+      </c>
+      <c r="Q44">
+        <v>2.7</v>
+      </c>
+      <c r="R44">
         <v>2.1</v>
       </c>
-      <c r="O44">
-        <v>3</v>
-      </c>
-      <c r="P44">
-        <v>3.25</v>
-      </c>
-      <c r="Q44">
-        <v>2.79</v>
-      </c>
-      <c r="R44">
-        <v>1.93</v>
-      </c>
       <c r="S44">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T44">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="U44">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="V44">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W44">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z44">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="AA44">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AB44">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AC44">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD44">
+        <v>1.3</v>
+      </c>
+      <c r="AE44">
+        <v>1.1</v>
+      </c>
+      <c r="AF44">
+        <v>1.75</v>
+      </c>
+      <c r="AG44">
+        <v>1.95</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>["22", "54", "63", "67"]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>["15", "17", "88"]</t>
+        </is>
+      </c>
+      <c r="AJ44">
         <v>1.22</v>
       </c>
-      <c r="AE44">
-        <v>1.05</v>
-      </c>
-      <c r="AF44">
-        <v>1.83</v>
-      </c>
-      <c r="AG44">
-        <v>1.8</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.28</v>
-      </c>
       <c r="AK44">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AL44">
         <v>0</v>
       </c>
       <c r="AM44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN44">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
@@ -7621,13 +7621,13 @@
         </is>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -7636,11 +7636,11 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N45">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21"]</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["55"]</t>
         </is>
       </c>
       <c r="AJ45">
@@ -7723,28 +7723,28 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN45">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP45">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ45">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AR45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS45">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT45">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
@@ -7775,100 +7775,100 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cannes</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46">
         <v>0</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46">
         <v>0</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N46">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="O46">
         <v>3.35</v>
       </c>
       <c r="P46">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="Q46">
-        <v>2.48</v>
+        <v>2.37</v>
       </c>
       <c r="R46">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="S46">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T46">
         <v>2.88</v>
       </c>
       <c r="U46">
-        <v>2.78</v>
+        <v>3.01</v>
       </c>
       <c r="V46">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W46">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y46">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z46">
+        <v>3.2</v>
+      </c>
+      <c r="AA46">
+        <v>2.02</v>
+      </c>
+      <c r="AB46">
+        <v>1.85</v>
+      </c>
+      <c r="AC46">
         <v>3.4</v>
       </c>
-      <c r="AA46">
-        <v>1.89</v>
-      </c>
-      <c r="AB46">
-        <v>1.82</v>
-      </c>
-      <c r="AC46">
-        <v>3.08</v>
-      </c>
       <c r="AD46">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE46">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF46">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG46">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "90+7"]</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
@@ -7880,34 +7880,34 @@
         <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AL46">
         <v>0</v>
       </c>
       <c r="AM46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN46">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO46">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP46">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ46">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR46">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS46">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT46">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
@@ -7938,112 +7938,112 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Cannes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47">
         <v>0</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47">
         <v>0</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N47">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="O47">
         <v>3.35</v>
       </c>
       <c r="P47">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="Q47">
-        <v>2.37</v>
+        <v>2.48</v>
       </c>
       <c r="R47">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="S47">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T47">
         <v>2.88</v>
       </c>
       <c r="U47">
-        <v>3.01</v>
+        <v>2.78</v>
       </c>
       <c r="V47">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W47">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
+        <v>1.29</v>
+      </c>
+      <c r="Z47">
+        <v>3.4</v>
+      </c>
+      <c r="AA47">
+        <v>1.89</v>
+      </c>
+      <c r="AB47">
+        <v>1.82</v>
+      </c>
+      <c r="AC47">
+        <v>3.08</v>
+      </c>
+      <c r="AD47">
         <v>1.32</v>
       </c>
-      <c r="Z47">
-        <v>3.2</v>
-      </c>
-      <c r="AA47">
-        <v>2.02</v>
-      </c>
-      <c r="AB47">
-        <v>1.85</v>
-      </c>
-      <c r="AC47">
-        <v>3.4</v>
-      </c>
-      <c r="AD47">
-        <v>1.28</v>
-      </c>
       <c r="AE47">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF47">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG47">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2"]</t>
         </is>
       </c>
       <c r="AJ47">
         <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8067,10 +8067,10 @@
         <v>0</v>
       </c>
       <c r="AS47">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT47">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
@@ -8101,22 +8101,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48">
         <v>0</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -8129,111 +8129,111 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N48">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="O48">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="P48">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="Q48">
         <v>2.7</v>
       </c>
       <c r="R48">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S48">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="T48">
-        <v>2.95</v>
+        <v>3.07</v>
       </c>
       <c r="U48">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="V48">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W48">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z48">
         <v>3.4</v>
       </c>
       <c r="AA48">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AB48">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AC48">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="AD48">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE48">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF48">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG48">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
+          <t>["40"]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ48">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK48">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL48">
         <v>0</v>
       </c>
       <c r="AM48">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN48">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO48">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP48">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ48">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AR48">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS48">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT48">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
@@ -8436,26 +8436,26 @@
         </is>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J50">
         <v>0</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N50">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "28", "54"]</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AJ50">
@@ -8538,28 +8538,28 @@
         <v>0</v>
       </c>
       <c r="AM50">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN50">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO50">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP50">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ50">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR50">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS50">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT50">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
@@ -8599,26 +8599,26 @@
         </is>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51">
         <v>0</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N51">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "17", "27", "58"]</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8"]</t>
         </is>
       </c>
       <c r="AJ51">
@@ -8701,28 +8701,28 @@
         <v>0</v>
       </c>
       <c r="AM51">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN51">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO51">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP51">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ51">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AR51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS51">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AT51">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
@@ -8762,26 +8762,26 @@
         </is>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N52">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61"]</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "83"]</t>
         </is>
       </c>
       <c r="AJ52">
@@ -8864,28 +8864,28 @@
         <v>0</v>
       </c>
       <c r="AM52">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN52">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO52">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP52">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ52">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR52">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS52">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT52">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
@@ -8925,26 +8925,26 @@
         </is>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N53">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "54", "79", "90+9"]</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+5", "56"]</t>
         </is>
       </c>
       <c r="AJ53">
@@ -9027,28 +9027,28 @@
         <v>0</v>
       </c>
       <c r="AM53">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN53">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO53">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP53">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ53">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AR53">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AS53">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT53">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
@@ -9088,26 +9088,26 @@
         </is>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J54">
         <v>0</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N54">
@@ -9172,12 +9172,12 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "26", "28", "82"]</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59", "64"]</t>
         </is>
       </c>
       <c r="AJ54">
@@ -9190,28 +9190,28 @@
         <v>0</v>
       </c>
       <c r="AM54">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN54">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO54">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP54">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ54">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AR54">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS54">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT54">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
@@ -9251,100 +9251,100 @@
         </is>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55">
         <v>0</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55">
         <v>0</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N55">
-        <v>3.7</v>
+        <v>3.46</v>
       </c>
       <c r="O55">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="P55">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q55">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="R55">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="S55">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="T55">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U55">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="V55">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W55">
         <v>1.03</v>
       </c>
       <c r="X55">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Y55">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z55">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AA55">
         <v>3</v>
       </c>
       <c r="AB55">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC55">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AD55">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE55">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF55">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AG55">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["80"]</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40"]</t>
         </is>
       </c>
       <c r="AJ55">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="AK55">
         <v>1.25</v>
@@ -9353,28 +9353,28 @@
         <v>0</v>
       </c>
       <c r="AM55">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN55">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO55">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP55">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ55">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AR55">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AS55">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT55">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
@@ -9414,26 +9414,26 @@
         </is>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H56">
         <v>0</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J56">
         <v>0</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56">
         <v>0</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N56">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "39", "61", "63"]</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
@@ -9516,28 +9516,28 @@
         <v>0</v>
       </c>
       <c r="AM56">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AN56">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO56">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP56">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ56">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AR56">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS56">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT56">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
@@ -10555,26 +10555,26 @@
         </is>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I63">
         <v>0</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N63">
@@ -10639,12 +10639,12 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+1"]</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "53", "90+7"]</t>
         </is>
       </c>
       <c r="AJ63">
@@ -10657,28 +10657,28 @@
         <v>0</v>
       </c>
       <c r="AM63">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN63">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO63">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP63">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ63">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AR63">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS63">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT63">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
@@ -10881,26 +10881,26 @@
         </is>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N65">
@@ -10965,12 +10965,12 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "51"]</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+4", "89", "90+3"]</t>
         </is>
       </c>
       <c r="AJ65">
@@ -10983,28 +10983,28 @@
         <v>0</v>
       </c>
       <c r="AM65">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN65">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO65">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP65">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ65">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR65">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS65">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT65">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
@@ -11044,26 +11044,26 @@
         </is>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66">
         <v>0</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N66">
@@ -11128,12 +11128,12 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "49", "90+4"]</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9"]</t>
         </is>
       </c>
       <c r="AJ66">
@@ -11146,28 +11146,28 @@
         <v>0</v>
       </c>
       <c r="AM66">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN66">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO66">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP66">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ66">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR66">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS66">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT66">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
@@ -11210,23 +11210,23 @@
         <v>0</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I67">
         <v>0</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N67">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "49"]</t>
         </is>
       </c>
       <c r="AJ67">
@@ -11309,28 +11309,28 @@
         <v>0</v>
       </c>
       <c r="AM67">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN67">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO67">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP67">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ67">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AR67">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS67">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT67">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
@@ -11533,26 +11533,26 @@
         </is>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69">
         <v>0</v>
       </c>
       <c r="K69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N69">
@@ -11617,12 +11617,12 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+3", "74", "89"]</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["62", "87"]</t>
         </is>
       </c>
       <c r="AJ69">
@@ -11635,28 +11635,28 @@
         <v>0</v>
       </c>
       <c r="AM69">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AN69">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO69">
-        <v>-1</v>
+        <v>30</v>
       </c>
       <c r="AP69">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ69">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AR69">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS69">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT69">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
@@ -11696,26 +11696,26 @@
         </is>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L70">
         <v>0</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N70">
@@ -11780,12 +11780,12 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["40", "52", "63", "82"]</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10"]</t>
         </is>
       </c>
       <c r="AJ70">
@@ -11798,28 +11798,28 @@
         <v>0</v>
       </c>
       <c r="AM70">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN70">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO70">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP70">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ70">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR70">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS70">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT70">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
@@ -11859,10 +11859,10 @@
         </is>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -11871,14 +11871,14 @@
         <v>0</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N71">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53", "90"]</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59", "61"]</t>
         </is>
       </c>
       <c r="AJ71">
@@ -11961,28 +11961,28 @@
         <v>0</v>
       </c>
       <c r="AM71">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AN71">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO71">
-        <v>-1</v>
+        <v>38</v>
       </c>
       <c r="AP71">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ71">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AR71">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS71">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AT71">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>0</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -12037,11 +12037,11 @@
         <v>0</v>
       </c>
       <c r="L72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N72">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+4"]</t>
         </is>
       </c>
       <c r="AJ72">
@@ -12124,28 +12124,28 @@
         <v>0</v>
       </c>
       <c r="AM72">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN72">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO72">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP72">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ72">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR72">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS72">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT72">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
@@ -12188,13 +12188,13 @@
         <v>0</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73">
         <v>0</v>
       </c>
       <c r="J73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73">
         <v>0</v>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N73">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7"]</t>
         </is>
       </c>
       <c r="AJ73">
@@ -12287,28 +12287,28 @@
         <v>0</v>
       </c>
       <c r="AM73">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN73">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO73">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP73">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ73">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AR73">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS73">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT73">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
@@ -12348,26 +12348,26 @@
         </is>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H74">
         <v>0</v>
       </c>
       <c r="I74">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J74">
         <v>0</v>
       </c>
       <c r="K74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74">
         <v>0</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N74">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "10", "17", "44", "51"]</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
@@ -12450,28 +12450,28 @@
         <v>0</v>
       </c>
       <c r="AM74">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN74">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO74">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP74">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ74">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR74">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AS74">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT74">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
@@ -12511,10 +12511,10 @@
         </is>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -12523,14 +12523,14 @@
         <v>0</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N75">
@@ -12595,12 +12595,12 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+5"]</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88"]</t>
         </is>
       </c>
       <c r="AJ75">
@@ -12613,28 +12613,28 @@
         <v>0</v>
       </c>
       <c r="AM75">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN75">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO75">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP75">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ75">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AR75">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AS75">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AT75">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
@@ -12674,16 +12674,16 @@
         </is>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76">
         <v>0</v>
@@ -12693,7 +12693,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N76">
@@ -12758,12 +12758,12 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18"]</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22"]</t>
         </is>
       </c>
       <c r="AJ76">
@@ -12776,28 +12776,28 @@
         <v>0</v>
       </c>
       <c r="AM76">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN76">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO76">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP76">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ76">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR76">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS76">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT76">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N77">
@@ -12939,28 +12939,28 @@
         <v>0</v>
       </c>
       <c r="AM77">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN77">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO77">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP77">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ77">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AR77">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS77">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT77">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -13015,11 +13015,11 @@
         <v>0</v>
       </c>
       <c r="L78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N78">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61"]</t>
         </is>
       </c>
       <c r="AJ78">
@@ -13102,28 +13102,28 @@
         <v>0</v>
       </c>
       <c r="AM78">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN78">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO78">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP78">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ78">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AR78">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="AS78">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT78">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
@@ -13163,26 +13163,26 @@
         </is>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H79">
         <v>0</v>
       </c>
       <c r="I79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79">
         <v>0</v>
       </c>
       <c r="K79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79">
         <v>0</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N79">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34", "72"]</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
@@ -13265,28 +13265,28 @@
         <v>0</v>
       </c>
       <c r="AM79">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN79">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO79">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP79">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ79">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR79">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AS79">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT79">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N80">
@@ -13428,28 +13428,28 @@
         <v>0</v>
       </c>
       <c r="AM80">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN80">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO80">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP80">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ80">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AR80">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AS80">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT80">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>0</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -13504,11 +13504,11 @@
         <v>0</v>
       </c>
       <c r="L81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N81">
@@ -13578,7 +13578,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72"]</t>
         </is>
       </c>
       <c r="AJ81">
@@ -13591,28 +13591,28 @@
         <v>0</v>
       </c>
       <c r="AM81">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN81">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO81">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP81">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ81">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR81">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AS81">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT81">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
@@ -13652,26 +13652,26 @@
         </is>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82">
         <v>0</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N82">
@@ -13736,12 +13736,12 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "90+5"]</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44"]</t>
         </is>
       </c>
       <c r="AJ82">
@@ -13754,28 +13754,28 @@
         <v>0</v>
       </c>
       <c r="AM82">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN82">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO82">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP82">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ82">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AR82">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS82">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT82">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
@@ -13815,26 +13815,26 @@
         </is>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N83">
@@ -13899,12 +13899,12 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "49", "54"]</t>
         </is>
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "72", "90+7"]</t>
         </is>
       </c>
       <c r="AJ83">
@@ -13917,28 +13917,28 @@
         <v>0</v>
       </c>
       <c r="AM83">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN83">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO83">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP83">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ83">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR83">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AS83">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT83">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84">
         <v>0</v>
@@ -13990,14 +13990,14 @@
         <v>0</v>
       </c>
       <c r="K84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84">
         <v>0</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N84">
@@ -14062,7 +14062,7 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["86"]</t>
         </is>
       </c>
       <c r="AI84" t="inlineStr">
@@ -14080,28 +14080,28 @@
         <v>0</v>
       </c>
       <c r="AM84">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN84">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO84">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP84">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ84">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR84">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS84">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AT84">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
@@ -14141,26 +14141,26 @@
         </is>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85">
         <v>0</v>
       </c>
       <c r="K85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N85">
@@ -14225,12 +14225,12 @@
       </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "54", "71"]</t>
         </is>
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89"]</t>
         </is>
       </c>
       <c r="AJ85">
@@ -14243,28 +14243,28 @@
         <v>0</v>
       </c>
       <c r="AM85">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN85">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO85">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP85">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ85">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AR85">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AS85">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT85">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
@@ -14304,26 +14304,26 @@
         </is>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N86">
@@ -14388,12 +14388,12 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "82", "90+3"]</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1", "37", "47"]</t>
         </is>
       </c>
       <c r="AJ86">
@@ -14406,28 +14406,28 @@
         <v>0</v>
       </c>
       <c r="AM86">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN86">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO86">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AP86">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ86">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AR86">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS86">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT86">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         </is>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -14479,14 +14479,14 @@
         <v>0</v>
       </c>
       <c r="K87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87">
         <v>0</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N87">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+8"]</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
@@ -14569,28 +14569,28 @@
         <v>0</v>
       </c>
       <c r="AM87">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN87">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO87">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AP87">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ87">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AR87">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS87">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AT87">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
@@ -14633,7 +14633,7 @@
         <v>0</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -14645,11 +14645,11 @@
         <v>0</v>
       </c>
       <c r="L88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N88">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65"]</t>
         </is>
       </c>
       <c r="AJ88">
@@ -14732,28 +14732,28 @@
         <v>0</v>
       </c>
       <c r="AM88">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN88">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO88">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP88">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ88">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR88">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS88">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AT88">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
@@ -14793,26 +14793,26 @@
         </is>
       </c>
       <c r="G89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N89">
@@ -14877,12 +14877,12 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "90+3"]</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "48"]</t>
         </is>
       </c>
       <c r="AJ89">
@@ -14895,28 +14895,28 @@
         <v>0</v>
       </c>
       <c r="AM89">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN89">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO89">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP89">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ89">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AR89">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS89">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT89">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
@@ -14956,13 +14956,13 @@
         </is>
       </c>
       <c r="G90">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I90">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -14971,11 +14971,11 @@
         <v>0</v>
       </c>
       <c r="L90">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N90">
@@ -15040,12 +15040,12 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "22", "41"]</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66", "68"]</t>
         </is>
       </c>
       <c r="AJ90">
@@ -15058,28 +15058,28 @@
         <v>0</v>
       </c>
       <c r="AM90">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN90">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO90">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP90">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ90">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AR90">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AS90">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT90">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
@@ -15119,10 +15119,10 @@
         </is>
       </c>
       <c r="G91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -15131,27 +15131,27 @@
         <v>0</v>
       </c>
       <c r="K91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N91">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="O91">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P91">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="Q91">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="R91">
         <v>2.02</v>
@@ -15163,7 +15163,7 @@
         <v>2.39</v>
       </c>
       <c r="U91">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="V91">
         <v>1.32</v>
@@ -15172,22 +15172,22 @@
         <v>1.06</v>
       </c>
       <c r="X91">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y91">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z91">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AA91">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AB91">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC91">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="AD91">
         <v>1.18</v>
@@ -15203,16 +15203,16 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72"]</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58"]</t>
         </is>
       </c>
       <c r="AJ91">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AK91">
         <v>1.3</v>
@@ -15239,10 +15239,10 @@
         <v>0</v>
       </c>
       <c r="AS91">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT91">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
@@ -15631,10 +15631,10 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="O94">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P94">
         <v>2.65</v>
@@ -15643,52 +15643,52 @@
         <v>2.85</v>
       </c>
       <c r="R94">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S94">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="T94">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="U94">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V94">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W94">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X94">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y94">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z94">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA94">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AB94">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC94">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD94">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE94">
         <v>1.1</v>
       </c>
       <c r="AF94">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG94">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK94">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,46 +15794,46 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="O95">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P95">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q95">
-        <v>3.56</v>
+        <v>3.75</v>
       </c>
       <c r="R95">
         <v>1.78</v>
       </c>
       <c r="S95">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="T95">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U95">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="V95">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="W95">
         <v>1.03</v>
       </c>
       <c r="X95">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Y95">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Z95">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AA95">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AB95">
         <v>1.3</v>
@@ -15842,7 +15842,7 @@
         <v>8</v>
       </c>
       <c r="AD95">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AE95">
         <v>1.02</v>
@@ -15851,7 +15851,7 @@
         <v>2.5</v>
       </c>
       <c r="AG95">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>1.4</v>
       </c>
       <c r="AK95">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -16292,7 +16292,7 @@
         <v>11</v>
       </c>
       <c r="Q98">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="R98">
         <v>3.6</v>
@@ -16307,7 +16307,7 @@
         <v>1.6</v>
       </c>
       <c r="V98">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="W98">
         <v>1.36</v>
@@ -16331,13 +16331,13 @@
         <v>1.5</v>
       </c>
       <c r="AD98">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AE98">
         <v>1.68</v>
       </c>
       <c r="AF98">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG98">
         <v>2</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK98">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,28 +16446,28 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="O99">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="P99">
-        <v>11.28</v>
+        <v>12</v>
       </c>
       <c r="Q99">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R99">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="S99">
         <v>1.2</v>
       </c>
       <c r="T99">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U99">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="V99">
         <v>1.57</v>
@@ -16476,7 +16476,7 @@
         <v>1.12</v>
       </c>
       <c r="X99">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y99">
         <v>1.2</v>
@@ -16485,25 +16485,25 @@
         <v>4.33</v>
       </c>
       <c r="AA99">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB99">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC99">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="AD99">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE99">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF99">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AG99">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK99">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16618,25 +16618,25 @@
         <v>3.61</v>
       </c>
       <c r="Q100">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R100">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="S100">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T100">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="U100">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="V100">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W100">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X100">
         <v>1.01</v>
@@ -16645,28 +16645,28 @@
         <v>1.22</v>
       </c>
       <c r="Z100">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA100">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AB100">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AC100">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AD100">
         <v>1.33</v>
       </c>
       <c r="AE100">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF100">
         <v>1.67</v>
       </c>
       <c r="AG100">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK100">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="O101">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P101">
-        <v>5.25</v>
+        <v>4.22</v>
       </c>
       <c r="Q101">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="R101">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S101">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T101">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="U101">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="V101">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W101">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X101">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y101">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z101">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA101">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB101">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AC101">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD101">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AE101">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AF101">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AG101">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>1.2</v>
       </c>
       <c r="AK101">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16944,55 +16944,55 @@
         <v>0</v>
       </c>
       <c r="Q102">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="R102">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="S102">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="T102">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U102">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="V102">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="W102">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X102">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z102">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA102">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AB102">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AC102">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AD102">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AE102">
         <v>1.19</v>
       </c>
       <c r="AF102">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AG102">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK102">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17107,55 +17107,55 @@
         <v>4.05</v>
       </c>
       <c r="Q103">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="R103">
+        <v>2.2</v>
+      </c>
+      <c r="S103">
+        <v>1.22</v>
+      </c>
+      <c r="T103">
+        <v>2.63</v>
+      </c>
+      <c r="U103">
+        <v>2.32</v>
+      </c>
+      <c r="V103">
+        <v>1.53</v>
+      </c>
+      <c r="W103">
+        <v>1.12</v>
+      </c>
+      <c r="X103">
+        <v>1.03</v>
+      </c>
+      <c r="Y103">
+        <v>1.15</v>
+      </c>
+      <c r="Z103">
+        <v>4.25</v>
+      </c>
+      <c r="AA103">
+        <v>1.61</v>
+      </c>
+      <c r="AB103">
         <v>2.15</v>
       </c>
-      <c r="S103">
-        <v>1.25</v>
-      </c>
-      <c r="T103">
-        <v>3.6</v>
-      </c>
-      <c r="U103">
-        <v>2.35</v>
-      </c>
-      <c r="V103">
-        <v>1.51</v>
-      </c>
-      <c r="W103">
-        <v>1.11</v>
-      </c>
-      <c r="X103">
-        <v>1.01</v>
-      </c>
-      <c r="Y103">
-        <v>1.16</v>
-      </c>
-      <c r="Z103">
-        <v>4.15</v>
-      </c>
-      <c r="AA103">
-        <v>1.62</v>
-      </c>
-      <c r="AB103">
-        <v>2.14</v>
-      </c>
       <c r="AC103">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="AD103">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE103">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF103">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG103">
-        <v>2.16</v>
+        <v>2.03</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK103">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17261,64 +17261,64 @@
         </is>
       </c>
       <c r="N104">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="O104">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P104">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="Q104">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="R104">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S104">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="T104">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="U104">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="V104">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W104">
         <v>1.11</v>
       </c>
       <c r="X104">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y104">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z104">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AA104">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB104">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AC104">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="AD104">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE104">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF104">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG104">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AK104">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AL104">
         <v>0</v>
